--- a/Sindhi Muslim/People Diary/January-2025.xlsx
+++ b/Sindhi Muslim/People Diary/January-2025.xlsx
@@ -8,24 +8,37 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\People Diary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC41F643-589E-4D64-BF22-18A46A00D7E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35332AD7-BA0F-4FD0-A2ED-6194E3576C97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01-01-2025" sheetId="1" r:id="rId1"/>
+    <sheet name="02-01-2025" sheetId="2" r:id="rId2"/>
+    <sheet name="03-01-2025" sheetId="3" r:id="rId3"/>
+    <sheet name="04-01-2025" sheetId="4" r:id="rId4"/>
+    <sheet name="06-01-2025" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="25">
   <si>
     <t>CLASS WISE ENROLLED SUMMARY</t>
   </si>
@@ -46,9 +59,6 @@
   </si>
   <si>
     <t>PERCENTAGE</t>
-  </si>
-  <si>
-    <t>ECE</t>
   </si>
   <si>
     <t>ONE</t>
@@ -81,10 +91,28 @@
     <t>Monthly Attendance Summary of Student GHS</t>
   </si>
   <si>
-    <t>SJCHS (January 2025)</t>
+    <t>SJCHS (January-2025)</t>
   </si>
   <si>
-    <t>Enrollment (01-01-2025)</t>
+    <t>ECE (ROSE)</t>
+  </si>
+  <si>
+    <t>ECE (Daffodils)</t>
+  </si>
+  <si>
+    <t>Enrollment (01-01-2025) (Wednesday)</t>
+  </si>
+  <si>
+    <t>Enrollment (02-01-2025) (Thursday)</t>
+  </si>
+  <si>
+    <t>Enrollment (03-01-2025) (Friday)</t>
+  </si>
+  <si>
+    <t>Enrollment (04-01-2025) (Saturday)</t>
+  </si>
+  <si>
+    <t>Enrollment (06-01-2025) (Monday)</t>
   </si>
 </sst>
 </file>
@@ -150,7 +178,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -189,21 +217,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -393,29 +406,35 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -425,6 +444,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -439,31 +461,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -744,10 +742,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.7109375" customWidth="1"/>
+    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.28515625" bestFit="1" customWidth="1"/>
@@ -758,202 +756,2045 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="17"/>
+    </row>
+    <row r="2" spans="1:8" ht="21" x14ac:dyDescent="0.35">
+      <c r="A2" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="7"/>
-    </row>
-    <row r="2" spans="1:8" ht="21" x14ac:dyDescent="0.35">
-      <c r="A2" s="8" t="s">
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="20"/>
+    </row>
+    <row r="3" spans="1:8" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="22"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="22"/>
+      <c r="H3" s="23"/>
+    </row>
+    <row r="4" spans="1:8" ht="48" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="9"/>
-    </row>
-    <row r="3" spans="1:8" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="10" t="s">
+      <c r="B5" s="4">
+        <v>30</v>
+      </c>
+      <c r="C5" s="4">
+        <v>24</v>
+      </c>
+      <c r="D5" s="4">
+        <f>B5+C5</f>
+        <v>54</v>
+      </c>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="1">
+        <f t="shared" ref="G5:G6" si="0">E5+F5</f>
+        <v>0</v>
+      </c>
+      <c r="H5" s="24">
+        <f t="shared" ref="H5:H15" si="1">G5/D5*100</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11"/>
-      <c r="H3" s="12"/>
-    </row>
-    <row r="4" spans="1:8" ht="48" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="16" t="s">
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4">
+        <f>B6+C6</f>
         <v>0</v>
       </c>
-      <c r="B4" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="F4" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="G4" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="H4" s="19" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="14"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="14"/>
-      <c r="H5" s="15"/>
-    </row>
-    <row r="6" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="3"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H6" s="24" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
     </row>
     <row r="7" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="3"/>
+        <v>7</v>
+      </c>
+      <c r="B7" s="1">
+        <v>32</v>
+      </c>
+      <c r="C7" s="1">
+        <v>23</v>
+      </c>
+      <c r="D7" s="4">
+        <f t="shared" ref="D7:D15" si="2">B7+C7</f>
+        <v>55</v>
+      </c>
+      <c r="E7" s="1">
+        <v>4</v>
+      </c>
+      <c r="F7" s="1">
+        <v>2</v>
+      </c>
+      <c r="G7" s="1">
+        <f>E7+F7</f>
+        <v>6</v>
+      </c>
+      <c r="H7" s="24">
+        <f t="shared" si="1"/>
+        <v>10.909090909090908</v>
+      </c>
     </row>
     <row r="8" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="3"/>
+        <v>8</v>
+      </c>
+      <c r="B8" s="1">
+        <v>26</v>
+      </c>
+      <c r="C8" s="1">
+        <v>26</v>
+      </c>
+      <c r="D8" s="4">
+        <f t="shared" si="2"/>
+        <v>52</v>
+      </c>
+      <c r="E8" s="1">
+        <v>3</v>
+      </c>
+      <c r="F8" s="1">
+        <v>1</v>
+      </c>
+      <c r="G8" s="1">
+        <f t="shared" ref="G8:G15" si="3">E8+F8</f>
+        <v>4</v>
+      </c>
+      <c r="H8" s="24">
+        <f t="shared" si="1"/>
+        <v>7.6923076923076925</v>
+      </c>
     </row>
     <row r="9" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="3"/>
+        <v>9</v>
+      </c>
+      <c r="B9" s="1">
+        <v>28</v>
+      </c>
+      <c r="C9" s="1">
+        <v>24</v>
+      </c>
+      <c r="D9" s="4">
+        <f t="shared" si="2"/>
+        <v>52</v>
+      </c>
+      <c r="E9" s="1">
+        <v>4</v>
+      </c>
+      <c r="F9" s="1">
+        <v>6</v>
+      </c>
+      <c r="G9" s="1">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="H9" s="24">
+        <f t="shared" si="1"/>
+        <v>19.230769230769234</v>
+      </c>
     </row>
     <row r="10" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="1">
+        <v>22</v>
+      </c>
+      <c r="C10" s="1">
+        <v>31</v>
+      </c>
+      <c r="D10" s="4">
+        <f t="shared" si="2"/>
+        <v>53</v>
+      </c>
+      <c r="E10" s="1">
+        <v>1</v>
+      </c>
+      <c r="F10" s="1">
+        <v>5</v>
+      </c>
+      <c r="G10" s="1">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="H10" s="24">
+        <f t="shared" si="1"/>
+        <v>11.320754716981133</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="1">
+        <v>23</v>
+      </c>
+      <c r="C11" s="1">
+        <v>23</v>
+      </c>
+      <c r="D11" s="4">
+        <f t="shared" si="2"/>
+        <v>46</v>
+      </c>
+      <c r="E11" s="1">
+        <v>5</v>
+      </c>
+      <c r="F11" s="1">
+        <v>2</v>
+      </c>
+      <c r="G11" s="1">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="H11" s="24">
+        <f t="shared" si="1"/>
+        <v>15.217391304347828</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
+      <c r="B12" s="1">
+        <v>17</v>
+      </c>
+      <c r="C12" s="1">
+        <v>25</v>
+      </c>
+      <c r="D12" s="4">
+        <f t="shared" si="2"/>
+        <v>42</v>
+      </c>
+      <c r="E12" s="1">
+        <v>10</v>
+      </c>
+      <c r="F12" s="1">
+        <v>7</v>
+      </c>
+      <c r="G12" s="1">
+        <f t="shared" si="3"/>
+        <v>17</v>
+      </c>
+      <c r="H12" s="24">
+        <f t="shared" si="1"/>
+        <v>40.476190476190474</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="1">
+        <v>27</v>
+      </c>
+      <c r="C13" s="1">
+        <v>18</v>
+      </c>
+      <c r="D13" s="4">
+        <f t="shared" si="2"/>
+        <v>45</v>
+      </c>
+      <c r="E13" s="1">
+        <v>3</v>
+      </c>
+      <c r="F13" s="1">
+        <v>2</v>
+      </c>
+      <c r="G13" s="1">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="H13" s="24">
+        <f t="shared" si="1"/>
+        <v>11.111111111111111</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="1">
+        <v>19</v>
+      </c>
+      <c r="C14" s="1">
+        <v>23</v>
+      </c>
+      <c r="D14" s="4">
+        <f t="shared" si="2"/>
+        <v>42</v>
+      </c>
+      <c r="E14" s="1">
+        <v>4</v>
+      </c>
+      <c r="F14" s="1">
+        <v>5</v>
+      </c>
+      <c r="G14" s="1">
+        <f t="shared" si="3"/>
+        <v>9</v>
+      </c>
+      <c r="H14" s="24">
+        <f t="shared" si="1"/>
+        <v>21.428571428571427</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="10">
+        <v>16</v>
+      </c>
+      <c r="C15" s="10">
+        <v>19</v>
+      </c>
+      <c r="D15" s="4">
+        <f t="shared" si="2"/>
+        <v>35</v>
+      </c>
+      <c r="E15" s="10">
+        <v>3</v>
+      </c>
+      <c r="F15" s="10">
+        <v>0</v>
+      </c>
+      <c r="G15" s="1">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="H15" s="24">
+        <f t="shared" si="1"/>
+        <v>8.5714285714285712</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="12"/>
+    </row>
+    <row r="17" spans="5:6" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E17" s="13"/>
+      <c r="F17" s="12"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:H3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6A76C6F-7346-4E3E-9D3A-7A332125E520}">
+  <dimension ref="A1:H17"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5703125" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" customWidth="1"/>
+    <col min="7" max="7" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.35">
+      <c r="A1" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="17"/>
+    </row>
+    <row r="2" spans="1:8" ht="21" x14ac:dyDescent="0.35">
+      <c r="A2" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="20"/>
+    </row>
+    <row r="3" spans="1:8" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="22"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="22"/>
+      <c r="H3" s="23"/>
+    </row>
+    <row r="4" spans="1:8" ht="48" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="4">
+        <v>30</v>
+      </c>
+      <c r="C5" s="4">
+        <v>24</v>
+      </c>
+      <c r="D5" s="4">
+        <f>B5+C5</f>
+        <v>54</v>
+      </c>
+      <c r="E5" s="4">
+        <v>8</v>
+      </c>
+      <c r="F5" s="4">
+        <v>11</v>
+      </c>
+      <c r="G5" s="1">
+        <f t="shared" ref="G5:G6" si="0">E5+F5</f>
+        <v>19</v>
+      </c>
+      <c r="H5" s="24">
+        <f>G5/D5*100</f>
+        <v>35.185185185185183</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="4">
+        <v>31</v>
+      </c>
+      <c r="C6" s="4">
+        <v>25</v>
+      </c>
+      <c r="D6" s="4">
+        <f>B6+C6</f>
+        <v>56</v>
+      </c>
+      <c r="E6" s="4">
+        <v>17</v>
+      </c>
+      <c r="F6" s="4">
+        <v>12</v>
+      </c>
+      <c r="G6" s="1">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="H6" s="24">
+        <f t="shared" ref="H6:H15" si="1">G6/D6*100</f>
+        <v>51.785714285714292</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="1">
+        <v>32</v>
+      </c>
+      <c r="C7" s="1">
+        <v>23</v>
+      </c>
+      <c r="D7" s="4">
+        <f t="shared" ref="D6:D7" si="2">B7+C7</f>
+        <v>55</v>
+      </c>
+      <c r="E7" s="1">
+        <v>17</v>
+      </c>
+      <c r="F7" s="1">
+        <v>14</v>
+      </c>
+      <c r="G7" s="1">
+        <f>E7+F7</f>
+        <v>31</v>
+      </c>
+      <c r="H7" s="24">
+        <f t="shared" si="1"/>
+        <v>56.36363636363636</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="1">
+        <v>26</v>
+      </c>
+      <c r="C8" s="1">
+        <v>26</v>
+      </c>
+      <c r="D8" s="4">
+        <f t="shared" ref="D8:D15" si="3">B8+C8</f>
+        <v>52</v>
+      </c>
+      <c r="E8" s="1">
+        <v>11</v>
+      </c>
+      <c r="F8" s="1">
+        <v>14</v>
+      </c>
+      <c r="G8" s="1">
+        <f t="shared" ref="G8:G15" si="4">E8+F8</f>
+        <v>25</v>
+      </c>
+      <c r="H8" s="24">
+        <f t="shared" si="1"/>
+        <v>48.07692307692308</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="1">
+        <v>28</v>
+      </c>
+      <c r="C9" s="1">
+        <v>24</v>
+      </c>
+      <c r="D9" s="4">
+        <f t="shared" si="3"/>
+        <v>52</v>
+      </c>
+      <c r="E9" s="1">
+        <v>16</v>
+      </c>
+      <c r="F9" s="1">
+        <v>13</v>
+      </c>
+      <c r="G9" s="1">
+        <f t="shared" si="4"/>
+        <v>29</v>
+      </c>
+      <c r="H9" s="24">
+        <f t="shared" si="1"/>
+        <v>55.769230769230774</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="1">
+        <v>22</v>
+      </c>
+      <c r="C10" s="1">
+        <v>31</v>
+      </c>
+      <c r="D10" s="4">
+        <f t="shared" si="3"/>
+        <v>53</v>
+      </c>
+      <c r="E10" s="1">
+        <v>5</v>
+      </c>
+      <c r="F10" s="1">
+        <v>12</v>
+      </c>
+      <c r="G10" s="1">
+        <f t="shared" si="4"/>
+        <v>17</v>
+      </c>
+      <c r="H10" s="24">
+        <f t="shared" si="1"/>
+        <v>32.075471698113205</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="1">
+        <v>23</v>
+      </c>
+      <c r="C11" s="1">
+        <v>23</v>
+      </c>
+      <c r="D11" s="4">
+        <f t="shared" si="3"/>
+        <v>46</v>
+      </c>
+      <c r="E11" s="1">
+        <v>9</v>
+      </c>
+      <c r="F11" s="1">
+        <v>7</v>
+      </c>
+      <c r="G11" s="1">
+        <f t="shared" si="4"/>
+        <v>16</v>
+      </c>
+      <c r="H11" s="24">
+        <f t="shared" si="1"/>
+        <v>34.782608695652172</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="1">
+        <v>17</v>
+      </c>
+      <c r="C12" s="1">
+        <v>25</v>
+      </c>
+      <c r="D12" s="4">
+        <f t="shared" si="3"/>
+        <v>42</v>
+      </c>
+      <c r="E12" s="1">
+        <v>2</v>
+      </c>
+      <c r="F12" s="1">
+        <v>10</v>
+      </c>
+      <c r="G12" s="1">
+        <f t="shared" si="4"/>
+        <v>12</v>
+      </c>
+      <c r="H12" s="24">
+        <f t="shared" si="1"/>
+        <v>28.571428571428569</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="1">
+        <v>27</v>
+      </c>
+      <c r="C13" s="1">
+        <v>18</v>
+      </c>
+      <c r="D13" s="4">
+        <f t="shared" si="3"/>
+        <v>45</v>
+      </c>
+      <c r="E13" s="1">
+        <v>12</v>
+      </c>
+      <c r="F13" s="1">
+        <v>11</v>
+      </c>
+      <c r="G13" s="1">
+        <f t="shared" si="4"/>
+        <v>23</v>
+      </c>
+      <c r="H13" s="24">
+        <f t="shared" si="1"/>
+        <v>51.111111111111107</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="1">
+        <v>19</v>
+      </c>
+      <c r="C14" s="1">
+        <v>23</v>
+      </c>
+      <c r="D14" s="4">
+        <f t="shared" si="3"/>
+        <v>42</v>
+      </c>
+      <c r="E14" s="1">
+        <v>8</v>
+      </c>
+      <c r="F14" s="1">
+        <v>10</v>
+      </c>
+      <c r="G14" s="1">
+        <f t="shared" si="4"/>
+        <v>18</v>
+      </c>
+      <c r="H14" s="24">
+        <f t="shared" si="1"/>
+        <v>42.857142857142854</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="10">
+        <v>16</v>
+      </c>
+      <c r="C15" s="10">
+        <v>19</v>
+      </c>
+      <c r="D15" s="4">
+        <f t="shared" si="3"/>
+        <v>35</v>
+      </c>
+      <c r="E15" s="10">
+        <v>9</v>
+      </c>
+      <c r="F15" s="10">
+        <v>9</v>
+      </c>
+      <c r="G15" s="1">
+        <f t="shared" si="4"/>
+        <v>18</v>
+      </c>
+      <c r="H15" s="24">
+        <f t="shared" si="1"/>
+        <v>51.428571428571423</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="12"/>
+    </row>
+    <row r="17" spans="5:6" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E17" s="13"/>
+      <c r="F17" s="12"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:H3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{943B4986-70E4-4CC7-A180-52208B012F00}">
+  <dimension ref="A1:H17"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5703125" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" customWidth="1"/>
+    <col min="7" max="7" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.35">
+      <c r="A1" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="17"/>
+    </row>
+    <row r="2" spans="1:8" ht="21" x14ac:dyDescent="0.35">
+      <c r="A2" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="20"/>
+    </row>
+    <row r="3" spans="1:8" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="22"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="22"/>
+      <c r="H3" s="23"/>
+    </row>
+    <row r="4" spans="1:8" ht="48" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="4">
+        <v>30</v>
+      </c>
+      <c r="C5" s="4">
+        <v>24</v>
+      </c>
+      <c r="D5" s="4">
+        <f>B5+C5</f>
+        <v>54</v>
+      </c>
+      <c r="E5" s="4">
+        <v>13</v>
+      </c>
+      <c r="F5" s="4">
+        <v>10</v>
+      </c>
+      <c r="G5" s="1">
+        <f t="shared" ref="G5:G6" si="0">E5+F5</f>
+        <v>23</v>
+      </c>
+      <c r="H5" s="24">
+        <f>G5/D5*100</f>
+        <v>42.592592592592595</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="4">
+        <v>31</v>
+      </c>
+      <c r="C6" s="4">
+        <v>25</v>
+      </c>
+      <c r="D6" s="4">
+        <f t="shared" ref="D6:D15" si="1">B6+C6</f>
+        <v>56</v>
+      </c>
+      <c r="E6" s="4">
+        <v>13</v>
+      </c>
+      <c r="F6" s="4">
+        <v>10</v>
+      </c>
+      <c r="G6" s="1">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="H6" s="24">
+        <f t="shared" ref="H6:H15" si="2">G6/D6*100</f>
+        <v>41.071428571428569</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="1">
+        <v>32</v>
+      </c>
+      <c r="C7" s="1">
+        <v>23</v>
+      </c>
+      <c r="D7" s="4">
+        <f t="shared" si="1"/>
+        <v>55</v>
+      </c>
+      <c r="E7" s="1">
+        <v>12</v>
+      </c>
+      <c r="F7" s="1">
+        <v>14</v>
+      </c>
+      <c r="G7" s="1">
+        <f>E7+F7</f>
+        <v>26</v>
+      </c>
+      <c r="H7" s="24">
+        <f t="shared" si="2"/>
+        <v>47.272727272727273</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="1">
+        <v>26</v>
+      </c>
+      <c r="C8" s="1">
+        <v>26</v>
+      </c>
+      <c r="D8" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="E8" s="1">
+        <v>12</v>
+      </c>
+      <c r="F8" s="1">
+        <v>14</v>
+      </c>
+      <c r="G8" s="1">
+        <f t="shared" ref="G8:G15" si="3">E8+F8</f>
+        <v>26</v>
+      </c>
+      <c r="H8" s="24">
+        <f t="shared" si="2"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="1">
+        <v>28</v>
+      </c>
+      <c r="C9" s="1">
+        <v>24</v>
+      </c>
+      <c r="D9" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="E9" s="1">
+        <v>12</v>
+      </c>
+      <c r="F9" s="1">
+        <v>13</v>
+      </c>
+      <c r="G9" s="1">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+      <c r="H9" s="24">
+        <f t="shared" si="2"/>
+        <v>48.07692307692308</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="1">
+        <v>22</v>
+      </c>
+      <c r="C10" s="1">
+        <v>30</v>
+      </c>
+      <c r="D10" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="E10" s="1">
+        <v>5</v>
+      </c>
+      <c r="F10" s="1">
+        <v>10</v>
+      </c>
+      <c r="G10" s="1">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="H10" s="24">
+        <f t="shared" si="2"/>
+        <v>28.846153846153843</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="1">
+        <v>23</v>
+      </c>
+      <c r="C11" s="1">
+        <v>23</v>
+      </c>
+      <c r="D11" s="4">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="E11" s="1">
+        <v>8</v>
+      </c>
+      <c r="F11" s="1">
+        <v>11</v>
+      </c>
+      <c r="G11" s="1">
+        <f t="shared" si="3"/>
+        <v>19</v>
+      </c>
+      <c r="H11" s="24">
+        <f t="shared" si="2"/>
+        <v>41.304347826086953</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="1">
+        <v>17</v>
+      </c>
+      <c r="C12" s="1">
+        <v>25</v>
+      </c>
+      <c r="D12" s="4">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="E12" s="1">
+        <v>3</v>
+      </c>
+      <c r="F12" s="1">
+        <v>12</v>
+      </c>
+      <c r="G12" s="1">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="H12" s="24">
+        <f t="shared" si="2"/>
+        <v>35.714285714285715</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="1">
+        <v>27</v>
+      </c>
+      <c r="C13" s="1">
+        <v>18</v>
+      </c>
+      <c r="D13" s="4">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="E13" s="1">
+        <v>10</v>
+      </c>
+      <c r="F13" s="1">
+        <v>11</v>
+      </c>
+      <c r="G13" s="1">
+        <f t="shared" si="3"/>
+        <v>21</v>
+      </c>
+      <c r="H13" s="24">
+        <f t="shared" si="2"/>
+        <v>46.666666666666664</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="1">
+        <v>19</v>
+      </c>
+      <c r="C14" s="1">
+        <v>23</v>
+      </c>
+      <c r="D14" s="4">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="E14" s="1">
+        <v>8</v>
+      </c>
+      <c r="F14" s="1">
+        <v>12</v>
+      </c>
+      <c r="G14" s="1">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="H14" s="24">
+        <f t="shared" si="2"/>
+        <v>47.619047619047613</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="10">
+        <v>16</v>
+      </c>
+      <c r="C15" s="10">
+        <v>19</v>
+      </c>
+      <c r="D15" s="4">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="E15" s="10">
+        <v>6</v>
+      </c>
+      <c r="F15" s="10">
+        <v>11</v>
+      </c>
+      <c r="G15" s="1">
+        <f t="shared" si="3"/>
+        <v>17</v>
+      </c>
+      <c r="H15" s="24">
+        <f t="shared" si="2"/>
+        <v>48.571428571428569</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="12"/>
+    </row>
+    <row r="17" spans="5:6" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E17" s="13"/>
+      <c r="F17" s="12"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:H3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9ED2B8D0-8AE0-4062-BC18-81E850C3EF3A}">
+  <dimension ref="A1:H17"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5703125" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" customWidth="1"/>
+    <col min="7" max="7" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.35">
+      <c r="A1" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="17"/>
+    </row>
+    <row r="2" spans="1:8" ht="21" x14ac:dyDescent="0.35">
+      <c r="A2" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="20"/>
+    </row>
+    <row r="3" spans="1:8" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="22"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="22"/>
+      <c r="H3" s="23"/>
+    </row>
+    <row r="4" spans="1:8" ht="48" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="4">
+        <v>30</v>
+      </c>
+      <c r="C5" s="4">
+        <v>24</v>
+      </c>
+      <c r="D5" s="4">
+        <f>B5+C5</f>
+        <v>54</v>
+      </c>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="1">
+        <f t="shared" ref="G5:G6" si="0">E5+F5</f>
+        <v>0</v>
+      </c>
+      <c r="H5" s="24">
+        <f>G5/D5*100</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="4">
+        <v>31</v>
+      </c>
+      <c r="C6" s="4">
+        <v>25</v>
+      </c>
+      <c r="D6" s="4">
+        <f t="shared" ref="D6:D15" si="1">B6+C6</f>
+        <v>56</v>
+      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H6" s="24">
+        <f t="shared" ref="H6:H15" si="2">G6/D6*100</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="1">
+        <v>32</v>
+      </c>
+      <c r="C7" s="1">
+        <v>23</v>
+      </c>
+      <c r="D7" s="4">
+        <f t="shared" si="1"/>
+        <v>55</v>
+      </c>
+      <c r="E7" s="1">
+        <v>10</v>
+      </c>
+      <c r="F7" s="1">
+        <v>10</v>
+      </c>
+      <c r="G7" s="1">
+        <f>E7+F7</f>
+        <v>20</v>
+      </c>
+      <c r="H7" s="24">
+        <f t="shared" si="2"/>
+        <v>36.363636363636367</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="1">
+        <v>26</v>
+      </c>
+      <c r="C8" s="1">
+        <v>26</v>
+      </c>
+      <c r="D8" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="E8" s="1">
+        <v>12</v>
+      </c>
+      <c r="F8" s="1">
+        <v>14</v>
+      </c>
+      <c r="G8" s="1">
+        <f t="shared" ref="G8:G15" si="3">E8+F8</f>
+        <v>26</v>
+      </c>
+      <c r="H8" s="24">
+        <f t="shared" si="2"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="1">
+        <v>28</v>
+      </c>
+      <c r="C9" s="1">
+        <v>24</v>
+      </c>
+      <c r="D9" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="E9" s="1">
+        <v>11</v>
+      </c>
+      <c r="F9" s="1">
+        <v>5</v>
+      </c>
+      <c r="G9" s="1">
+        <f t="shared" si="3"/>
+        <v>16</v>
+      </c>
+      <c r="H9" s="24">
+        <f t="shared" si="2"/>
+        <v>30.76923076923077</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="1">
+        <v>22</v>
+      </c>
+      <c r="C10" s="1">
+        <v>30</v>
+      </c>
+      <c r="D10" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="E10" s="1">
+        <v>4</v>
+      </c>
+      <c r="F10" s="1">
+        <v>14</v>
+      </c>
+      <c r="G10" s="1">
+        <f t="shared" si="3"/>
+        <v>18</v>
+      </c>
+      <c r="H10" s="24">
+        <f t="shared" si="2"/>
+        <v>34.615384615384613</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="1">
+        <v>23</v>
+      </c>
+      <c r="C11" s="1">
+        <v>23</v>
+      </c>
+      <c r="D11" s="4">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="E11" s="1">
+        <v>8</v>
+      </c>
+      <c r="F11" s="1">
+        <v>11</v>
+      </c>
+      <c r="G11" s="1">
+        <f t="shared" si="3"/>
+        <v>19</v>
+      </c>
+      <c r="H11" s="24">
+        <f t="shared" si="2"/>
+        <v>41.304347826086953</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="1">
+        <v>17</v>
+      </c>
+      <c r="C12" s="1">
+        <v>25</v>
+      </c>
+      <c r="D12" s="4">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="E12" s="1">
+        <v>2</v>
+      </c>
+      <c r="F12" s="1">
+        <v>15</v>
+      </c>
+      <c r="G12" s="1">
+        <f t="shared" si="3"/>
+        <v>17</v>
+      </c>
+      <c r="H12" s="24">
+        <f t="shared" si="2"/>
+        <v>40.476190476190474</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="1">
+        <v>27</v>
+      </c>
+      <c r="C13" s="1">
+        <v>18</v>
+      </c>
+      <c r="D13" s="4">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="E13" s="1">
+        <v>9</v>
+      </c>
+      <c r="F13" s="1">
+        <v>13</v>
+      </c>
+      <c r="G13" s="1">
+        <f t="shared" si="3"/>
+        <v>22</v>
+      </c>
+      <c r="H13" s="24">
+        <f t="shared" si="2"/>
+        <v>48.888888888888886</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="1">
+        <v>19</v>
+      </c>
+      <c r="C14" s="1">
+        <v>23</v>
+      </c>
+      <c r="D14" s="4">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="E14" s="1">
+        <v>8</v>
+      </c>
+      <c r="F14" s="1">
+        <v>10</v>
+      </c>
+      <c r="G14" s="1">
+        <f t="shared" si="3"/>
+        <v>18</v>
+      </c>
+      <c r="H14" s="24">
+        <f t="shared" si="2"/>
+        <v>42.857142857142854</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="10">
+        <v>16</v>
+      </c>
+      <c r="C15" s="10">
+        <v>19</v>
+      </c>
+      <c r="D15" s="4">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="E15" s="10">
+        <v>6</v>
+      </c>
+      <c r="F15" s="10">
+        <v>10</v>
+      </c>
+      <c r="G15" s="1">
+        <f t="shared" si="3"/>
+        <v>16</v>
+      </c>
+      <c r="H15" s="24">
+        <f t="shared" si="2"/>
+        <v>45.714285714285715</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="12"/>
+    </row>
+    <row r="17" spans="5:6" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E17" s="13"/>
+      <c r="F17" s="12"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:H3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C813D76-7268-4299-A57C-4EF0186DE3DE}">
+  <dimension ref="A1:H17"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5703125" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" customWidth="1"/>
+    <col min="7" max="7" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.35">
+      <c r="A1" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="17"/>
+    </row>
+    <row r="2" spans="1:8" ht="21" x14ac:dyDescent="0.35">
+      <c r="A2" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="20"/>
+    </row>
+    <row r="3" spans="1:8" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="22"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="22"/>
+      <c r="H3" s="23"/>
+    </row>
+    <row r="4" spans="1:8" ht="48" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="4">
+        <v>30</v>
+      </c>
+      <c r="C5" s="4">
+        <v>24</v>
+      </c>
+      <c r="D5" s="4">
+        <f>B5+C5</f>
+        <v>54</v>
+      </c>
+      <c r="E5" s="4">
+        <v>15</v>
+      </c>
+      <c r="F5" s="4">
+        <v>16</v>
+      </c>
+      <c r="G5" s="1">
+        <f t="shared" ref="G5:G6" si="0">E5+F5</f>
+        <v>31</v>
+      </c>
+      <c r="H5" s="24">
+        <f>G5/D5*100</f>
+        <v>57.407407407407405</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="4">
+        <v>31</v>
+      </c>
+      <c r="C6" s="4">
+        <v>25</v>
+      </c>
+      <c r="D6" s="4">
+        <f t="shared" ref="D6:D15" si="1">B6+C6</f>
+        <v>56</v>
+      </c>
+      <c r="E6" s="4">
+        <v>24</v>
+      </c>
+      <c r="F6" s="4">
+        <v>17</v>
+      </c>
+      <c r="G6" s="1">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="H6" s="24">
+        <f t="shared" ref="H6:H15" si="2">G6/D6*100</f>
+        <v>73.214285714285708</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="1">
+        <v>32</v>
+      </c>
+      <c r="C7" s="1">
+        <v>23</v>
+      </c>
+      <c r="D7" s="4">
+        <f t="shared" si="1"/>
+        <v>55</v>
+      </c>
+      <c r="E7" s="1">
+        <v>22</v>
+      </c>
+      <c r="F7" s="1">
+        <v>18</v>
+      </c>
+      <c r="G7" s="1">
+        <f>E7+F7</f>
+        <v>40</v>
+      </c>
+      <c r="H7" s="24">
+        <f t="shared" si="2"/>
+        <v>72.727272727272734</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="1">
+        <v>26</v>
+      </c>
+      <c r="C8" s="1">
+        <v>26</v>
+      </c>
+      <c r="D8" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="E8" s="1">
+        <v>18</v>
+      </c>
+      <c r="F8" s="1">
+        <v>15</v>
+      </c>
+      <c r="G8" s="1">
+        <f t="shared" ref="G8:G15" si="3">E8+F8</f>
+        <v>33</v>
+      </c>
+      <c r="H8" s="24">
+        <f t="shared" si="2"/>
+        <v>63.46153846153846</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="1">
+        <v>28</v>
+      </c>
+      <c r="C9" s="1">
+        <v>24</v>
+      </c>
+      <c r="D9" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="E9" s="1">
+        <v>18</v>
+      </c>
+      <c r="F9" s="1">
+        <v>16</v>
+      </c>
+      <c r="G9" s="1">
+        <f t="shared" si="3"/>
+        <v>34</v>
+      </c>
+      <c r="H9" s="24">
+        <f t="shared" si="2"/>
+        <v>65.384615384615387</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="1">
+        <v>22</v>
+      </c>
+      <c r="C10" s="1">
+        <v>30</v>
+      </c>
+      <c r="D10" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="3"/>
+      <c r="G10" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H10" s="24">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
+        <v>11</v>
+      </c>
+      <c r="B11" s="1">
+        <v>23</v>
+      </c>
+      <c r="C11" s="1">
+        <v>23</v>
+      </c>
+      <c r="D11" s="4">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="3"/>
+      <c r="G11" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H11" s="24">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
+        <v>12</v>
+      </c>
+      <c r="B12" s="1">
+        <v>17</v>
+      </c>
+      <c r="C12" s="1">
+        <v>25</v>
+      </c>
+      <c r="D12" s="4">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="3"/>
+      <c r="G12" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H12" s="24">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
+        <v>13</v>
+      </c>
+      <c r="B13" s="1">
+        <v>27</v>
+      </c>
+      <c r="C13" s="1">
+        <v>18</v>
+      </c>
+      <c r="D13" s="4">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="3"/>
-    </row>
-    <row r="14" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="20" t="s">
+      <c r="G13" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H13" s="24">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="1">
+        <v>19</v>
+      </c>
+      <c r="C14" s="1">
+        <v>23</v>
+      </c>
+      <c r="D14" s="4">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H14" s="24">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="10">
         <v>16</v>
       </c>
-      <c r="B14" s="21"/>
-      <c r="C14" s="21"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="21"/>
-      <c r="G14" s="21"/>
-      <c r="H14" s="22"/>
-    </row>
-    <row r="15" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="26" t="s">
+      <c r="C15" s="10">
+        <v>19</v>
+      </c>
+      <c r="D15" s="4">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H15" s="24">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="B15" s="23"/>
-      <c r="C15" s="23"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
-      <c r="G15" s="23"/>
-      <c r="H15" s="24"/>
-    </row>
-    <row r="16" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E16" s="25"/>
-      <c r="F16" s="24"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="12"/>
+    </row>
+    <row r="17" spans="5:6" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E17" s="13"/>
+      <c r="F17" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/Sindhi Muslim/People Diary/January-2025.xlsx
+++ b/Sindhi Muslim/People Diary/January-2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\People Diary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35332AD7-BA0F-4FD0-A2ED-6194E3576C97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1811AD4C-918E-49DB-BF86-72747619CC1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="14" activeTab="19" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01-01-2025" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,21 @@
     <sheet name="03-01-2025" sheetId="3" r:id="rId3"/>
     <sheet name="04-01-2025" sheetId="4" r:id="rId4"/>
     <sheet name="06-01-2025" sheetId="5" r:id="rId5"/>
+    <sheet name="07-01-2025" sheetId="6" r:id="rId6"/>
+    <sheet name="08-01-2025" sheetId="7" r:id="rId7"/>
+    <sheet name="09-01-2025" sheetId="8" r:id="rId8"/>
+    <sheet name="10-01-2025" sheetId="9" r:id="rId9"/>
+    <sheet name="11-01-2025" sheetId="10" r:id="rId10"/>
+    <sheet name="13-01-2025" sheetId="11" r:id="rId11"/>
+    <sheet name="14-01-2025" sheetId="12" r:id="rId12"/>
+    <sheet name="15-01-2025" sheetId="13" r:id="rId13"/>
+    <sheet name="16-01-2025" sheetId="14" r:id="rId14"/>
+    <sheet name="17-01-2025" sheetId="15" r:id="rId15"/>
+    <sheet name="18-01-2025" sheetId="16" r:id="rId16"/>
+    <sheet name="20-01-2025" sheetId="17" r:id="rId17"/>
+    <sheet name="21-01-2025" sheetId="18" r:id="rId18"/>
+    <sheet name="22-01-2025" sheetId="19" r:id="rId19"/>
+    <sheet name="23-01-2025" sheetId="20" r:id="rId20"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="21">
   <si>
     <t>CLASS WISE ENROLLED SUMMARY</t>
   </si>
@@ -100,25 +115,16 @@
     <t>ECE (Daffodils)</t>
   </si>
   <si>
-    <t>Enrollment (01-01-2025) (Wednesday)</t>
-  </si>
-  <si>
-    <t>Enrollment (02-01-2025) (Thursday)</t>
-  </si>
-  <si>
-    <t>Enrollment (03-01-2025) (Friday)</t>
-  </si>
-  <si>
-    <t>Enrollment (04-01-2025) (Saturday)</t>
-  </si>
-  <si>
-    <t>Enrollment (06-01-2025) (Monday)</t>
+    <t>ECE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="&quot;Enrollment&quot;\ \(dd\-mm\-yyyy\)\ \(dddd\)"/>
+  </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -178,7 +184,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="30">
     <border>
       <left/>
       <right/>
@@ -406,11 +412,162 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -434,6 +591,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -452,16 +620,24 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -756,40 +932,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="17"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="28"/>
     </row>
     <row r="2" spans="1:8" ht="21" x14ac:dyDescent="0.35">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="20"/>
-    </row>
-    <row r="3" spans="1:8" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" s="22"/>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="22"/>
-      <c r="F3" s="22"/>
-      <c r="G3" s="22"/>
-      <c r="H3" s="23"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="31"/>
+    </row>
+    <row r="3" spans="1:8" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="32">
+        <v>45658</v>
+      </c>
+      <c r="B3" s="33"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
+      <c r="H3" s="34"/>
     </row>
     <row r="4" spans="1:8" ht="48" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
@@ -831,36 +1007,48 @@
         <f>B5+C5</f>
         <v>54</v>
       </c>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
+      <c r="E5" s="4">
+        <v>3</v>
+      </c>
+      <c r="F5" s="4">
+        <v>2</v>
+      </c>
       <c r="G5" s="1">
         <f t="shared" ref="G5:G6" si="0">E5+F5</f>
-        <v>0</v>
-      </c>
-      <c r="H5" s="24">
+        <v>5</v>
+      </c>
+      <c r="H5" s="15">
         <f t="shared" ref="H5:H15" si="1">G5/D5*100</f>
-        <v>0</v>
+        <v>9.2592592592592595</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
+      <c r="B6" s="4">
+        <v>32</v>
+      </c>
+      <c r="C6" s="4">
+        <v>24</v>
+      </c>
       <c r="D6" s="4">
         <f>B6+C6</f>
-        <v>0</v>
-      </c>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
+        <v>56</v>
+      </c>
+      <c r="E6" s="4">
+        <v>16</v>
+      </c>
+      <c r="F6" s="4">
+        <v>12</v>
+      </c>
       <c r="G6" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H6" s="24" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>28</v>
+      </c>
+      <c r="H6" s="15">
+        <f t="shared" si="1"/>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -887,7 +1075,7 @@
         <f>E7+F7</f>
         <v>6</v>
       </c>
-      <c r="H7" s="24">
+      <c r="H7" s="15">
         <f t="shared" si="1"/>
         <v>10.909090909090908</v>
       </c>
@@ -916,7 +1104,7 @@
         <f t="shared" ref="G8:G15" si="3">E8+F8</f>
         <v>4</v>
       </c>
-      <c r="H8" s="24">
+      <c r="H8" s="15">
         <f t="shared" si="1"/>
         <v>7.6923076923076925</v>
       </c>
@@ -945,7 +1133,7 @@
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
-      <c r="H9" s="24">
+      <c r="H9" s="15">
         <f t="shared" si="1"/>
         <v>19.230769230769234</v>
       </c>
@@ -974,7 +1162,7 @@
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="H10" s="24">
+      <c r="H10" s="15">
         <f t="shared" si="1"/>
         <v>11.320754716981133</v>
       </c>
@@ -1003,7 +1191,7 @@
         <f t="shared" si="3"/>
         <v>7</v>
       </c>
-      <c r="H11" s="24">
+      <c r="H11" s="15">
         <f t="shared" si="1"/>
         <v>15.217391304347828</v>
       </c>
@@ -1032,7 +1220,7 @@
         <f t="shared" si="3"/>
         <v>17</v>
       </c>
-      <c r="H12" s="24">
+      <c r="H12" s="15">
         <f t="shared" si="1"/>
         <v>40.476190476190474</v>
       </c>
@@ -1061,7 +1249,7 @@
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="H13" s="24">
+      <c r="H13" s="15">
         <f t="shared" si="1"/>
         <v>11.111111111111111</v>
       </c>
@@ -1090,7 +1278,7 @@
         <f t="shared" si="3"/>
         <v>9</v>
       </c>
-      <c r="H14" s="24">
+      <c r="H14" s="15">
         <f t="shared" si="1"/>
         <v>21.428571428571427</v>
       </c>
@@ -1119,7 +1307,7 @@
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="H15" s="24">
+      <c r="H15" s="15">
         <f t="shared" si="1"/>
         <v>8.5714285714285712</v>
       </c>
@@ -1146,6 +1334,4173 @@
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A3:H3"/>
   </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48E3B2AA-DBE0-4B5E-8008-056C9A949320}">
+  <dimension ref="A1:H16"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5703125" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" customWidth="1"/>
+    <col min="7" max="7" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.35">
+      <c r="A1" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="28"/>
+    </row>
+    <row r="2" spans="1:8" ht="21" x14ac:dyDescent="0.35">
+      <c r="A2" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="31"/>
+    </row>
+    <row r="3" spans="1:8" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="32">
+        <v>45668</v>
+      </c>
+      <c r="B3" s="33"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
+      <c r="H3" s="34"/>
+    </row>
+    <row r="4" spans="1:8" ht="48" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="4">
+        <v>61</v>
+      </c>
+      <c r="C5" s="4">
+        <v>49</v>
+      </c>
+      <c r="D5" s="4">
+        <f>B5+C5</f>
+        <v>110</v>
+      </c>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="1">
+        <f t="shared" ref="G5" si="0">E5+F5</f>
+        <v>0</v>
+      </c>
+      <c r="H5" s="15">
+        <f>G5/D5*100</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="1">
+        <v>32</v>
+      </c>
+      <c r="C6" s="1">
+        <v>23</v>
+      </c>
+      <c r="D6" s="4">
+        <f t="shared" ref="D6:D14" si="1">B6+C6</f>
+        <v>55</v>
+      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="1">
+        <f>E6+F6</f>
+        <v>0</v>
+      </c>
+      <c r="H6" s="15">
+        <f t="shared" ref="H6:H14" si="2">G6/D6*100</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="1">
+        <v>26</v>
+      </c>
+      <c r="C7" s="1">
+        <v>26</v>
+      </c>
+      <c r="D7" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="E7" s="4">
+        <v>12</v>
+      </c>
+      <c r="F7" s="4">
+        <v>19</v>
+      </c>
+      <c r="G7" s="1">
+        <f t="shared" ref="G7:G14" si="3">E7+F7</f>
+        <v>31</v>
+      </c>
+      <c r="H7" s="15">
+        <f t="shared" si="2"/>
+        <v>59.615384615384613</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="1">
+        <v>28</v>
+      </c>
+      <c r="C8" s="1">
+        <v>24</v>
+      </c>
+      <c r="D8" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="E8" s="4">
+        <v>17</v>
+      </c>
+      <c r="F8" s="4">
+        <v>21</v>
+      </c>
+      <c r="G8" s="1">
+        <f t="shared" si="3"/>
+        <v>38</v>
+      </c>
+      <c r="H8" s="15">
+        <f t="shared" si="2"/>
+        <v>73.076923076923066</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="1">
+        <v>22</v>
+      </c>
+      <c r="C9" s="1">
+        <v>30</v>
+      </c>
+      <c r="D9" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="E9" s="4">
+        <v>14</v>
+      </c>
+      <c r="F9" s="4">
+        <v>23</v>
+      </c>
+      <c r="G9" s="1">
+        <f t="shared" si="3"/>
+        <v>37</v>
+      </c>
+      <c r="H9" s="15">
+        <f t="shared" si="2"/>
+        <v>71.15384615384616</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="1">
+        <v>23</v>
+      </c>
+      <c r="C10" s="1">
+        <v>23</v>
+      </c>
+      <c r="D10" s="4">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="E10" s="4">
+        <v>16</v>
+      </c>
+      <c r="F10" s="4">
+        <v>15</v>
+      </c>
+      <c r="G10" s="1">
+        <f t="shared" si="3"/>
+        <v>31</v>
+      </c>
+      <c r="H10" s="15">
+        <f t="shared" si="2"/>
+        <v>67.391304347826093</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="1">
+        <v>17</v>
+      </c>
+      <c r="C11" s="1">
+        <v>25</v>
+      </c>
+      <c r="D11" s="4">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="E11" s="4">
+        <v>13</v>
+      </c>
+      <c r="F11" s="4">
+        <v>19</v>
+      </c>
+      <c r="G11" s="1">
+        <f t="shared" si="3"/>
+        <v>32</v>
+      </c>
+      <c r="H11" s="15">
+        <f t="shared" si="2"/>
+        <v>76.19047619047619</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="1">
+        <v>27</v>
+      </c>
+      <c r="C12" s="1">
+        <v>18</v>
+      </c>
+      <c r="D12" s="4">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="E12" s="4">
+        <v>18</v>
+      </c>
+      <c r="F12" s="4">
+        <v>16</v>
+      </c>
+      <c r="G12" s="1">
+        <f t="shared" si="3"/>
+        <v>34</v>
+      </c>
+      <c r="H12" s="15">
+        <f t="shared" si="2"/>
+        <v>75.555555555555557</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="1">
+        <v>19</v>
+      </c>
+      <c r="C13" s="1">
+        <v>23</v>
+      </c>
+      <c r="D13" s="4">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="E13" s="4">
+        <v>10</v>
+      </c>
+      <c r="F13" s="4">
+        <v>13</v>
+      </c>
+      <c r="G13" s="1">
+        <f t="shared" si="3"/>
+        <v>23</v>
+      </c>
+      <c r="H13" s="15">
+        <f t="shared" si="2"/>
+        <v>54.761904761904766</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="10">
+        <v>16</v>
+      </c>
+      <c r="C14" s="10">
+        <v>19</v>
+      </c>
+      <c r="D14" s="4">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="E14" s="10">
+        <v>12</v>
+      </c>
+      <c r="F14" s="4">
+        <v>13</v>
+      </c>
+      <c r="G14" s="1">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+      <c r="H14" s="15">
+        <f t="shared" si="2"/>
+        <v>71.428571428571431</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="12"/>
+    </row>
+    <row r="16" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E16" s="13"/>
+      <c r="F16" s="12"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:H3"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Wrong Entry" error="Kindly Enter Value Less then Available Girls" sqref="F5:F14" xr:uid="{D39A5BFC-3292-4CAA-B430-3E5DA09579C2}">
+      <formula1>C5&gt;=F5</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Wrong Entry" error="Kindly Enter Value Less then Available Boys" sqref="E5:E13" xr:uid="{AF026129-D8F3-475A-9F36-F0D18A879EB5}">
+      <formula1>B5&gt;=E5</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42F1096B-ABC2-4A0E-90BC-9F43D6EF51F0}">
+  <dimension ref="A1:H16"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5703125" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" customWidth="1"/>
+    <col min="7" max="7" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.35">
+      <c r="A1" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="28"/>
+    </row>
+    <row r="2" spans="1:8" ht="21" x14ac:dyDescent="0.35">
+      <c r="A2" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="31"/>
+    </row>
+    <row r="3" spans="1:8" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="32">
+        <v>45670</v>
+      </c>
+      <c r="B3" s="33"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
+      <c r="H3" s="34"/>
+    </row>
+    <row r="4" spans="1:8" ht="48" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="4">
+        <v>61</v>
+      </c>
+      <c r="C5" s="4">
+        <v>49</v>
+      </c>
+      <c r="D5" s="4">
+        <f>B5+C5</f>
+        <v>110</v>
+      </c>
+      <c r="E5" s="4">
+        <v>49</v>
+      </c>
+      <c r="F5" s="4">
+        <v>41</v>
+      </c>
+      <c r="G5" s="1">
+        <f t="shared" ref="G5" si="0">E5+F5</f>
+        <v>90</v>
+      </c>
+      <c r="H5" s="15">
+        <f>G5/D5*100</f>
+        <v>81.818181818181827</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="1">
+        <v>32</v>
+      </c>
+      <c r="C6" s="1">
+        <v>23</v>
+      </c>
+      <c r="D6" s="4">
+        <f t="shared" ref="D6:D14" si="1">B6+C6</f>
+        <v>55</v>
+      </c>
+      <c r="E6" s="4">
+        <v>27</v>
+      </c>
+      <c r="F6" s="4">
+        <v>22</v>
+      </c>
+      <c r="G6" s="1">
+        <f>E6+F6</f>
+        <v>49</v>
+      </c>
+      <c r="H6" s="15">
+        <f t="shared" ref="H6:H14" si="2">G6/D6*100</f>
+        <v>89.090909090909093</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="1">
+        <v>26</v>
+      </c>
+      <c r="C7" s="1">
+        <v>26</v>
+      </c>
+      <c r="D7" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="E7" s="4">
+        <v>18</v>
+      </c>
+      <c r="F7" s="4">
+        <v>17</v>
+      </c>
+      <c r="G7" s="1">
+        <f t="shared" ref="G7:G14" si="3">E7+F7</f>
+        <v>35</v>
+      </c>
+      <c r="H7" s="15">
+        <f t="shared" si="2"/>
+        <v>67.307692307692307</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="1">
+        <v>28</v>
+      </c>
+      <c r="C8" s="1">
+        <v>24</v>
+      </c>
+      <c r="D8" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="E8" s="4">
+        <v>21</v>
+      </c>
+      <c r="F8" s="4">
+        <v>22</v>
+      </c>
+      <c r="G8" s="1">
+        <f t="shared" si="3"/>
+        <v>43</v>
+      </c>
+      <c r="H8" s="15">
+        <f t="shared" si="2"/>
+        <v>82.692307692307693</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="1">
+        <v>22</v>
+      </c>
+      <c r="C9" s="1">
+        <v>30</v>
+      </c>
+      <c r="D9" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="E9" s="4">
+        <v>16</v>
+      </c>
+      <c r="F9" s="4">
+        <v>27</v>
+      </c>
+      <c r="G9" s="1">
+        <f t="shared" si="3"/>
+        <v>43</v>
+      </c>
+      <c r="H9" s="15">
+        <f t="shared" si="2"/>
+        <v>82.692307692307693</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="1">
+        <v>23</v>
+      </c>
+      <c r="C10" s="1">
+        <v>23</v>
+      </c>
+      <c r="D10" s="4">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="E10" s="4">
+        <v>21</v>
+      </c>
+      <c r="F10" s="4">
+        <v>14</v>
+      </c>
+      <c r="G10" s="1">
+        <f t="shared" si="3"/>
+        <v>35</v>
+      </c>
+      <c r="H10" s="15">
+        <f t="shared" si="2"/>
+        <v>76.08695652173914</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="1">
+        <v>17</v>
+      </c>
+      <c r="C11" s="1">
+        <v>25</v>
+      </c>
+      <c r="D11" s="4">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="E11" s="4">
+        <v>15</v>
+      </c>
+      <c r="F11" s="4">
+        <v>20</v>
+      </c>
+      <c r="G11" s="1">
+        <f t="shared" si="3"/>
+        <v>35</v>
+      </c>
+      <c r="H11" s="15">
+        <f t="shared" si="2"/>
+        <v>83.333333333333343</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="1">
+        <v>27</v>
+      </c>
+      <c r="C12" s="1">
+        <v>18</v>
+      </c>
+      <c r="D12" s="4">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="E12" s="4">
+        <v>19</v>
+      </c>
+      <c r="F12" s="4">
+        <v>14</v>
+      </c>
+      <c r="G12" s="1">
+        <f t="shared" si="3"/>
+        <v>33</v>
+      </c>
+      <c r="H12" s="15">
+        <f t="shared" si="2"/>
+        <v>73.333333333333329</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="1">
+        <v>19</v>
+      </c>
+      <c r="C13" s="1">
+        <v>23</v>
+      </c>
+      <c r="D13" s="4">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="E13" s="4">
+        <v>14</v>
+      </c>
+      <c r="F13" s="4">
+        <v>16</v>
+      </c>
+      <c r="G13" s="1">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+      <c r="H13" s="15">
+        <f t="shared" si="2"/>
+        <v>71.428571428571431</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="10">
+        <v>16</v>
+      </c>
+      <c r="C14" s="10">
+        <v>19</v>
+      </c>
+      <c r="D14" s="4">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="E14" s="10">
+        <v>12</v>
+      </c>
+      <c r="F14" s="4">
+        <v>15</v>
+      </c>
+      <c r="G14" s="1">
+        <f t="shared" si="3"/>
+        <v>27</v>
+      </c>
+      <c r="H14" s="15">
+        <f t="shared" si="2"/>
+        <v>77.142857142857153</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="12"/>
+    </row>
+    <row r="16" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E16" s="13"/>
+      <c r="F16" s="12"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:H3"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Wrong Entry" error="Kindly Enter Value Less then Available Boys" sqref="E5:E13" xr:uid="{5BB6E8EE-AABD-495B-B619-1054BFCC8476}">
+      <formula1>B5&gt;=E5</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Wrong Entry" error="Kindly Enter Value Less then Available Girls" sqref="F5:F14" xr:uid="{DDA77982-76D0-4970-83DD-A476B5A7D23F}">
+      <formula1>C5&gt;=F5</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A5888A8-1E09-42C3-8B8A-4FE4BC82BF49}">
+  <dimension ref="A1:H16"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5703125" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" customWidth="1"/>
+    <col min="7" max="7" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.35">
+      <c r="A1" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="28"/>
+    </row>
+    <row r="2" spans="1:8" ht="21" x14ac:dyDescent="0.35">
+      <c r="A2" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="31"/>
+    </row>
+    <row r="3" spans="1:8" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="32">
+        <v>45671</v>
+      </c>
+      <c r="B3" s="33"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
+      <c r="H3" s="34"/>
+    </row>
+    <row r="4" spans="1:8" ht="48" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="4">
+        <v>61</v>
+      </c>
+      <c r="C5" s="4">
+        <v>49</v>
+      </c>
+      <c r="D5" s="4">
+        <f>B5+C5</f>
+        <v>110</v>
+      </c>
+      <c r="E5" s="4">
+        <v>50</v>
+      </c>
+      <c r="F5" s="4">
+        <v>37</v>
+      </c>
+      <c r="G5" s="1">
+        <f t="shared" ref="G5" si="0">E5+F5</f>
+        <v>87</v>
+      </c>
+      <c r="H5" s="15">
+        <f>G5/D5*100</f>
+        <v>79.090909090909093</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="1">
+        <v>32</v>
+      </c>
+      <c r="C6" s="1">
+        <v>23</v>
+      </c>
+      <c r="D6" s="4">
+        <f t="shared" ref="D6:D14" si="1">B6+C6</f>
+        <v>55</v>
+      </c>
+      <c r="E6" s="4">
+        <v>27</v>
+      </c>
+      <c r="F6" s="4">
+        <v>17</v>
+      </c>
+      <c r="G6" s="1">
+        <f>E6+F6</f>
+        <v>44</v>
+      </c>
+      <c r="H6" s="15">
+        <f t="shared" ref="H6:H14" si="2">G6/D6*100</f>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="1">
+        <v>26</v>
+      </c>
+      <c r="C7" s="1">
+        <v>26</v>
+      </c>
+      <c r="D7" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="E7" s="4">
+        <v>20</v>
+      </c>
+      <c r="F7" s="4">
+        <v>19</v>
+      </c>
+      <c r="G7" s="1">
+        <f t="shared" ref="G7:G14" si="3">E7+F7</f>
+        <v>39</v>
+      </c>
+      <c r="H7" s="15">
+        <f t="shared" si="2"/>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="1">
+        <v>28</v>
+      </c>
+      <c r="C8" s="1">
+        <v>24</v>
+      </c>
+      <c r="D8" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="E8" s="4">
+        <v>22</v>
+      </c>
+      <c r="F8" s="4">
+        <v>19</v>
+      </c>
+      <c r="G8" s="1">
+        <f t="shared" si="3"/>
+        <v>41</v>
+      </c>
+      <c r="H8" s="15">
+        <f t="shared" si="2"/>
+        <v>78.84615384615384</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="1">
+        <v>22</v>
+      </c>
+      <c r="C9" s="1">
+        <v>30</v>
+      </c>
+      <c r="D9" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="E9" s="4">
+        <v>16</v>
+      </c>
+      <c r="F9" s="4">
+        <v>23</v>
+      </c>
+      <c r="G9" s="1">
+        <f t="shared" si="3"/>
+        <v>39</v>
+      </c>
+      <c r="H9" s="15">
+        <f t="shared" si="2"/>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="1">
+        <v>23</v>
+      </c>
+      <c r="C10" s="1">
+        <v>23</v>
+      </c>
+      <c r="D10" s="4">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="E10" s="4">
+        <v>19</v>
+      </c>
+      <c r="F10" s="4">
+        <v>23</v>
+      </c>
+      <c r="G10" s="1">
+        <f t="shared" si="3"/>
+        <v>42</v>
+      </c>
+      <c r="H10" s="15">
+        <f t="shared" si="2"/>
+        <v>91.304347826086953</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="1">
+        <v>17</v>
+      </c>
+      <c r="C11" s="1">
+        <v>25</v>
+      </c>
+      <c r="D11" s="4">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="E11" s="4">
+        <v>15</v>
+      </c>
+      <c r="F11" s="4">
+        <v>22</v>
+      </c>
+      <c r="G11" s="1">
+        <f t="shared" si="3"/>
+        <v>37</v>
+      </c>
+      <c r="H11" s="15">
+        <f t="shared" si="2"/>
+        <v>88.095238095238088</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="1">
+        <v>27</v>
+      </c>
+      <c r="C12" s="1">
+        <v>18</v>
+      </c>
+      <c r="D12" s="4">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="E12" s="4">
+        <v>18</v>
+      </c>
+      <c r="F12" s="4">
+        <v>14</v>
+      </c>
+      <c r="G12" s="1">
+        <f t="shared" si="3"/>
+        <v>32</v>
+      </c>
+      <c r="H12" s="15">
+        <f t="shared" si="2"/>
+        <v>71.111111111111114</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="1">
+        <v>19</v>
+      </c>
+      <c r="C13" s="1">
+        <v>23</v>
+      </c>
+      <c r="D13" s="4">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="E13" s="4">
+        <v>14</v>
+      </c>
+      <c r="F13" s="4">
+        <v>18</v>
+      </c>
+      <c r="G13" s="1">
+        <f t="shared" si="3"/>
+        <v>32</v>
+      </c>
+      <c r="H13" s="15">
+        <f t="shared" si="2"/>
+        <v>76.19047619047619</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="10">
+        <v>16</v>
+      </c>
+      <c r="C14" s="10">
+        <v>19</v>
+      </c>
+      <c r="D14" s="4">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="E14" s="10">
+        <v>12</v>
+      </c>
+      <c r="F14" s="4">
+        <v>11</v>
+      </c>
+      <c r="G14" s="1">
+        <f t="shared" si="3"/>
+        <v>23</v>
+      </c>
+      <c r="H14" s="15">
+        <f t="shared" si="2"/>
+        <v>65.714285714285708</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" s="11">
+        <f t="shared" ref="B15:G15" si="4">SUM(B5:B14)</f>
+        <v>271</v>
+      </c>
+      <c r="C15" s="11">
+        <f t="shared" si="4"/>
+        <v>260</v>
+      </c>
+      <c r="D15" s="11">
+        <f t="shared" si="4"/>
+        <v>531</v>
+      </c>
+      <c r="E15" s="11">
+        <f t="shared" si="4"/>
+        <v>213</v>
+      </c>
+      <c r="F15" s="11">
+        <f t="shared" si="4"/>
+        <v>203</v>
+      </c>
+      <c r="G15" s="11">
+        <f t="shared" si="4"/>
+        <v>416</v>
+      </c>
+      <c r="H15" s="12"/>
+    </row>
+    <row r="16" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E16" s="13"/>
+      <c r="F16" s="12"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:H3"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Wrong Entry" error="Kindly Enter Value Less then Available Girls" sqref="F5:F14" xr:uid="{D67886D9-B5F0-44F3-985B-ADCEE61ED2FA}">
+      <formula1>C5&gt;=F5</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Wrong Entry" error="Kindly Enter Value Less then Available Boys" sqref="E5:E13" xr:uid="{85749E5F-7F8F-4350-A35D-C9368103AB8D}">
+      <formula1>B5&gt;=E5</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B66DE1C3-55C0-4FDB-BF17-C2192DFF87BC}">
+  <dimension ref="A1:H16"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5703125" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" customWidth="1"/>
+    <col min="7" max="7" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.35">
+      <c r="A1" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="28"/>
+    </row>
+    <row r="2" spans="1:8" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="31"/>
+    </row>
+    <row r="3" spans="1:8" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="35">
+        <v>45672</v>
+      </c>
+      <c r="B3" s="36"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="36"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="37"/>
+    </row>
+    <row r="4" spans="1:8" ht="48" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="18">
+        <v>61</v>
+      </c>
+      <c r="C5" s="18">
+        <v>49</v>
+      </c>
+      <c r="D5" s="18">
+        <f>B5+C5</f>
+        <v>110</v>
+      </c>
+      <c r="E5" s="18">
+        <v>50</v>
+      </c>
+      <c r="F5" s="18">
+        <v>39</v>
+      </c>
+      <c r="G5" s="18">
+        <f t="shared" ref="G5" si="0">E5+F5</f>
+        <v>89</v>
+      </c>
+      <c r="H5" s="19">
+        <f>G5/D5*100</f>
+        <v>80.909090909090907</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="1">
+        <v>32</v>
+      </c>
+      <c r="C6" s="1">
+        <v>23</v>
+      </c>
+      <c r="D6" s="4">
+        <f t="shared" ref="D6:D14" si="1">B6+C6</f>
+        <v>55</v>
+      </c>
+      <c r="E6" s="4">
+        <v>31</v>
+      </c>
+      <c r="F6" s="4">
+        <v>19</v>
+      </c>
+      <c r="G6" s="1">
+        <f>E6+F6</f>
+        <v>50</v>
+      </c>
+      <c r="H6" s="15">
+        <f t="shared" ref="H6:H15" si="2">G6/D6*100</f>
+        <v>90.909090909090907</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="1">
+        <v>26</v>
+      </c>
+      <c r="C7" s="1">
+        <v>26</v>
+      </c>
+      <c r="D7" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="E7" s="4">
+        <v>22</v>
+      </c>
+      <c r="F7" s="4">
+        <v>20</v>
+      </c>
+      <c r="G7" s="1">
+        <f t="shared" ref="G7:G14" si="3">E7+F7</f>
+        <v>42</v>
+      </c>
+      <c r="H7" s="15">
+        <f t="shared" si="2"/>
+        <v>80.769230769230774</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="1">
+        <v>28</v>
+      </c>
+      <c r="C8" s="1">
+        <v>24</v>
+      </c>
+      <c r="D8" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="E8" s="4">
+        <v>22</v>
+      </c>
+      <c r="F8" s="4">
+        <v>22</v>
+      </c>
+      <c r="G8" s="1">
+        <f t="shared" si="3"/>
+        <v>44</v>
+      </c>
+      <c r="H8" s="15">
+        <f t="shared" si="2"/>
+        <v>84.615384615384613</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="1">
+        <v>22</v>
+      </c>
+      <c r="C9" s="1">
+        <v>30</v>
+      </c>
+      <c r="D9" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="E9" s="4">
+        <v>13</v>
+      </c>
+      <c r="F9" s="4">
+        <v>27</v>
+      </c>
+      <c r="G9" s="1">
+        <f t="shared" si="3"/>
+        <v>40</v>
+      </c>
+      <c r="H9" s="15">
+        <f t="shared" si="2"/>
+        <v>76.923076923076934</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="1">
+        <v>23</v>
+      </c>
+      <c r="C10" s="1">
+        <v>23</v>
+      </c>
+      <c r="D10" s="4">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="E10" s="4">
+        <v>18</v>
+      </c>
+      <c r="F10" s="4">
+        <v>18</v>
+      </c>
+      <c r="G10" s="1">
+        <f t="shared" si="3"/>
+        <v>36</v>
+      </c>
+      <c r="H10" s="15">
+        <f t="shared" si="2"/>
+        <v>78.260869565217391</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="1">
+        <v>17</v>
+      </c>
+      <c r="C11" s="1">
+        <v>25</v>
+      </c>
+      <c r="D11" s="4">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="E11" s="4">
+        <v>15</v>
+      </c>
+      <c r="F11" s="4">
+        <v>21</v>
+      </c>
+      <c r="G11" s="1">
+        <f t="shared" si="3"/>
+        <v>36</v>
+      </c>
+      <c r="H11" s="15">
+        <f t="shared" si="2"/>
+        <v>85.714285714285708</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="1">
+        <v>27</v>
+      </c>
+      <c r="C12" s="1">
+        <v>18</v>
+      </c>
+      <c r="D12" s="4">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="E12" s="4">
+        <v>25</v>
+      </c>
+      <c r="F12" s="4">
+        <v>17</v>
+      </c>
+      <c r="G12" s="1">
+        <f t="shared" si="3"/>
+        <v>42</v>
+      </c>
+      <c r="H12" s="15">
+        <f t="shared" si="2"/>
+        <v>93.333333333333329</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="1">
+        <v>19</v>
+      </c>
+      <c r="C13" s="1">
+        <v>23</v>
+      </c>
+      <c r="D13" s="4">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="E13" s="4">
+        <v>15</v>
+      </c>
+      <c r="F13" s="4">
+        <v>17</v>
+      </c>
+      <c r="G13" s="1">
+        <f t="shared" si="3"/>
+        <v>32</v>
+      </c>
+      <c r="H13" s="15">
+        <f t="shared" si="2"/>
+        <v>76.19047619047619</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="21">
+        <v>16</v>
+      </c>
+      <c r="C14" s="21">
+        <v>19</v>
+      </c>
+      <c r="D14" s="16">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="E14" s="21">
+        <v>16</v>
+      </c>
+      <c r="F14" s="16">
+        <v>14</v>
+      </c>
+      <c r="G14" s="21">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+      <c r="H14" s="22">
+        <f t="shared" si="2"/>
+        <v>85.714285714285708</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" s="11">
+        <f t="shared" ref="B15:G15" si="4">SUM(B5:B14)</f>
+        <v>271</v>
+      </c>
+      <c r="C15" s="11">
+        <f t="shared" si="4"/>
+        <v>260</v>
+      </c>
+      <c r="D15" s="11">
+        <f t="shared" si="4"/>
+        <v>531</v>
+      </c>
+      <c r="E15" s="11">
+        <f t="shared" si="4"/>
+        <v>227</v>
+      </c>
+      <c r="F15" s="11">
+        <f t="shared" si="4"/>
+        <v>214</v>
+      </c>
+      <c r="G15" s="11">
+        <f t="shared" si="4"/>
+        <v>441</v>
+      </c>
+      <c r="H15" s="25">
+        <f t="shared" si="2"/>
+        <v>83.050847457627114</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E16" s="23"/>
+      <c r="F16" s="24"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:H3"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Wrong Entry" error="Kindly Enter Value Less then Available Boys" sqref="E5:E13" xr:uid="{C815BFC9-054B-43BA-8839-22FFD8FB1453}">
+      <formula1>B5&gt;=E5</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Wrong Entry" error="Kindly Enter Value Less then Available Girls" sqref="F5:F14" xr:uid="{78751C2D-94A3-4402-B4F5-53A62629A15F}">
+      <formula1>C5&gt;=F5</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B9768BF-B3A4-4B5B-A723-43A6C4FB05FE}">
+  <dimension ref="A1:H16"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5703125" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" customWidth="1"/>
+    <col min="7" max="7" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.35">
+      <c r="A1" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="28"/>
+    </row>
+    <row r="2" spans="1:8" ht="21" x14ac:dyDescent="0.35">
+      <c r="A2" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="31"/>
+    </row>
+    <row r="3" spans="1:8" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="32">
+        <v>45673</v>
+      </c>
+      <c r="B3" s="33"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
+      <c r="H3" s="34"/>
+    </row>
+    <row r="4" spans="1:8" ht="48" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="18">
+        <v>61</v>
+      </c>
+      <c r="C5" s="18">
+        <v>49</v>
+      </c>
+      <c r="D5" s="18">
+        <f>B5+C5</f>
+        <v>110</v>
+      </c>
+      <c r="E5" s="18">
+        <v>51</v>
+      </c>
+      <c r="F5" s="18">
+        <v>44</v>
+      </c>
+      <c r="G5" s="18">
+        <f t="shared" ref="G5" si="0">E5+F5</f>
+        <v>95</v>
+      </c>
+      <c r="H5" s="19">
+        <f>G5/D5*100</f>
+        <v>86.36363636363636</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="1">
+        <v>32</v>
+      </c>
+      <c r="C6" s="1">
+        <v>23</v>
+      </c>
+      <c r="D6" s="4">
+        <f t="shared" ref="D6:D14" si="1">B6+C6</f>
+        <v>55</v>
+      </c>
+      <c r="E6" s="4">
+        <v>30</v>
+      </c>
+      <c r="F6" s="4">
+        <v>18</v>
+      </c>
+      <c r="G6" s="1">
+        <f>E6+F6</f>
+        <v>48</v>
+      </c>
+      <c r="H6" s="15">
+        <f t="shared" ref="H6:H15" si="2">G6/D6*100</f>
+        <v>87.272727272727266</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="1">
+        <v>26</v>
+      </c>
+      <c r="C7" s="1">
+        <v>26</v>
+      </c>
+      <c r="D7" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="E7" s="4">
+        <v>20</v>
+      </c>
+      <c r="F7" s="4">
+        <v>20</v>
+      </c>
+      <c r="G7" s="1">
+        <f t="shared" ref="G7:G14" si="3">E7+F7</f>
+        <v>40</v>
+      </c>
+      <c r="H7" s="15">
+        <f t="shared" si="2"/>
+        <v>76.923076923076934</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="1">
+        <v>28</v>
+      </c>
+      <c r="C8" s="1">
+        <v>24</v>
+      </c>
+      <c r="D8" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="E8" s="4">
+        <v>22</v>
+      </c>
+      <c r="F8" s="4">
+        <v>21</v>
+      </c>
+      <c r="G8" s="1">
+        <f t="shared" si="3"/>
+        <v>43</v>
+      </c>
+      <c r="H8" s="15">
+        <f t="shared" si="2"/>
+        <v>82.692307692307693</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="1">
+        <v>22</v>
+      </c>
+      <c r="C9" s="1">
+        <v>30</v>
+      </c>
+      <c r="D9" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="E9" s="4">
+        <v>18</v>
+      </c>
+      <c r="F9" s="4">
+        <v>22</v>
+      </c>
+      <c r="G9" s="1">
+        <f t="shared" si="3"/>
+        <v>40</v>
+      </c>
+      <c r="H9" s="15">
+        <f t="shared" si="2"/>
+        <v>76.923076923076934</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="1">
+        <v>23</v>
+      </c>
+      <c r="C10" s="1">
+        <v>23</v>
+      </c>
+      <c r="D10" s="4">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="E10" s="4">
+        <v>19</v>
+      </c>
+      <c r="F10" s="4">
+        <v>16</v>
+      </c>
+      <c r="G10" s="1">
+        <f t="shared" si="3"/>
+        <v>35</v>
+      </c>
+      <c r="H10" s="15">
+        <f t="shared" si="2"/>
+        <v>76.08695652173914</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="1">
+        <v>17</v>
+      </c>
+      <c r="C11" s="1">
+        <v>25</v>
+      </c>
+      <c r="D11" s="4">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="E11" s="4">
+        <v>16</v>
+      </c>
+      <c r="F11" s="4">
+        <v>23</v>
+      </c>
+      <c r="G11" s="1">
+        <f t="shared" si="3"/>
+        <v>39</v>
+      </c>
+      <c r="H11" s="15">
+        <f t="shared" si="2"/>
+        <v>92.857142857142861</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="1">
+        <v>27</v>
+      </c>
+      <c r="C12" s="1">
+        <v>18</v>
+      </c>
+      <c r="D12" s="4">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="E12" s="4">
+        <v>25</v>
+      </c>
+      <c r="F12" s="4">
+        <v>17</v>
+      </c>
+      <c r="G12" s="1">
+        <f t="shared" si="3"/>
+        <v>42</v>
+      </c>
+      <c r="H12" s="15">
+        <f t="shared" si="2"/>
+        <v>93.333333333333329</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="1">
+        <v>19</v>
+      </c>
+      <c r="C13" s="1">
+        <v>23</v>
+      </c>
+      <c r="D13" s="4">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="E13" s="4">
+        <v>16</v>
+      </c>
+      <c r="F13" s="4">
+        <v>18</v>
+      </c>
+      <c r="G13" s="1">
+        <f t="shared" si="3"/>
+        <v>34</v>
+      </c>
+      <c r="H13" s="15">
+        <f t="shared" si="2"/>
+        <v>80.952380952380949</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="21">
+        <v>16</v>
+      </c>
+      <c r="C14" s="21">
+        <v>19</v>
+      </c>
+      <c r="D14" s="16">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="E14" s="21">
+        <v>15</v>
+      </c>
+      <c r="F14" s="16">
+        <v>14</v>
+      </c>
+      <c r="G14" s="21">
+        <f t="shared" si="3"/>
+        <v>29</v>
+      </c>
+      <c r="H14" s="22">
+        <f t="shared" si="2"/>
+        <v>82.857142857142861</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" s="11">
+        <f t="shared" ref="B15:G15" si="4">SUM(B5:B14)</f>
+        <v>271</v>
+      </c>
+      <c r="C15" s="11">
+        <f t="shared" si="4"/>
+        <v>260</v>
+      </c>
+      <c r="D15" s="11">
+        <f t="shared" si="4"/>
+        <v>531</v>
+      </c>
+      <c r="E15" s="11">
+        <f t="shared" si="4"/>
+        <v>232</v>
+      </c>
+      <c r="F15" s="11">
+        <f t="shared" si="4"/>
+        <v>213</v>
+      </c>
+      <c r="G15" s="11">
+        <f t="shared" si="4"/>
+        <v>445</v>
+      </c>
+      <c r="H15" s="25">
+        <f t="shared" si="2"/>
+        <v>83.804143126177024</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E16" s="23"/>
+      <c r="F16" s="24"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:H3"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Wrong Entry" error="Kindly Enter Value Less then Available Girls" sqref="F5:F14" xr:uid="{75420EF7-1555-4EF0-8F32-860E291D9460}">
+      <formula1>C5&gt;=F5</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Wrong Entry" error="Kindly Enter Value Less then Available Boys" sqref="E5:E13" xr:uid="{13D1A81B-0ECB-42C6-9A23-073C4D6F4F11}">
+      <formula1>B5&gt;=E5</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09C7376B-DBA3-42C7-BF5C-7993F5324B10}">
+  <dimension ref="A1:H16"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5703125" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" customWidth="1"/>
+    <col min="7" max="7" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.35">
+      <c r="A1" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="28"/>
+    </row>
+    <row r="2" spans="1:8" ht="21" x14ac:dyDescent="0.35">
+      <c r="A2" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="31"/>
+    </row>
+    <row r="3" spans="1:8" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="32">
+        <v>45674</v>
+      </c>
+      <c r="B3" s="33"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
+      <c r="H3" s="34"/>
+    </row>
+    <row r="4" spans="1:8" ht="48" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="18">
+        <v>61</v>
+      </c>
+      <c r="C5" s="18">
+        <v>49</v>
+      </c>
+      <c r="D5" s="18">
+        <f>B5+C5</f>
+        <v>110</v>
+      </c>
+      <c r="E5" s="18">
+        <v>43</v>
+      </c>
+      <c r="F5" s="18">
+        <v>37</v>
+      </c>
+      <c r="G5" s="18">
+        <f t="shared" ref="G5" si="0">E5+F5</f>
+        <v>80</v>
+      </c>
+      <c r="H5" s="19">
+        <f>G5/D5*100</f>
+        <v>72.727272727272734</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="1">
+        <v>32</v>
+      </c>
+      <c r="C6" s="1">
+        <v>23</v>
+      </c>
+      <c r="D6" s="4">
+        <f t="shared" ref="D6:D14" si="1">B6+C6</f>
+        <v>55</v>
+      </c>
+      <c r="E6" s="4">
+        <v>26</v>
+      </c>
+      <c r="F6" s="4">
+        <v>21</v>
+      </c>
+      <c r="G6" s="1">
+        <f>E6+F6</f>
+        <v>47</v>
+      </c>
+      <c r="H6" s="15">
+        <f t="shared" ref="H6:H15" si="2">G6/D6*100</f>
+        <v>85.454545454545453</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="1">
+        <v>26</v>
+      </c>
+      <c r="C7" s="1">
+        <v>26</v>
+      </c>
+      <c r="D7" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="E7" s="4">
+        <v>20</v>
+      </c>
+      <c r="F7" s="4">
+        <v>17</v>
+      </c>
+      <c r="G7" s="1">
+        <f t="shared" ref="G7:G14" si="3">E7+F7</f>
+        <v>37</v>
+      </c>
+      <c r="H7" s="15">
+        <f t="shared" si="2"/>
+        <v>71.15384615384616</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="1">
+        <v>28</v>
+      </c>
+      <c r="C8" s="1">
+        <v>24</v>
+      </c>
+      <c r="D8" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="E8" s="4">
+        <v>23</v>
+      </c>
+      <c r="F8" s="4">
+        <v>23</v>
+      </c>
+      <c r="G8" s="1">
+        <f t="shared" si="3"/>
+        <v>46</v>
+      </c>
+      <c r="H8" s="15">
+        <f t="shared" si="2"/>
+        <v>88.461538461538453</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="1">
+        <v>22</v>
+      </c>
+      <c r="C9" s="1">
+        <v>30</v>
+      </c>
+      <c r="D9" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="E9" s="4">
+        <v>16</v>
+      </c>
+      <c r="F9" s="4">
+        <v>21</v>
+      </c>
+      <c r="G9" s="1">
+        <f t="shared" si="3"/>
+        <v>37</v>
+      </c>
+      <c r="H9" s="15">
+        <f t="shared" si="2"/>
+        <v>71.15384615384616</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="1">
+        <v>23</v>
+      </c>
+      <c r="C10" s="1">
+        <v>23</v>
+      </c>
+      <c r="D10" s="4">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="E10" s="4">
+        <v>19</v>
+      </c>
+      <c r="F10" s="4">
+        <v>17</v>
+      </c>
+      <c r="G10" s="1">
+        <f t="shared" si="3"/>
+        <v>36</v>
+      </c>
+      <c r="H10" s="15">
+        <f t="shared" si="2"/>
+        <v>78.260869565217391</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="1">
+        <v>17</v>
+      </c>
+      <c r="C11" s="1">
+        <v>25</v>
+      </c>
+      <c r="D11" s="4">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="E11" s="4">
+        <v>14</v>
+      </c>
+      <c r="F11" s="4">
+        <v>23</v>
+      </c>
+      <c r="G11" s="1">
+        <f t="shared" si="3"/>
+        <v>37</v>
+      </c>
+      <c r="H11" s="15">
+        <f t="shared" si="2"/>
+        <v>88.095238095238088</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="1">
+        <v>27</v>
+      </c>
+      <c r="C12" s="1">
+        <v>18</v>
+      </c>
+      <c r="D12" s="4">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="E12" s="4">
+        <v>23</v>
+      </c>
+      <c r="F12" s="4">
+        <v>16</v>
+      </c>
+      <c r="G12" s="1">
+        <f t="shared" si="3"/>
+        <v>39</v>
+      </c>
+      <c r="H12" s="15">
+        <f t="shared" si="2"/>
+        <v>86.666666666666671</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="1">
+        <v>19</v>
+      </c>
+      <c r="C13" s="1">
+        <v>23</v>
+      </c>
+      <c r="D13" s="4">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="E13" s="4">
+        <v>13</v>
+      </c>
+      <c r="F13" s="4">
+        <v>20</v>
+      </c>
+      <c r="G13" s="1">
+        <f t="shared" si="3"/>
+        <v>33</v>
+      </c>
+      <c r="H13" s="15">
+        <f t="shared" si="2"/>
+        <v>78.571428571428569</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="21">
+        <v>16</v>
+      </c>
+      <c r="C14" s="21">
+        <v>19</v>
+      </c>
+      <c r="D14" s="16">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="E14" s="21">
+        <v>15</v>
+      </c>
+      <c r="F14" s="16">
+        <v>15</v>
+      </c>
+      <c r="G14" s="21">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+      <c r="H14" s="22">
+        <f t="shared" si="2"/>
+        <v>85.714285714285708</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" s="11">
+        <f t="shared" ref="B15:G15" si="4">SUM(B5:B14)</f>
+        <v>271</v>
+      </c>
+      <c r="C15" s="11">
+        <f t="shared" si="4"/>
+        <v>260</v>
+      </c>
+      <c r="D15" s="11">
+        <f t="shared" si="4"/>
+        <v>531</v>
+      </c>
+      <c r="E15" s="11">
+        <f t="shared" si="4"/>
+        <v>212</v>
+      </c>
+      <c r="F15" s="11">
+        <f t="shared" si="4"/>
+        <v>210</v>
+      </c>
+      <c r="G15" s="11">
+        <f t="shared" si="4"/>
+        <v>422</v>
+      </c>
+      <c r="H15" s="25">
+        <f t="shared" si="2"/>
+        <v>79.472693032015059</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E16" s="23"/>
+      <c r="F16" s="24"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:H3"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Wrong Entry" error="Kindly Enter Value Less then Available Boys" sqref="E5:E13" xr:uid="{3781A471-CF14-47B9-BDD9-53B6B48BE11E}">
+      <formula1>B5&gt;=E5</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Wrong Entry" error="Kindly Enter Value Less then Available Girls" sqref="F5:F14" xr:uid="{2919C1E8-20DF-4C2A-BE4A-D74445B425CF}">
+      <formula1>C5&gt;=F5</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4EBB64E-9213-43F5-8CBD-944011632933}">
+  <dimension ref="A1:H16"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5703125" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" customWidth="1"/>
+    <col min="7" max="7" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.35">
+      <c r="A1" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="28"/>
+    </row>
+    <row r="2" spans="1:8" ht="21" x14ac:dyDescent="0.35">
+      <c r="A2" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="31"/>
+    </row>
+    <row r="3" spans="1:8" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="32">
+        <v>45675</v>
+      </c>
+      <c r="B3" s="33"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
+      <c r="H3" s="34"/>
+    </row>
+    <row r="4" spans="1:8" ht="48" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="18">
+        <v>61</v>
+      </c>
+      <c r="C5" s="18">
+        <v>49</v>
+      </c>
+      <c r="D5" s="18">
+        <f>B5+C5</f>
+        <v>110</v>
+      </c>
+      <c r="E5" s="18">
+        <v>38</v>
+      </c>
+      <c r="F5" s="18">
+        <v>30</v>
+      </c>
+      <c r="G5" s="18">
+        <f t="shared" ref="G5" si="0">E5+F5</f>
+        <v>68</v>
+      </c>
+      <c r="H5" s="19">
+        <f>G5/D5*100</f>
+        <v>61.818181818181813</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="1">
+        <v>32</v>
+      </c>
+      <c r="C6" s="1">
+        <v>23</v>
+      </c>
+      <c r="D6" s="4">
+        <f t="shared" ref="D6:D14" si="1">B6+C6</f>
+        <v>55</v>
+      </c>
+      <c r="E6" s="4">
+        <v>28</v>
+      </c>
+      <c r="F6" s="4">
+        <v>16</v>
+      </c>
+      <c r="G6" s="1">
+        <f>E6+F6</f>
+        <v>44</v>
+      </c>
+      <c r="H6" s="15">
+        <f t="shared" ref="H6:H15" si="2">G6/D6*100</f>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="1">
+        <v>26</v>
+      </c>
+      <c r="C7" s="1">
+        <v>26</v>
+      </c>
+      <c r="D7" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="E7" s="4">
+        <v>21</v>
+      </c>
+      <c r="F7" s="4">
+        <v>13</v>
+      </c>
+      <c r="G7" s="1">
+        <f t="shared" ref="G7:G14" si="3">E7+F7</f>
+        <v>34</v>
+      </c>
+      <c r="H7" s="15">
+        <f t="shared" si="2"/>
+        <v>65.384615384615387</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="1">
+        <v>28</v>
+      </c>
+      <c r="C8" s="1">
+        <v>24</v>
+      </c>
+      <c r="D8" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="E8" s="4">
+        <v>18</v>
+      </c>
+      <c r="F8" s="4">
+        <v>19</v>
+      </c>
+      <c r="G8" s="1">
+        <f t="shared" si="3"/>
+        <v>37</v>
+      </c>
+      <c r="H8" s="15">
+        <f t="shared" si="2"/>
+        <v>71.15384615384616</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="1">
+        <v>22</v>
+      </c>
+      <c r="C9" s="1">
+        <v>30</v>
+      </c>
+      <c r="D9" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="E9" s="4">
+        <v>14</v>
+      </c>
+      <c r="F9" s="4">
+        <v>25</v>
+      </c>
+      <c r="G9" s="1">
+        <f t="shared" si="3"/>
+        <v>39</v>
+      </c>
+      <c r="H9" s="15">
+        <f t="shared" si="2"/>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="1">
+        <v>23</v>
+      </c>
+      <c r="C10" s="1">
+        <v>23</v>
+      </c>
+      <c r="D10" s="4">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="E10" s="4">
+        <v>15</v>
+      </c>
+      <c r="F10" s="4">
+        <v>12</v>
+      </c>
+      <c r="G10" s="1">
+        <f t="shared" si="3"/>
+        <v>27</v>
+      </c>
+      <c r="H10" s="15">
+        <f t="shared" si="2"/>
+        <v>58.695652173913047</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="1">
+        <v>17</v>
+      </c>
+      <c r="C11" s="1">
+        <v>25</v>
+      </c>
+      <c r="D11" s="4">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="E11" s="4">
+        <v>13</v>
+      </c>
+      <c r="F11" s="4">
+        <v>20</v>
+      </c>
+      <c r="G11" s="1">
+        <f t="shared" si="3"/>
+        <v>33</v>
+      </c>
+      <c r="H11" s="15">
+        <f t="shared" si="2"/>
+        <v>78.571428571428569</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="1">
+        <v>27</v>
+      </c>
+      <c r="C12" s="1">
+        <v>18</v>
+      </c>
+      <c r="D12" s="4">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="E12" s="4">
+        <v>20</v>
+      </c>
+      <c r="F12" s="4">
+        <v>17</v>
+      </c>
+      <c r="G12" s="1">
+        <f t="shared" si="3"/>
+        <v>37</v>
+      </c>
+      <c r="H12" s="15">
+        <f t="shared" si="2"/>
+        <v>82.222222222222214</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="1">
+        <v>19</v>
+      </c>
+      <c r="C13" s="1">
+        <v>23</v>
+      </c>
+      <c r="D13" s="4">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="E13" s="4">
+        <v>10</v>
+      </c>
+      <c r="F13" s="4">
+        <v>18</v>
+      </c>
+      <c r="G13" s="1">
+        <f t="shared" si="3"/>
+        <v>28</v>
+      </c>
+      <c r="H13" s="15">
+        <f t="shared" si="2"/>
+        <v>66.666666666666657</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="21">
+        <v>16</v>
+      </c>
+      <c r="C14" s="21">
+        <v>19</v>
+      </c>
+      <c r="D14" s="16">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="E14" s="21">
+        <v>13</v>
+      </c>
+      <c r="F14" s="16">
+        <v>15</v>
+      </c>
+      <c r="G14" s="21">
+        <f t="shared" si="3"/>
+        <v>28</v>
+      </c>
+      <c r="H14" s="22">
+        <f t="shared" si="2"/>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" s="11">
+        <f t="shared" ref="B15:G15" si="4">SUM(B5:B14)</f>
+        <v>271</v>
+      </c>
+      <c r="C15" s="11">
+        <f t="shared" si="4"/>
+        <v>260</v>
+      </c>
+      <c r="D15" s="11">
+        <f t="shared" si="4"/>
+        <v>531</v>
+      </c>
+      <c r="E15" s="11">
+        <f t="shared" si="4"/>
+        <v>190</v>
+      </c>
+      <c r="F15" s="11">
+        <f t="shared" si="4"/>
+        <v>185</v>
+      </c>
+      <c r="G15" s="11">
+        <f t="shared" si="4"/>
+        <v>375</v>
+      </c>
+      <c r="H15" s="25">
+        <f t="shared" si="2"/>
+        <v>70.621468926553675</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E16" s="23"/>
+      <c r="F16" s="24"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:H3"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Wrong Entry" error="Kindly Enter Value Less then Available Girls" sqref="F5:F14" xr:uid="{8AC3E3B0-7C58-4C54-8854-E2CA1502B08D}">
+      <formula1>C5&gt;=F5</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Wrong Entry" error="Kindly Enter Value Less then Available Boys" sqref="E5:E13" xr:uid="{99A256D8-BD22-4A76-8B5B-7FF135762345}">
+      <formula1>B5&gt;=E5</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A051A89-C5CF-4E31-B22F-18746ACB2762}">
+  <dimension ref="A1:H16"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5703125" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" customWidth="1"/>
+    <col min="7" max="7" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.35">
+      <c r="A1" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="28"/>
+    </row>
+    <row r="2" spans="1:8" ht="21" x14ac:dyDescent="0.35">
+      <c r="A2" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="31"/>
+    </row>
+    <row r="3" spans="1:8" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="32">
+        <v>45677</v>
+      </c>
+      <c r="B3" s="33"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
+      <c r="H3" s="34"/>
+    </row>
+    <row r="4" spans="1:8" ht="48" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="18">
+        <v>61</v>
+      </c>
+      <c r="C5" s="18">
+        <v>49</v>
+      </c>
+      <c r="D5" s="18">
+        <f>B5+C5</f>
+        <v>110</v>
+      </c>
+      <c r="E5" s="18">
+        <v>54</v>
+      </c>
+      <c r="F5" s="18">
+        <v>36</v>
+      </c>
+      <c r="G5" s="18">
+        <f t="shared" ref="G5" si="0">E5+F5</f>
+        <v>90</v>
+      </c>
+      <c r="H5" s="19">
+        <f>G5/D5*100</f>
+        <v>81.818181818181827</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="1">
+        <v>32</v>
+      </c>
+      <c r="C6" s="1">
+        <v>23</v>
+      </c>
+      <c r="D6" s="4">
+        <f t="shared" ref="D6:D14" si="1">B6+C6</f>
+        <v>55</v>
+      </c>
+      <c r="E6" s="4">
+        <v>29</v>
+      </c>
+      <c r="F6" s="4">
+        <v>19</v>
+      </c>
+      <c r="G6" s="1">
+        <f>E6+F6</f>
+        <v>48</v>
+      </c>
+      <c r="H6" s="15">
+        <f t="shared" ref="H6:H15" si="2">G6/D6*100</f>
+        <v>87.272727272727266</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="1">
+        <v>26</v>
+      </c>
+      <c r="C7" s="1">
+        <v>26</v>
+      </c>
+      <c r="D7" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="E7" s="4">
+        <v>20</v>
+      </c>
+      <c r="F7" s="4">
+        <v>21</v>
+      </c>
+      <c r="G7" s="1">
+        <f t="shared" ref="G7:G14" si="3">E7+F7</f>
+        <v>41</v>
+      </c>
+      <c r="H7" s="15">
+        <f t="shared" si="2"/>
+        <v>78.84615384615384</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="1">
+        <v>28</v>
+      </c>
+      <c r="C8" s="1">
+        <v>24</v>
+      </c>
+      <c r="D8" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="E8" s="4">
+        <v>24</v>
+      </c>
+      <c r="F8" s="4">
+        <v>21</v>
+      </c>
+      <c r="G8" s="1">
+        <f t="shared" si="3"/>
+        <v>45</v>
+      </c>
+      <c r="H8" s="15">
+        <f t="shared" si="2"/>
+        <v>86.538461538461547</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="1">
+        <v>22</v>
+      </c>
+      <c r="C9" s="1">
+        <v>30</v>
+      </c>
+      <c r="D9" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="E9" s="4">
+        <v>17</v>
+      </c>
+      <c r="F9" s="4">
+        <v>25</v>
+      </c>
+      <c r="G9" s="1">
+        <f t="shared" si="3"/>
+        <v>42</v>
+      </c>
+      <c r="H9" s="15">
+        <f t="shared" si="2"/>
+        <v>80.769230769230774</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="1">
+        <v>23</v>
+      </c>
+      <c r="C10" s="1">
+        <v>23</v>
+      </c>
+      <c r="D10" s="4">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="E10" s="4">
+        <v>19</v>
+      </c>
+      <c r="F10" s="4">
+        <v>18</v>
+      </c>
+      <c r="G10" s="1">
+        <f t="shared" si="3"/>
+        <v>37</v>
+      </c>
+      <c r="H10" s="15">
+        <f t="shared" si="2"/>
+        <v>80.434782608695656</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="1">
+        <v>17</v>
+      </c>
+      <c r="C11" s="1">
+        <v>25</v>
+      </c>
+      <c r="D11" s="4">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="E11" s="4">
+        <v>15</v>
+      </c>
+      <c r="F11" s="4">
+        <v>23</v>
+      </c>
+      <c r="G11" s="1">
+        <f t="shared" si="3"/>
+        <v>38</v>
+      </c>
+      <c r="H11" s="15">
+        <f t="shared" si="2"/>
+        <v>90.476190476190482</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="1">
+        <v>27</v>
+      </c>
+      <c r="C12" s="1">
+        <v>18</v>
+      </c>
+      <c r="D12" s="4">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="E12" s="4">
+        <v>24</v>
+      </c>
+      <c r="F12" s="4">
+        <v>12</v>
+      </c>
+      <c r="G12" s="1">
+        <f t="shared" si="3"/>
+        <v>36</v>
+      </c>
+      <c r="H12" s="15">
+        <f t="shared" si="2"/>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="1">
+        <v>19</v>
+      </c>
+      <c r="C13" s="1">
+        <v>23</v>
+      </c>
+      <c r="D13" s="4">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="E13" s="4">
+        <v>13</v>
+      </c>
+      <c r="F13" s="4">
+        <v>17</v>
+      </c>
+      <c r="G13" s="1">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+      <c r="H13" s="15">
+        <f t="shared" si="2"/>
+        <v>71.428571428571431</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="21">
+        <v>16</v>
+      </c>
+      <c r="C14" s="21">
+        <v>19</v>
+      </c>
+      <c r="D14" s="16">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="E14" s="21">
+        <v>13</v>
+      </c>
+      <c r="F14" s="16">
+        <v>12</v>
+      </c>
+      <c r="G14" s="21">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+      <c r="H14" s="22">
+        <f t="shared" si="2"/>
+        <v>71.428571428571431</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" s="11">
+        <f t="shared" ref="B15:G15" si="4">SUM(B5:B14)</f>
+        <v>271</v>
+      </c>
+      <c r="C15" s="11">
+        <f t="shared" si="4"/>
+        <v>260</v>
+      </c>
+      <c r="D15" s="11">
+        <f t="shared" si="4"/>
+        <v>531</v>
+      </c>
+      <c r="E15" s="11">
+        <f t="shared" si="4"/>
+        <v>228</v>
+      </c>
+      <c r="F15" s="11">
+        <f t="shared" si="4"/>
+        <v>204</v>
+      </c>
+      <c r="G15" s="11">
+        <f t="shared" si="4"/>
+        <v>432</v>
+      </c>
+      <c r="H15" s="25">
+        <f t="shared" si="2"/>
+        <v>81.355932203389841</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E16" s="23"/>
+      <c r="F16" s="24"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:H3"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Wrong Entry" error="Kindly Enter Value Less then Available Boys" sqref="E5:E13" xr:uid="{DB0E171C-EAC3-488E-9157-C504CB013FD0}">
+      <formula1>B5&gt;=E5</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Wrong Entry" error="Kindly Enter Value Less then Available Girls" sqref="F5:F14" xr:uid="{8FAC761B-992B-4432-8D3F-26C50059D06A}">
+      <formula1>C5&gt;=F5</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{332BB496-C281-4984-BD3F-567E649AB8E8}">
+  <dimension ref="A1:H16"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5703125" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" customWidth="1"/>
+    <col min="7" max="7" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.35">
+      <c r="A1" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="28"/>
+    </row>
+    <row r="2" spans="1:8" ht="21" x14ac:dyDescent="0.35">
+      <c r="A2" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="31"/>
+    </row>
+    <row r="3" spans="1:8" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="32">
+        <v>45678</v>
+      </c>
+      <c r="B3" s="33"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
+      <c r="H3" s="34"/>
+    </row>
+    <row r="4" spans="1:8" ht="48" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="18">
+        <v>61</v>
+      </c>
+      <c r="C5" s="18">
+        <v>49</v>
+      </c>
+      <c r="D5" s="18">
+        <f>B5+C5</f>
+        <v>110</v>
+      </c>
+      <c r="E5" s="18">
+        <v>55</v>
+      </c>
+      <c r="F5" s="18">
+        <v>37</v>
+      </c>
+      <c r="G5" s="18">
+        <f t="shared" ref="G5" si="0">E5+F5</f>
+        <v>92</v>
+      </c>
+      <c r="H5" s="19">
+        <f>G5/D5*100</f>
+        <v>83.636363636363626</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="1">
+        <v>32</v>
+      </c>
+      <c r="C6" s="1">
+        <v>23</v>
+      </c>
+      <c r="D6" s="4">
+        <f t="shared" ref="D6:D14" si="1">B6+C6</f>
+        <v>55</v>
+      </c>
+      <c r="E6" s="4">
+        <v>31</v>
+      </c>
+      <c r="F6" s="4">
+        <v>17</v>
+      </c>
+      <c r="G6" s="1">
+        <f>E6+F6</f>
+        <v>48</v>
+      </c>
+      <c r="H6" s="15">
+        <f t="shared" ref="H6:H15" si="2">G6/D6*100</f>
+        <v>87.272727272727266</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="1">
+        <v>26</v>
+      </c>
+      <c r="C7" s="1">
+        <v>26</v>
+      </c>
+      <c r="D7" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="E7" s="4">
+        <v>24</v>
+      </c>
+      <c r="F7" s="4">
+        <v>20</v>
+      </c>
+      <c r="G7" s="1">
+        <f t="shared" ref="G7:G14" si="3">E7+F7</f>
+        <v>44</v>
+      </c>
+      <c r="H7" s="15">
+        <f t="shared" si="2"/>
+        <v>84.615384615384613</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="1">
+        <v>28</v>
+      </c>
+      <c r="C8" s="1">
+        <v>24</v>
+      </c>
+      <c r="D8" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="E8" s="4">
+        <v>24</v>
+      </c>
+      <c r="F8" s="4">
+        <v>22</v>
+      </c>
+      <c r="G8" s="1">
+        <f t="shared" si="3"/>
+        <v>46</v>
+      </c>
+      <c r="H8" s="15">
+        <f t="shared" si="2"/>
+        <v>88.461538461538453</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="1">
+        <v>22</v>
+      </c>
+      <c r="C9" s="1">
+        <v>30</v>
+      </c>
+      <c r="D9" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="E9" s="4">
+        <v>17</v>
+      </c>
+      <c r="F9" s="4">
+        <v>22</v>
+      </c>
+      <c r="G9" s="1">
+        <f t="shared" si="3"/>
+        <v>39</v>
+      </c>
+      <c r="H9" s="15">
+        <f t="shared" si="2"/>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="1">
+        <v>23</v>
+      </c>
+      <c r="C10" s="1">
+        <v>23</v>
+      </c>
+      <c r="D10" s="4">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="E10" s="4">
+        <v>21</v>
+      </c>
+      <c r="F10" s="4">
+        <v>17</v>
+      </c>
+      <c r="G10" s="1">
+        <f t="shared" si="3"/>
+        <v>38</v>
+      </c>
+      <c r="H10" s="15">
+        <f t="shared" si="2"/>
+        <v>82.608695652173907</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="1">
+        <v>17</v>
+      </c>
+      <c r="C11" s="1">
+        <v>25</v>
+      </c>
+      <c r="D11" s="4">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="E11" s="4">
+        <v>15</v>
+      </c>
+      <c r="F11" s="4">
+        <v>22</v>
+      </c>
+      <c r="G11" s="1">
+        <f t="shared" si="3"/>
+        <v>37</v>
+      </c>
+      <c r="H11" s="15">
+        <f t="shared" si="2"/>
+        <v>88.095238095238088</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="1">
+        <v>27</v>
+      </c>
+      <c r="C12" s="1">
+        <v>18</v>
+      </c>
+      <c r="D12" s="4">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="E12" s="4">
+        <v>23</v>
+      </c>
+      <c r="F12" s="4">
+        <v>15</v>
+      </c>
+      <c r="G12" s="1">
+        <f t="shared" si="3"/>
+        <v>38</v>
+      </c>
+      <c r="H12" s="15">
+        <f t="shared" si="2"/>
+        <v>84.444444444444443</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="1">
+        <v>19</v>
+      </c>
+      <c r="C13" s="1">
+        <v>23</v>
+      </c>
+      <c r="D13" s="4">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="E13" s="4">
+        <v>15</v>
+      </c>
+      <c r="F13" s="4">
+        <v>15</v>
+      </c>
+      <c r="G13" s="1">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+      <c r="H13" s="15">
+        <f t="shared" si="2"/>
+        <v>71.428571428571431</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="21">
+        <v>16</v>
+      </c>
+      <c r="C14" s="21">
+        <v>19</v>
+      </c>
+      <c r="D14" s="16">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="E14" s="21">
+        <v>13</v>
+      </c>
+      <c r="F14" s="16">
+        <v>14</v>
+      </c>
+      <c r="G14" s="21">
+        <f t="shared" si="3"/>
+        <v>27</v>
+      </c>
+      <c r="H14" s="22">
+        <f t="shared" si="2"/>
+        <v>77.142857142857153</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" s="11">
+        <f t="shared" ref="B15:G15" si="4">SUM(B5:B14)</f>
+        <v>271</v>
+      </c>
+      <c r="C15" s="11">
+        <f t="shared" si="4"/>
+        <v>260</v>
+      </c>
+      <c r="D15" s="11">
+        <f t="shared" si="4"/>
+        <v>531</v>
+      </c>
+      <c r="E15" s="11">
+        <f t="shared" si="4"/>
+        <v>238</v>
+      </c>
+      <c r="F15" s="11">
+        <f t="shared" si="4"/>
+        <v>201</v>
+      </c>
+      <c r="G15" s="11">
+        <f t="shared" si="4"/>
+        <v>439</v>
+      </c>
+      <c r="H15" s="25">
+        <f t="shared" si="2"/>
+        <v>82.674199623352166</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E16" s="23"/>
+      <c r="F16" s="24"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:H3"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Wrong Entry" error="Kindly Enter Value Less then Available Girls" sqref="F5:F14" xr:uid="{7E496C8E-0EEB-4717-AD70-80F7BC185D53}">
+      <formula1>C5&gt;=F5</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Wrong Entry" error="Kindly Enter Value Less then Available Boys" sqref="E5:E13" xr:uid="{10E35FE1-520E-4F29-AC5F-56406469EE1B}">
+      <formula1>B5&gt;=E5</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC34C576-0B5E-43DA-BB22-C576A882224D}">
+  <dimension ref="A1:H16"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5703125" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" customWidth="1"/>
+    <col min="7" max="7" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.35">
+      <c r="A1" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="28"/>
+    </row>
+    <row r="2" spans="1:8" ht="21" x14ac:dyDescent="0.35">
+      <c r="A2" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="31"/>
+    </row>
+    <row r="3" spans="1:8" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="32">
+        <v>45679</v>
+      </c>
+      <c r="B3" s="33"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
+      <c r="H3" s="34"/>
+    </row>
+    <row r="4" spans="1:8" ht="48" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="18">
+        <v>61</v>
+      </c>
+      <c r="C5" s="18">
+        <v>49</v>
+      </c>
+      <c r="D5" s="18">
+        <f>B5+C5</f>
+        <v>110</v>
+      </c>
+      <c r="E5" s="18">
+        <v>52</v>
+      </c>
+      <c r="F5" s="18">
+        <v>43</v>
+      </c>
+      <c r="G5" s="18">
+        <f t="shared" ref="G5" si="0">E5+F5</f>
+        <v>95</v>
+      </c>
+      <c r="H5" s="19">
+        <f>G5/D5*100</f>
+        <v>86.36363636363636</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="1">
+        <v>32</v>
+      </c>
+      <c r="C6" s="1">
+        <v>23</v>
+      </c>
+      <c r="D6" s="4">
+        <f t="shared" ref="D6:D14" si="1">B6+C6</f>
+        <v>55</v>
+      </c>
+      <c r="E6" s="4">
+        <v>32</v>
+      </c>
+      <c r="F6" s="4">
+        <v>18</v>
+      </c>
+      <c r="G6" s="1">
+        <f>E6+F6</f>
+        <v>50</v>
+      </c>
+      <c r="H6" s="15">
+        <f t="shared" ref="H6:H15" si="2">G6/D6*100</f>
+        <v>90.909090909090907</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="1">
+        <v>26</v>
+      </c>
+      <c r="C7" s="1">
+        <v>26</v>
+      </c>
+      <c r="D7" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="E7" s="4">
+        <v>20</v>
+      </c>
+      <c r="F7" s="4">
+        <v>20</v>
+      </c>
+      <c r="G7" s="1">
+        <f t="shared" ref="G7:G14" si="3">E7+F7</f>
+        <v>40</v>
+      </c>
+      <c r="H7" s="15">
+        <f t="shared" si="2"/>
+        <v>76.923076923076934</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="1">
+        <v>28</v>
+      </c>
+      <c r="C8" s="1">
+        <v>24</v>
+      </c>
+      <c r="D8" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="E8" s="4">
+        <v>21</v>
+      </c>
+      <c r="F8" s="4">
+        <v>19</v>
+      </c>
+      <c r="G8" s="1">
+        <f t="shared" si="3"/>
+        <v>40</v>
+      </c>
+      <c r="H8" s="15">
+        <f t="shared" si="2"/>
+        <v>76.923076923076934</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="1">
+        <v>22</v>
+      </c>
+      <c r="C9" s="1">
+        <v>30</v>
+      </c>
+      <c r="D9" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="E9" s="4">
+        <v>15</v>
+      </c>
+      <c r="F9" s="4">
+        <v>22</v>
+      </c>
+      <c r="G9" s="1">
+        <f t="shared" si="3"/>
+        <v>37</v>
+      </c>
+      <c r="H9" s="15">
+        <f t="shared" si="2"/>
+        <v>71.15384615384616</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="1">
+        <v>23</v>
+      </c>
+      <c r="C10" s="1">
+        <v>23</v>
+      </c>
+      <c r="D10" s="4">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="E10" s="4">
+        <v>17</v>
+      </c>
+      <c r="F10" s="4">
+        <v>16</v>
+      </c>
+      <c r="G10" s="1">
+        <f t="shared" si="3"/>
+        <v>33</v>
+      </c>
+      <c r="H10" s="15">
+        <f t="shared" si="2"/>
+        <v>71.739130434782609</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="1">
+        <v>17</v>
+      </c>
+      <c r="C11" s="1">
+        <v>25</v>
+      </c>
+      <c r="D11" s="4">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="E11" s="4">
+        <v>15</v>
+      </c>
+      <c r="F11" s="4">
+        <v>21</v>
+      </c>
+      <c r="G11" s="1">
+        <f t="shared" si="3"/>
+        <v>36</v>
+      </c>
+      <c r="H11" s="15">
+        <f t="shared" si="2"/>
+        <v>85.714285714285708</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="1">
+        <v>27</v>
+      </c>
+      <c r="C12" s="1">
+        <v>18</v>
+      </c>
+      <c r="D12" s="4">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="E12" s="4">
+        <v>23</v>
+      </c>
+      <c r="F12" s="4">
+        <v>15</v>
+      </c>
+      <c r="G12" s="1">
+        <f t="shared" si="3"/>
+        <v>38</v>
+      </c>
+      <c r="H12" s="15">
+        <f t="shared" si="2"/>
+        <v>84.444444444444443</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="1">
+        <v>19</v>
+      </c>
+      <c r="C13" s="1">
+        <v>23</v>
+      </c>
+      <c r="D13" s="4">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="E13" s="4">
+        <v>14</v>
+      </c>
+      <c r="F13" s="4">
+        <v>21</v>
+      </c>
+      <c r="G13" s="1">
+        <f t="shared" si="3"/>
+        <v>35</v>
+      </c>
+      <c r="H13" s="15">
+        <f t="shared" si="2"/>
+        <v>83.333333333333343</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="21">
+        <v>16</v>
+      </c>
+      <c r="C14" s="21">
+        <v>19</v>
+      </c>
+      <c r="D14" s="16">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="E14" s="21">
+        <v>13</v>
+      </c>
+      <c r="F14" s="16">
+        <v>14</v>
+      </c>
+      <c r="G14" s="21">
+        <f t="shared" si="3"/>
+        <v>27</v>
+      </c>
+      <c r="H14" s="22">
+        <f t="shared" si="2"/>
+        <v>77.142857142857153</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" s="11">
+        <f t="shared" ref="B15:G15" si="4">SUM(B5:B14)</f>
+        <v>271</v>
+      </c>
+      <c r="C15" s="11">
+        <f t="shared" si="4"/>
+        <v>260</v>
+      </c>
+      <c r="D15" s="11">
+        <f t="shared" si="4"/>
+        <v>531</v>
+      </c>
+      <c r="E15" s="11">
+        <f t="shared" si="4"/>
+        <v>222</v>
+      </c>
+      <c r="F15" s="11">
+        <f t="shared" si="4"/>
+        <v>209</v>
+      </c>
+      <c r="G15" s="11">
+        <f t="shared" si="4"/>
+        <v>431</v>
+      </c>
+      <c r="H15" s="25">
+        <f t="shared" si="2"/>
+        <v>81.16760828625236</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E16" s="23"/>
+      <c r="F16" s="24"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:H3"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Wrong Entry" error="Kindly Enter Value Less then Available Boys" sqref="E5:E13" xr:uid="{501954EA-E377-4B4F-8EBB-D393D27D0487}">
+      <formula1>B5&gt;=E5</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Wrong Entry" error="Kindly Enter Value Less then Available Girls" sqref="F5:F14" xr:uid="{1076A0DF-0026-4ACD-85A5-70C8F3EC414E}">
+      <formula1>C5&gt;=F5</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1166,40 +5521,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="17"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="28"/>
     </row>
     <row r="2" spans="1:8" ht="21" x14ac:dyDescent="0.35">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="20"/>
-    </row>
-    <row r="3" spans="1:8" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" s="22"/>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="22"/>
-      <c r="F3" s="22"/>
-      <c r="G3" s="22"/>
-      <c r="H3" s="23"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="31"/>
+    </row>
+    <row r="3" spans="1:8" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="32">
+        <v>45659</v>
+      </c>
+      <c r="B3" s="33"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
+      <c r="H3" s="34"/>
     </row>
     <row r="4" spans="1:8" ht="48" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
@@ -1251,7 +5606,7 @@
         <f t="shared" ref="G5:G6" si="0">E5+F5</f>
         <v>19</v>
       </c>
-      <c r="H5" s="24">
+      <c r="H5" s="15">
         <f>G5/D5*100</f>
         <v>35.185185185185183</v>
       </c>
@@ -1280,7 +5635,7 @@
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="H6" s="24">
+      <c r="H6" s="15">
         <f t="shared" ref="H6:H15" si="1">G6/D6*100</f>
         <v>51.785714285714292</v>
       </c>
@@ -1296,7 +5651,7 @@
         <v>23</v>
       </c>
       <c r="D7" s="4">
-        <f t="shared" ref="D6:D7" si="2">B7+C7</f>
+        <f t="shared" ref="D7" si="2">B7+C7</f>
         <v>55</v>
       </c>
       <c r="E7" s="1">
@@ -1309,7 +5664,7 @@
         <f>E7+F7</f>
         <v>31</v>
       </c>
-      <c r="H7" s="24">
+      <c r="H7" s="15">
         <f t="shared" si="1"/>
         <v>56.36363636363636</v>
       </c>
@@ -1338,7 +5693,7 @@
         <f t="shared" ref="G8:G15" si="4">E8+F8</f>
         <v>25</v>
       </c>
-      <c r="H8" s="24">
+      <c r="H8" s="15">
         <f t="shared" si="1"/>
         <v>48.07692307692308</v>
       </c>
@@ -1367,7 +5722,7 @@
         <f t="shared" si="4"/>
         <v>29</v>
       </c>
-      <c r="H9" s="24">
+      <c r="H9" s="15">
         <f t="shared" si="1"/>
         <v>55.769230769230774</v>
       </c>
@@ -1396,7 +5751,7 @@
         <f t="shared" si="4"/>
         <v>17</v>
       </c>
-      <c r="H10" s="24">
+      <c r="H10" s="15">
         <f t="shared" si="1"/>
         <v>32.075471698113205</v>
       </c>
@@ -1425,7 +5780,7 @@
         <f t="shared" si="4"/>
         <v>16</v>
       </c>
-      <c r="H11" s="24">
+      <c r="H11" s="15">
         <f t="shared" si="1"/>
         <v>34.782608695652172</v>
       </c>
@@ -1454,7 +5809,7 @@
         <f t="shared" si="4"/>
         <v>12</v>
       </c>
-      <c r="H12" s="24">
+      <c r="H12" s="15">
         <f t="shared" si="1"/>
         <v>28.571428571428569</v>
       </c>
@@ -1483,7 +5838,7 @@
         <f t="shared" si="4"/>
         <v>23</v>
       </c>
-      <c r="H13" s="24">
+      <c r="H13" s="15">
         <f t="shared" si="1"/>
         <v>51.111111111111107</v>
       </c>
@@ -1512,7 +5867,7 @@
         <f t="shared" si="4"/>
         <v>18</v>
       </c>
-      <c r="H14" s="24">
+      <c r="H14" s="15">
         <f t="shared" si="1"/>
         <v>42.857142857142854</v>
       </c>
@@ -1541,7 +5896,7 @@
         <f t="shared" si="4"/>
         <v>18</v>
       </c>
-      <c r="H15" s="24">
+      <c r="H15" s="15">
         <f t="shared" si="1"/>
         <v>51.428571428571423</v>
       </c>
@@ -1568,6 +5923,388 @@
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A3:H3"/>
   </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{687A9552-ED84-4E5C-9EFC-73F68637F4A8}">
+  <dimension ref="A1:H16"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5703125" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" customWidth="1"/>
+    <col min="7" max="7" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.35">
+      <c r="A1" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="28"/>
+    </row>
+    <row r="2" spans="1:8" ht="21" x14ac:dyDescent="0.35">
+      <c r="A2" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="31"/>
+    </row>
+    <row r="3" spans="1:8" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="32">
+        <v>45680</v>
+      </c>
+      <c r="B3" s="33"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
+      <c r="H3" s="34"/>
+    </row>
+    <row r="4" spans="1:8" ht="48" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="18">
+        <v>61</v>
+      </c>
+      <c r="C5" s="18">
+        <v>49</v>
+      </c>
+      <c r="D5" s="18">
+        <f>B5+C5</f>
+        <v>110</v>
+      </c>
+      <c r="E5" s="18"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18">
+        <f t="shared" ref="G5" si="0">E5+F5</f>
+        <v>0</v>
+      </c>
+      <c r="H5" s="19">
+        <f>G5/D5*100</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="1">
+        <v>32</v>
+      </c>
+      <c r="C6" s="1">
+        <v>23</v>
+      </c>
+      <c r="D6" s="4">
+        <f t="shared" ref="D6:D14" si="1">B6+C6</f>
+        <v>55</v>
+      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="1">
+        <f>E6+F6</f>
+        <v>0</v>
+      </c>
+      <c r="H6" s="15">
+        <f t="shared" ref="H6:H15" si="2">G6/D6*100</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="1">
+        <v>26</v>
+      </c>
+      <c r="C7" s="1">
+        <v>26</v>
+      </c>
+      <c r="D7" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="1">
+        <f t="shared" ref="G7:G14" si="3">E7+F7</f>
+        <v>0</v>
+      </c>
+      <c r="H7" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="1">
+        <v>28</v>
+      </c>
+      <c r="C8" s="1">
+        <v>24</v>
+      </c>
+      <c r="D8" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H8" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="1">
+        <v>22</v>
+      </c>
+      <c r="C9" s="1">
+        <v>30</v>
+      </c>
+      <c r="D9" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H9" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="1">
+        <v>23</v>
+      </c>
+      <c r="C10" s="1">
+        <v>23</v>
+      </c>
+      <c r="D10" s="4">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H10" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="1">
+        <v>17</v>
+      </c>
+      <c r="C11" s="1">
+        <v>25</v>
+      </c>
+      <c r="D11" s="4">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H11" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="1">
+        <v>27</v>
+      </c>
+      <c r="C12" s="1">
+        <v>18</v>
+      </c>
+      <c r="D12" s="4">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H12" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="1">
+        <v>19</v>
+      </c>
+      <c r="C13" s="1">
+        <v>23</v>
+      </c>
+      <c r="D13" s="4">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H13" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="21">
+        <v>16</v>
+      </c>
+      <c r="C14" s="21">
+        <v>19</v>
+      </c>
+      <c r="D14" s="16">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="E14" s="21"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="21">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H14" s="22">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" s="11">
+        <f t="shared" ref="B15:G15" si="4">SUM(B5:B14)</f>
+        <v>271</v>
+      </c>
+      <c r="C15" s="11">
+        <f t="shared" si="4"/>
+        <v>260</v>
+      </c>
+      <c r="D15" s="11">
+        <f t="shared" si="4"/>
+        <v>531</v>
+      </c>
+      <c r="E15" s="11">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F15" s="11">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G15" s="11">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H15" s="25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E16" s="23"/>
+      <c r="F16" s="24"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:H3"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Wrong Entry" error="Kindly Enter Value Less then Available Girls" sqref="F5:F14" xr:uid="{5C3FE259-7004-4823-BDB5-7FCF503B66E7}">
+      <formula1>C5&gt;=F5</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Wrong Entry" error="Kindly Enter Value Less then Available Boys" sqref="E5:E13" xr:uid="{44B33FB1-88C8-4CEE-9374-1BD3AADD558E}">
+      <formula1>B5&gt;=E5</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1588,40 +6325,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="17"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="28"/>
     </row>
     <row r="2" spans="1:8" ht="21" x14ac:dyDescent="0.35">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="20"/>
-    </row>
-    <row r="3" spans="1:8" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" s="22"/>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="22"/>
-      <c r="F3" s="22"/>
-      <c r="G3" s="22"/>
-      <c r="H3" s="23"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="31"/>
+    </row>
+    <row r="3" spans="1:8" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="32">
+        <v>45660</v>
+      </c>
+      <c r="B3" s="33"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
+      <c r="H3" s="34"/>
     </row>
     <row r="4" spans="1:8" ht="48" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
@@ -1673,7 +6410,7 @@
         <f t="shared" ref="G5:G6" si="0">E5+F5</f>
         <v>23</v>
       </c>
-      <c r="H5" s="24">
+      <c r="H5" s="15">
         <f>G5/D5*100</f>
         <v>42.592592592592595</v>
       </c>
@@ -1702,7 +6439,7 @@
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="H6" s="24">
+      <c r="H6" s="15">
         <f t="shared" ref="H6:H15" si="2">G6/D6*100</f>
         <v>41.071428571428569</v>
       </c>
@@ -1722,18 +6459,18 @@
         <v>55</v>
       </c>
       <c r="E7" s="1">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F7" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G7" s="1">
         <f>E7+F7</f>
-        <v>26</v>
-      </c>
-      <c r="H7" s="24">
-        <f t="shared" si="2"/>
-        <v>47.272727272727273</v>
+        <v>28</v>
+      </c>
+      <c r="H7" s="15">
+        <f t="shared" si="2"/>
+        <v>50.909090909090907</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -1760,7 +6497,7 @@
         <f t="shared" ref="G8:G15" si="3">E8+F8</f>
         <v>26</v>
       </c>
-      <c r="H8" s="24">
+      <c r="H8" s="15">
         <f t="shared" si="2"/>
         <v>50</v>
       </c>
@@ -1789,7 +6526,7 @@
         <f t="shared" si="3"/>
         <v>25</v>
       </c>
-      <c r="H9" s="24">
+      <c r="H9" s="15">
         <f t="shared" si="2"/>
         <v>48.07692307692308</v>
       </c>
@@ -1818,7 +6555,7 @@
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
-      <c r="H10" s="24">
+      <c r="H10" s="15">
         <f t="shared" si="2"/>
         <v>28.846153846153843</v>
       </c>
@@ -1847,7 +6584,7 @@
         <f t="shared" si="3"/>
         <v>19</v>
       </c>
-      <c r="H11" s="24">
+      <c r="H11" s="15">
         <f t="shared" si="2"/>
         <v>41.304347826086953</v>
       </c>
@@ -1876,7 +6613,7 @@
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
-      <c r="H12" s="24">
+      <c r="H12" s="15">
         <f t="shared" si="2"/>
         <v>35.714285714285715</v>
       </c>
@@ -1905,7 +6642,7 @@
         <f t="shared" si="3"/>
         <v>21</v>
       </c>
-      <c r="H13" s="24">
+      <c r="H13" s="15">
         <f t="shared" si="2"/>
         <v>46.666666666666664</v>
       </c>
@@ -1934,7 +6671,7 @@
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
-      <c r="H14" s="24">
+      <c r="H14" s="15">
         <f t="shared" si="2"/>
         <v>47.619047619047613</v>
       </c>
@@ -1963,7 +6700,7 @@
         <f t="shared" si="3"/>
         <v>17</v>
       </c>
-      <c r="H15" s="24">
+      <c r="H15" s="15">
         <f t="shared" si="2"/>
         <v>48.571428571428569</v>
       </c>
@@ -2010,40 +6747,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="17"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="28"/>
     </row>
     <row r="2" spans="1:8" ht="21" x14ac:dyDescent="0.35">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="20"/>
-    </row>
-    <row r="3" spans="1:8" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3" s="22"/>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="22"/>
-      <c r="F3" s="22"/>
-      <c r="G3" s="22"/>
-      <c r="H3" s="23"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="31"/>
+    </row>
+    <row r="3" spans="1:8" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="32">
+        <v>45661</v>
+      </c>
+      <c r="B3" s="33"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
+      <c r="H3" s="34"/>
     </row>
     <row r="4" spans="1:8" ht="48" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
@@ -2085,15 +6822,19 @@
         <f>B5+C5</f>
         <v>54</v>
       </c>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
+      <c r="E5" s="4">
+        <v>10</v>
+      </c>
+      <c r="F5" s="4">
+        <v>11</v>
+      </c>
       <c r="G5" s="1">
         <f t="shared" ref="G5:G6" si="0">E5+F5</f>
-        <v>0</v>
-      </c>
-      <c r="H5" s="24">
+        <v>21</v>
+      </c>
+      <c r="H5" s="15">
         <f>G5/D5*100</f>
-        <v>0</v>
+        <v>38.888888888888893</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2110,15 +6851,19 @@
         <f t="shared" ref="D6:D15" si="1">B6+C6</f>
         <v>56</v>
       </c>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
+      <c r="E6" s="4">
+        <v>10</v>
+      </c>
+      <c r="F6" s="4">
+        <v>4</v>
+      </c>
       <c r="G6" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H6" s="24">
+        <v>14</v>
+      </c>
+      <c r="H6" s="15">
         <f t="shared" ref="H6:H15" si="2">G6/D6*100</f>
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2145,7 +6890,7 @@
         <f>E7+F7</f>
         <v>20</v>
       </c>
-      <c r="H7" s="24">
+      <c r="H7" s="15">
         <f t="shared" si="2"/>
         <v>36.363636363636367</v>
       </c>
@@ -2174,7 +6919,7 @@
         <f t="shared" ref="G8:G15" si="3">E8+F8</f>
         <v>26</v>
       </c>
-      <c r="H8" s="24">
+      <c r="H8" s="15">
         <f t="shared" si="2"/>
         <v>50</v>
       </c>
@@ -2203,7 +6948,7 @@
         <f t="shared" si="3"/>
         <v>16</v>
       </c>
-      <c r="H9" s="24">
+      <c r="H9" s="15">
         <f t="shared" si="2"/>
         <v>30.76923076923077</v>
       </c>
@@ -2232,7 +6977,7 @@
         <f t="shared" si="3"/>
         <v>18</v>
       </c>
-      <c r="H10" s="24">
+      <c r="H10" s="15">
         <f t="shared" si="2"/>
         <v>34.615384615384613</v>
       </c>
@@ -2261,7 +7006,7 @@
         <f t="shared" si="3"/>
         <v>19</v>
       </c>
-      <c r="H11" s="24">
+      <c r="H11" s="15">
         <f t="shared" si="2"/>
         <v>41.304347826086953</v>
       </c>
@@ -2290,7 +7035,7 @@
         <f t="shared" si="3"/>
         <v>17</v>
       </c>
-      <c r="H12" s="24">
+      <c r="H12" s="15">
         <f t="shared" si="2"/>
         <v>40.476190476190474</v>
       </c>
@@ -2319,7 +7064,7 @@
         <f t="shared" si="3"/>
         <v>22</v>
       </c>
-      <c r="H13" s="24">
+      <c r="H13" s="15">
         <f t="shared" si="2"/>
         <v>48.888888888888886</v>
       </c>
@@ -2348,7 +7093,7 @@
         <f t="shared" si="3"/>
         <v>18</v>
       </c>
-      <c r="H14" s="24">
+      <c r="H14" s="15">
         <f t="shared" si="2"/>
         <v>42.857142857142854</v>
       </c>
@@ -2377,7 +7122,7 @@
         <f t="shared" si="3"/>
         <v>16</v>
       </c>
-      <c r="H15" s="24">
+      <c r="H15" s="15">
         <f t="shared" si="2"/>
         <v>45.714285714285715</v>
       </c>
@@ -2424,40 +7169,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="17"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="28"/>
     </row>
     <row r="2" spans="1:8" ht="21" x14ac:dyDescent="0.35">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="20"/>
-    </row>
-    <row r="3" spans="1:8" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3" s="22"/>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="22"/>
-      <c r="F3" s="22"/>
-      <c r="G3" s="22"/>
-      <c r="H3" s="23"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="31"/>
+    </row>
+    <row r="3" spans="1:8" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="32">
+        <v>45663</v>
+      </c>
+      <c r="B3" s="33"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
+      <c r="H3" s="34"/>
     </row>
     <row r="4" spans="1:8" ht="48" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
@@ -2509,7 +7254,7 @@
         <f t="shared" ref="G5:G6" si="0">E5+F5</f>
         <v>31</v>
       </c>
-      <c r="H5" s="24">
+      <c r="H5" s="15">
         <f>G5/D5*100</f>
         <v>57.407407407407405</v>
       </c>
@@ -2538,7 +7283,7 @@
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="H6" s="24">
+      <c r="H6" s="15">
         <f t="shared" ref="H6:H15" si="2">G6/D6*100</f>
         <v>73.214285714285708</v>
       </c>
@@ -2567,7 +7312,7 @@
         <f>E7+F7</f>
         <v>40</v>
       </c>
-      <c r="H7" s="24">
+      <c r="H7" s="15">
         <f t="shared" si="2"/>
         <v>72.727272727272734</v>
       </c>
@@ -2596,7 +7341,7 @@
         <f t="shared" ref="G8:G15" si="3">E8+F8</f>
         <v>33</v>
       </c>
-      <c r="H8" s="24">
+      <c r="H8" s="15">
         <f t="shared" si="2"/>
         <v>63.46153846153846</v>
       </c>
@@ -2625,7 +7370,7 @@
         <f t="shared" si="3"/>
         <v>34</v>
       </c>
-      <c r="H9" s="24">
+      <c r="H9" s="15">
         <f t="shared" si="2"/>
         <v>65.384615384615387</v>
       </c>
@@ -2644,15 +7389,19 @@
         <f t="shared" si="1"/>
         <v>52</v>
       </c>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
+      <c r="E10" s="1">
+        <v>22</v>
+      </c>
+      <c r="F10" s="1">
+        <v>18</v>
+      </c>
       <c r="G10" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H10" s="24">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>40</v>
+      </c>
+      <c r="H10" s="15">
+        <f t="shared" si="2"/>
+        <v>76.923076923076934</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2669,15 +7418,19 @@
         <f t="shared" si="1"/>
         <v>46</v>
       </c>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
+      <c r="E11" s="1">
+        <v>20</v>
+      </c>
+      <c r="F11" s="1">
+        <v>19</v>
+      </c>
       <c r="G11" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H11" s="24">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>39</v>
+      </c>
+      <c r="H11" s="15">
+        <f t="shared" si="2"/>
+        <v>84.782608695652172</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2694,15 +7447,19 @@
         <f t="shared" si="1"/>
         <v>42</v>
       </c>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
+      <c r="E12" s="1">
+        <v>17</v>
+      </c>
+      <c r="F12" s="1">
+        <v>25</v>
+      </c>
       <c r="G12" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H12" s="24">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>42</v>
+      </c>
+      <c r="H12" s="15">
+        <f t="shared" si="2"/>
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2719,15 +7476,19 @@
         <f t="shared" si="1"/>
         <v>45</v>
       </c>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
+      <c r="E13" s="1">
+        <v>20</v>
+      </c>
+      <c r="F13" s="1">
+        <v>18</v>
+      </c>
       <c r="G13" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H13" s="24">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>38</v>
+      </c>
+      <c r="H13" s="15">
+        <f t="shared" si="2"/>
+        <v>84.444444444444443</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2744,15 +7505,19 @@
         <f t="shared" si="1"/>
         <v>42</v>
       </c>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
+      <c r="E14" s="1">
+        <v>10</v>
+      </c>
+      <c r="F14" s="1">
+        <v>13</v>
+      </c>
       <c r="G14" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H14" s="24">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>23</v>
+      </c>
+      <c r="H14" s="15">
+        <f t="shared" si="2"/>
+        <v>54.761904761904766</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2769,15 +7534,19 @@
         <f t="shared" si="1"/>
         <v>35</v>
       </c>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10"/>
+      <c r="E15" s="10">
+        <v>11</v>
+      </c>
+      <c r="F15" s="10">
+        <v>15</v>
+      </c>
       <c r="G15" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H15" s="24">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>26</v>
+      </c>
+      <c r="H15" s="15">
+        <f t="shared" si="2"/>
+        <v>74.285714285714292</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2804,4 +7573,1642 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81E7B287-C9E0-4469-9DE4-3F2FF0653019}">
+  <dimension ref="A1:H17"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5703125" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" customWidth="1"/>
+    <col min="7" max="7" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.35">
+      <c r="A1" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="28"/>
+    </row>
+    <row r="2" spans="1:8" ht="21" x14ac:dyDescent="0.35">
+      <c r="A2" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="31"/>
+    </row>
+    <row r="3" spans="1:8" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="32">
+        <v>45664</v>
+      </c>
+      <c r="B3" s="33"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
+      <c r="H3" s="34"/>
+    </row>
+    <row r="4" spans="1:8" ht="48" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="4">
+        <v>30</v>
+      </c>
+      <c r="C5" s="4">
+        <v>24</v>
+      </c>
+      <c r="D5" s="4">
+        <f>B5+C5</f>
+        <v>54</v>
+      </c>
+      <c r="E5" s="4">
+        <v>18</v>
+      </c>
+      <c r="F5" s="4">
+        <v>16</v>
+      </c>
+      <c r="G5" s="1">
+        <f t="shared" ref="G5:G6" si="0">E5+F5</f>
+        <v>34</v>
+      </c>
+      <c r="H5" s="15">
+        <f>G5/D5*100</f>
+        <v>62.962962962962962</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="4">
+        <v>31</v>
+      </c>
+      <c r="C6" s="4">
+        <v>25</v>
+      </c>
+      <c r="D6" s="4">
+        <f t="shared" ref="D6:D15" si="1">B6+C6</f>
+        <v>56</v>
+      </c>
+      <c r="E6" s="4">
+        <v>25</v>
+      </c>
+      <c r="F6" s="4">
+        <v>20</v>
+      </c>
+      <c r="G6" s="1">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="H6" s="15">
+        <f t="shared" ref="H6:H15" si="2">G6/D6*100</f>
+        <v>80.357142857142861</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="1">
+        <v>32</v>
+      </c>
+      <c r="C7" s="1">
+        <v>23</v>
+      </c>
+      <c r="D7" s="4">
+        <f t="shared" si="1"/>
+        <v>55</v>
+      </c>
+      <c r="E7" s="1">
+        <v>24</v>
+      </c>
+      <c r="F7" s="1">
+        <v>22</v>
+      </c>
+      <c r="G7" s="1">
+        <f>E7+F7</f>
+        <v>46</v>
+      </c>
+      <c r="H7" s="15">
+        <f t="shared" si="2"/>
+        <v>83.636363636363626</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="1">
+        <v>26</v>
+      </c>
+      <c r="C8" s="1">
+        <v>26</v>
+      </c>
+      <c r="D8" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="E8" s="1">
+        <v>19</v>
+      </c>
+      <c r="F8" s="1">
+        <v>20</v>
+      </c>
+      <c r="G8" s="1">
+        <f t="shared" ref="G8:G15" si="3">E8+F8</f>
+        <v>39</v>
+      </c>
+      <c r="H8" s="15">
+        <f t="shared" si="2"/>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="1">
+        <v>28</v>
+      </c>
+      <c r="C9" s="1">
+        <v>24</v>
+      </c>
+      <c r="D9" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="E9" s="1">
+        <v>23</v>
+      </c>
+      <c r="F9" s="1">
+        <v>20</v>
+      </c>
+      <c r="G9" s="1">
+        <f t="shared" si="3"/>
+        <v>43</v>
+      </c>
+      <c r="H9" s="15">
+        <f t="shared" si="2"/>
+        <v>82.692307692307693</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="1">
+        <v>22</v>
+      </c>
+      <c r="C10" s="1">
+        <v>30</v>
+      </c>
+      <c r="D10" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="E10" s="1">
+        <v>16</v>
+      </c>
+      <c r="F10" s="1">
+        <v>20</v>
+      </c>
+      <c r="G10" s="1">
+        <f t="shared" si="3"/>
+        <v>36</v>
+      </c>
+      <c r="H10" s="15">
+        <f t="shared" si="2"/>
+        <v>69.230769230769226</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="1">
+        <v>23</v>
+      </c>
+      <c r="C11" s="1">
+        <v>23</v>
+      </c>
+      <c r="D11" s="4">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="E11" s="1">
+        <v>15</v>
+      </c>
+      <c r="F11" s="1">
+        <v>16</v>
+      </c>
+      <c r="G11" s="1">
+        <f t="shared" si="3"/>
+        <v>31</v>
+      </c>
+      <c r="H11" s="15">
+        <f t="shared" si="2"/>
+        <v>67.391304347826093</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="1">
+        <v>17</v>
+      </c>
+      <c r="C12" s="1">
+        <v>25</v>
+      </c>
+      <c r="D12" s="4">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="E12" s="1">
+        <v>14</v>
+      </c>
+      <c r="F12" s="1">
+        <v>21</v>
+      </c>
+      <c r="G12" s="1">
+        <f t="shared" si="3"/>
+        <v>35</v>
+      </c>
+      <c r="H12" s="15">
+        <f t="shared" si="2"/>
+        <v>83.333333333333343</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="1">
+        <v>27</v>
+      </c>
+      <c r="C13" s="1">
+        <v>18</v>
+      </c>
+      <c r="D13" s="4">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="E13" s="1">
+        <v>18</v>
+      </c>
+      <c r="F13" s="1">
+        <v>14</v>
+      </c>
+      <c r="G13" s="1">
+        <f t="shared" si="3"/>
+        <v>32</v>
+      </c>
+      <c r="H13" s="15">
+        <f t="shared" si="2"/>
+        <v>71.111111111111114</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="1">
+        <v>19</v>
+      </c>
+      <c r="C14" s="1">
+        <v>23</v>
+      </c>
+      <c r="D14" s="4">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="E14" s="1">
+        <v>10</v>
+      </c>
+      <c r="F14" s="1">
+        <v>13</v>
+      </c>
+      <c r="G14" s="1">
+        <f t="shared" si="3"/>
+        <v>23</v>
+      </c>
+      <c r="H14" s="15">
+        <f t="shared" si="2"/>
+        <v>54.761904761904766</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="10">
+        <v>16</v>
+      </c>
+      <c r="C15" s="10">
+        <v>19</v>
+      </c>
+      <c r="D15" s="4">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="E15" s="10">
+        <v>11</v>
+      </c>
+      <c r="F15" s="10">
+        <v>15</v>
+      </c>
+      <c r="G15" s="1">
+        <f t="shared" si="3"/>
+        <v>26</v>
+      </c>
+      <c r="H15" s="15">
+        <f t="shared" si="2"/>
+        <v>74.285714285714292</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="12"/>
+    </row>
+    <row r="17" spans="5:6" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E17" s="13"/>
+      <c r="F17" s="12"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:H3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{077D56D8-62E1-4356-891E-D5AE7846088B}">
+  <dimension ref="A1:H17"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5703125" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" customWidth="1"/>
+    <col min="7" max="7" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.35">
+      <c r="A1" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="28"/>
+    </row>
+    <row r="2" spans="1:8" ht="21" x14ac:dyDescent="0.35">
+      <c r="A2" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="31"/>
+    </row>
+    <row r="3" spans="1:8" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="32">
+        <v>45665</v>
+      </c>
+      <c r="B3" s="33"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
+      <c r="H3" s="34"/>
+    </row>
+    <row r="4" spans="1:8" ht="48" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="4">
+        <v>30</v>
+      </c>
+      <c r="C5" s="4">
+        <v>24</v>
+      </c>
+      <c r="D5" s="4">
+        <f>B5+C5</f>
+        <v>54</v>
+      </c>
+      <c r="E5" s="4">
+        <v>24</v>
+      </c>
+      <c r="F5" s="4">
+        <v>17</v>
+      </c>
+      <c r="G5" s="1">
+        <f t="shared" ref="G5:G6" si="0">E5+F5</f>
+        <v>41</v>
+      </c>
+      <c r="H5" s="15">
+        <f>G5/D5*100</f>
+        <v>75.925925925925924</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="4">
+        <v>31</v>
+      </c>
+      <c r="C6" s="4">
+        <v>25</v>
+      </c>
+      <c r="D6" s="4">
+        <f t="shared" ref="D6:D15" si="1">B6+C6</f>
+        <v>56</v>
+      </c>
+      <c r="E6" s="4">
+        <v>27</v>
+      </c>
+      <c r="F6" s="4">
+        <v>20</v>
+      </c>
+      <c r="G6" s="1">
+        <f t="shared" si="0"/>
+        <v>47</v>
+      </c>
+      <c r="H6" s="15">
+        <f t="shared" ref="H6:H15" si="2">G6/D6*100</f>
+        <v>83.928571428571431</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="1">
+        <v>32</v>
+      </c>
+      <c r="C7" s="1">
+        <v>23</v>
+      </c>
+      <c r="D7" s="4">
+        <f t="shared" si="1"/>
+        <v>55</v>
+      </c>
+      <c r="E7" s="1">
+        <v>24</v>
+      </c>
+      <c r="F7" s="1">
+        <v>21</v>
+      </c>
+      <c r="G7" s="1">
+        <f>E7+F7</f>
+        <v>45</v>
+      </c>
+      <c r="H7" s="15">
+        <f t="shared" si="2"/>
+        <v>81.818181818181827</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="1">
+        <v>26</v>
+      </c>
+      <c r="C8" s="1">
+        <v>26</v>
+      </c>
+      <c r="D8" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="E8" s="1">
+        <v>20</v>
+      </c>
+      <c r="F8" s="1">
+        <v>20</v>
+      </c>
+      <c r="G8" s="1">
+        <f t="shared" ref="G8:G15" si="3">E8+F8</f>
+        <v>40</v>
+      </c>
+      <c r="H8" s="15">
+        <f t="shared" si="2"/>
+        <v>76.923076923076934</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="1">
+        <v>28</v>
+      </c>
+      <c r="C9" s="1">
+        <v>24</v>
+      </c>
+      <c r="D9" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="E9" s="1">
+        <v>22</v>
+      </c>
+      <c r="F9" s="1">
+        <v>22</v>
+      </c>
+      <c r="G9" s="1">
+        <f t="shared" si="3"/>
+        <v>44</v>
+      </c>
+      <c r="H9" s="15">
+        <f t="shared" si="2"/>
+        <v>84.615384615384613</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="1">
+        <v>22</v>
+      </c>
+      <c r="C10" s="1">
+        <v>30</v>
+      </c>
+      <c r="D10" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="E10" s="1">
+        <v>17</v>
+      </c>
+      <c r="F10" s="1">
+        <v>24</v>
+      </c>
+      <c r="G10" s="1">
+        <f t="shared" si="3"/>
+        <v>41</v>
+      </c>
+      <c r="H10" s="15">
+        <f t="shared" si="2"/>
+        <v>78.84615384615384</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="1">
+        <v>23</v>
+      </c>
+      <c r="C11" s="1">
+        <v>23</v>
+      </c>
+      <c r="D11" s="4">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="E11" s="1">
+        <v>17</v>
+      </c>
+      <c r="F11" s="1">
+        <v>16</v>
+      </c>
+      <c r="G11" s="1">
+        <f t="shared" si="3"/>
+        <v>33</v>
+      </c>
+      <c r="H11" s="15">
+        <f t="shared" si="2"/>
+        <v>71.739130434782609</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="1">
+        <v>17</v>
+      </c>
+      <c r="C12" s="1">
+        <v>25</v>
+      </c>
+      <c r="D12" s="4">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="E12" s="1">
+        <v>15</v>
+      </c>
+      <c r="F12" s="1">
+        <v>23</v>
+      </c>
+      <c r="G12" s="1">
+        <f t="shared" si="3"/>
+        <v>38</v>
+      </c>
+      <c r="H12" s="15">
+        <f t="shared" si="2"/>
+        <v>90.476190476190482</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="1">
+        <v>27</v>
+      </c>
+      <c r="C13" s="1">
+        <v>18</v>
+      </c>
+      <c r="D13" s="4">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="E13" s="1">
+        <v>18</v>
+      </c>
+      <c r="F13" s="1">
+        <v>16</v>
+      </c>
+      <c r="G13" s="1">
+        <f t="shared" si="3"/>
+        <v>34</v>
+      </c>
+      <c r="H13" s="15">
+        <f t="shared" si="2"/>
+        <v>75.555555555555557</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="1">
+        <v>19</v>
+      </c>
+      <c r="C14" s="1">
+        <v>23</v>
+      </c>
+      <c r="D14" s="4">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="E14" s="1">
+        <v>13</v>
+      </c>
+      <c r="F14" s="1">
+        <v>17</v>
+      </c>
+      <c r="G14" s="1">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+      <c r="H14" s="15">
+        <f t="shared" si="2"/>
+        <v>71.428571428571431</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="10">
+        <v>16</v>
+      </c>
+      <c r="C15" s="10">
+        <v>19</v>
+      </c>
+      <c r="D15" s="4">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="E15" s="10">
+        <v>11</v>
+      </c>
+      <c r="F15" s="10">
+        <v>12</v>
+      </c>
+      <c r="G15" s="1">
+        <f t="shared" si="3"/>
+        <v>23</v>
+      </c>
+      <c r="H15" s="15">
+        <f t="shared" si="2"/>
+        <v>65.714285714285708</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="12"/>
+    </row>
+    <row r="17" spans="5:6" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E17" s="13"/>
+      <c r="F17" s="12"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:H3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6A74744-380C-41E1-B4E7-06F9E909A80F}">
+  <dimension ref="A1:H16"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5703125" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" customWidth="1"/>
+    <col min="7" max="7" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.35">
+      <c r="A1" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="28"/>
+    </row>
+    <row r="2" spans="1:8" ht="21" x14ac:dyDescent="0.35">
+      <c r="A2" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="31"/>
+    </row>
+    <row r="3" spans="1:8" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="32">
+        <v>45666</v>
+      </c>
+      <c r="B3" s="33"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
+      <c r="H3" s="34"/>
+    </row>
+    <row r="4" spans="1:8" ht="48" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="4">
+        <v>61</v>
+      </c>
+      <c r="C5" s="4">
+        <v>49</v>
+      </c>
+      <c r="D5" s="4">
+        <f>B5+C5</f>
+        <v>110</v>
+      </c>
+      <c r="E5" s="4">
+        <v>48</v>
+      </c>
+      <c r="F5" s="4">
+        <v>39</v>
+      </c>
+      <c r="G5" s="1">
+        <f t="shared" ref="G5" si="0">E5+F5</f>
+        <v>87</v>
+      </c>
+      <c r="H5" s="15">
+        <f>G5/D5*100</f>
+        <v>79.090909090909093</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="1">
+        <v>32</v>
+      </c>
+      <c r="C6" s="1">
+        <v>23</v>
+      </c>
+      <c r="D6" s="4">
+        <f t="shared" ref="D6:D14" si="1">B6+C6</f>
+        <v>55</v>
+      </c>
+      <c r="E6" s="1">
+        <v>25</v>
+      </c>
+      <c r="F6" s="1">
+        <v>20</v>
+      </c>
+      <c r="G6" s="1">
+        <f>E6+F6</f>
+        <v>45</v>
+      </c>
+      <c r="H6" s="15">
+        <f t="shared" ref="H6:H14" si="2">G6/D6*100</f>
+        <v>81.818181818181827</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="1">
+        <v>26</v>
+      </c>
+      <c r="C7" s="1">
+        <v>26</v>
+      </c>
+      <c r="D7" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="E7" s="1">
+        <v>23</v>
+      </c>
+      <c r="F7" s="1">
+        <v>23</v>
+      </c>
+      <c r="G7" s="1">
+        <f t="shared" ref="G7:G14" si="3">E7+F7</f>
+        <v>46</v>
+      </c>
+      <c r="H7" s="15">
+        <f t="shared" si="2"/>
+        <v>88.461538461538453</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="1">
+        <v>28</v>
+      </c>
+      <c r="C8" s="1">
+        <v>24</v>
+      </c>
+      <c r="D8" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="E8" s="1">
+        <v>22</v>
+      </c>
+      <c r="F8" s="1">
+        <v>22</v>
+      </c>
+      <c r="G8" s="1">
+        <f t="shared" si="3"/>
+        <v>44</v>
+      </c>
+      <c r="H8" s="15">
+        <f t="shared" si="2"/>
+        <v>84.615384615384613</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="1">
+        <v>22</v>
+      </c>
+      <c r="C9" s="1">
+        <v>30</v>
+      </c>
+      <c r="D9" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="E9" s="1">
+        <v>17</v>
+      </c>
+      <c r="F9" s="1">
+        <v>24</v>
+      </c>
+      <c r="G9" s="1">
+        <f t="shared" si="3"/>
+        <v>41</v>
+      </c>
+      <c r="H9" s="15">
+        <f t="shared" si="2"/>
+        <v>78.84615384615384</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="1">
+        <v>23</v>
+      </c>
+      <c r="C10" s="1">
+        <v>23</v>
+      </c>
+      <c r="D10" s="4">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="E10" s="1">
+        <v>19</v>
+      </c>
+      <c r="F10" s="1">
+        <v>15</v>
+      </c>
+      <c r="G10" s="1">
+        <f t="shared" si="3"/>
+        <v>34</v>
+      </c>
+      <c r="H10" s="15">
+        <f t="shared" si="2"/>
+        <v>73.91304347826086</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="1">
+        <v>17</v>
+      </c>
+      <c r="C11" s="1">
+        <v>25</v>
+      </c>
+      <c r="D11" s="4">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="E11" s="1">
+        <v>17</v>
+      </c>
+      <c r="F11" s="1">
+        <v>24</v>
+      </c>
+      <c r="G11" s="1">
+        <f t="shared" si="3"/>
+        <v>41</v>
+      </c>
+      <c r="H11" s="15">
+        <f t="shared" si="2"/>
+        <v>97.61904761904762</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="1">
+        <v>27</v>
+      </c>
+      <c r="C12" s="1">
+        <v>18</v>
+      </c>
+      <c r="D12" s="4">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="E12" s="1">
+        <v>23</v>
+      </c>
+      <c r="F12" s="1">
+        <v>17</v>
+      </c>
+      <c r="G12" s="1">
+        <f t="shared" si="3"/>
+        <v>40</v>
+      </c>
+      <c r="H12" s="15">
+        <f t="shared" si="2"/>
+        <v>88.888888888888886</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="1">
+        <v>19</v>
+      </c>
+      <c r="C13" s="1">
+        <v>23</v>
+      </c>
+      <c r="D13" s="4">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="E13" s="1">
+        <v>13</v>
+      </c>
+      <c r="F13" s="1">
+        <v>18</v>
+      </c>
+      <c r="G13" s="1">
+        <f t="shared" si="3"/>
+        <v>31</v>
+      </c>
+      <c r="H13" s="15">
+        <f t="shared" si="2"/>
+        <v>73.80952380952381</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="10">
+        <v>16</v>
+      </c>
+      <c r="C14" s="10">
+        <v>19</v>
+      </c>
+      <c r="D14" s="4">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="E14" s="10">
+        <v>13</v>
+      </c>
+      <c r="F14" s="10">
+        <v>14</v>
+      </c>
+      <c r="G14" s="1">
+        <f t="shared" si="3"/>
+        <v>27</v>
+      </c>
+      <c r="H14" s="15">
+        <f t="shared" si="2"/>
+        <v>77.142857142857153</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="12"/>
+    </row>
+    <row r="16" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E16" s="13"/>
+      <c r="F16" s="12"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:H3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2981787-08BF-4906-B428-E34906478566}">
+  <dimension ref="A1:H16"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5703125" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" customWidth="1"/>
+    <col min="7" max="7" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.35">
+      <c r="A1" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="28"/>
+    </row>
+    <row r="2" spans="1:8" ht="21" x14ac:dyDescent="0.35">
+      <c r="A2" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="31"/>
+    </row>
+    <row r="3" spans="1:8" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="32">
+        <v>45667</v>
+      </c>
+      <c r="B3" s="33"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
+      <c r="H3" s="34"/>
+    </row>
+    <row r="4" spans="1:8" ht="48" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="4">
+        <v>61</v>
+      </c>
+      <c r="C5" s="4">
+        <v>49</v>
+      </c>
+      <c r="D5" s="4">
+        <f>B5+C5</f>
+        <v>110</v>
+      </c>
+      <c r="E5" s="4">
+        <v>49</v>
+      </c>
+      <c r="F5" s="4">
+        <v>37</v>
+      </c>
+      <c r="G5" s="1">
+        <f t="shared" ref="G5" si="0">E5+F5</f>
+        <v>86</v>
+      </c>
+      <c r="H5" s="15">
+        <f>G5/D5*100</f>
+        <v>78.181818181818187</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="1">
+        <v>32</v>
+      </c>
+      <c r="C6" s="1">
+        <v>23</v>
+      </c>
+      <c r="D6" s="4">
+        <f t="shared" ref="D6:D14" si="1">B6+C6</f>
+        <v>55</v>
+      </c>
+      <c r="E6" s="4">
+        <v>29</v>
+      </c>
+      <c r="F6" s="4">
+        <v>20</v>
+      </c>
+      <c r="G6" s="1">
+        <f>E6+F6</f>
+        <v>49</v>
+      </c>
+      <c r="H6" s="15">
+        <f t="shared" ref="H6:H14" si="2">G6/D6*100</f>
+        <v>89.090909090909093</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="1">
+        <v>26</v>
+      </c>
+      <c r="C7" s="1">
+        <v>26</v>
+      </c>
+      <c r="D7" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="E7" s="4">
+        <v>20</v>
+      </c>
+      <c r="F7" s="4">
+        <v>19</v>
+      </c>
+      <c r="G7" s="1">
+        <f t="shared" ref="G7:G14" si="3">E7+F7</f>
+        <v>39</v>
+      </c>
+      <c r="H7" s="15">
+        <f t="shared" si="2"/>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="1">
+        <v>28</v>
+      </c>
+      <c r="C8" s="1">
+        <v>24</v>
+      </c>
+      <c r="D8" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="E8" s="4">
+        <v>22</v>
+      </c>
+      <c r="F8" s="4">
+        <v>18</v>
+      </c>
+      <c r="G8" s="1">
+        <f t="shared" si="3"/>
+        <v>40</v>
+      </c>
+      <c r="H8" s="15">
+        <f t="shared" si="2"/>
+        <v>76.923076923076934</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="1">
+        <v>22</v>
+      </c>
+      <c r="C9" s="1">
+        <v>30</v>
+      </c>
+      <c r="D9" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="E9" s="4">
+        <v>18</v>
+      </c>
+      <c r="F9" s="4">
+        <v>25</v>
+      </c>
+      <c r="G9" s="1">
+        <f t="shared" si="3"/>
+        <v>43</v>
+      </c>
+      <c r="H9" s="15">
+        <f t="shared" si="2"/>
+        <v>82.692307692307693</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="1">
+        <v>23</v>
+      </c>
+      <c r="C10" s="1">
+        <v>23</v>
+      </c>
+      <c r="D10" s="4">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="E10" s="4">
+        <v>19</v>
+      </c>
+      <c r="F10" s="4">
+        <v>13</v>
+      </c>
+      <c r="G10" s="1">
+        <f t="shared" si="3"/>
+        <v>32</v>
+      </c>
+      <c r="H10" s="15">
+        <f t="shared" si="2"/>
+        <v>69.565217391304344</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="1">
+        <v>17</v>
+      </c>
+      <c r="C11" s="1">
+        <v>25</v>
+      </c>
+      <c r="D11" s="4">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="E11" s="4">
+        <v>16</v>
+      </c>
+      <c r="F11" s="4">
+        <v>24</v>
+      </c>
+      <c r="G11" s="1">
+        <f t="shared" si="3"/>
+        <v>40</v>
+      </c>
+      <c r="H11" s="15">
+        <f t="shared" si="2"/>
+        <v>95.238095238095227</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="1">
+        <v>27</v>
+      </c>
+      <c r="C12" s="1">
+        <v>18</v>
+      </c>
+      <c r="D12" s="4">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="E12" s="4">
+        <v>22</v>
+      </c>
+      <c r="F12" s="4">
+        <v>16</v>
+      </c>
+      <c r="G12" s="1">
+        <f t="shared" si="3"/>
+        <v>38</v>
+      </c>
+      <c r="H12" s="15">
+        <f t="shared" si="2"/>
+        <v>84.444444444444443</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="1">
+        <v>19</v>
+      </c>
+      <c r="C13" s="1">
+        <v>23</v>
+      </c>
+      <c r="D13" s="4">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="E13" s="4">
+        <v>11</v>
+      </c>
+      <c r="F13" s="4">
+        <v>19</v>
+      </c>
+      <c r="G13" s="1">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+      <c r="H13" s="15">
+        <f t="shared" si="2"/>
+        <v>71.428571428571431</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="10">
+        <v>16</v>
+      </c>
+      <c r="C14" s="10">
+        <v>19</v>
+      </c>
+      <c r="D14" s="4">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="E14" s="10">
+        <v>12</v>
+      </c>
+      <c r="F14" s="4">
+        <v>12</v>
+      </c>
+      <c r="G14" s="1">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+      <c r="H14" s="15">
+        <f t="shared" si="2"/>
+        <v>68.571428571428569</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="12"/>
+    </row>
+    <row r="16" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E16" s="13"/>
+      <c r="F16" s="12"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:H3"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Wrong Entry" error="Kindly Enter Value Less then Available Boys" sqref="E5:E13" xr:uid="{0AB10B49-8139-4815-9B7F-6640BD3A34C9}">
+      <formula1>B5&gt;=E5</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Wrong Entry" error="Kindly Enter Value Less then Available Girls" sqref="F5:F14" xr:uid="{1EC647D2-6BD9-4328-B540-9B521665E48B}">
+      <formula1>C5&gt;=F5</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Sindhi Muslim/People Diary/January-2025.xlsx
+++ b/Sindhi Muslim/People Diary/January-2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\People Diary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1811AD4C-918E-49DB-BF86-72747619CC1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B5B1975-A462-4127-A060-B00E8933A340}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="14" activeTab="19" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="17" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01-01-2025" sheetId="1" r:id="rId1"/>
@@ -33,6 +33,9 @@
     <sheet name="21-01-2025" sheetId="18" r:id="rId18"/>
     <sheet name="22-01-2025" sheetId="19" r:id="rId19"/>
     <sheet name="23-01-2025" sheetId="20" r:id="rId20"/>
+    <sheet name="24-01-2025" sheetId="21" r:id="rId21"/>
+    <sheet name="25-01-2025" sheetId="22" r:id="rId22"/>
+    <sheet name="27-01-2025" sheetId="23" r:id="rId23"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -53,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="21">
   <si>
     <t>CLASS WISE ENROLLED SUMMARY</t>
   </si>
@@ -6018,15 +6021,19 @@
         <f>B5+C5</f>
         <v>110</v>
       </c>
-      <c r="E5" s="18"/>
-      <c r="F5" s="18"/>
+      <c r="E5" s="18">
+        <v>48</v>
+      </c>
+      <c r="F5" s="18">
+        <v>37</v>
+      </c>
       <c r="G5" s="18">
         <f t="shared" ref="G5" si="0">E5+F5</f>
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="H5" s="19">
         <f>G5/D5*100</f>
-        <v>0</v>
+        <v>77.272727272727266</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -6043,15 +6050,19 @@
         <f t="shared" ref="D6:D14" si="1">B6+C6</f>
         <v>55</v>
       </c>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
+      <c r="E6" s="4">
+        <v>27</v>
+      </c>
+      <c r="F6" s="4">
+        <v>20</v>
+      </c>
       <c r="G6" s="1">
         <f>E6+F6</f>
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="H6" s="15">
         <f t="shared" ref="H6:H15" si="2">G6/D6*100</f>
-        <v>0</v>
+        <v>85.454545454545453</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -6068,15 +6079,19 @@
         <f t="shared" si="1"/>
         <v>52</v>
       </c>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
+      <c r="E7" s="4">
+        <v>21</v>
+      </c>
+      <c r="F7" s="4">
+        <v>20</v>
+      </c>
       <c r="G7" s="1">
         <f t="shared" ref="G7:G14" si="3">E7+F7</f>
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="H7" s="15">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>78.84615384615384</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -6093,15 +6108,19 @@
         <f t="shared" si="1"/>
         <v>52</v>
       </c>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
+      <c r="E8" s="4">
+        <v>20</v>
+      </c>
+      <c r="F8" s="4">
+        <v>20</v>
+      </c>
       <c r="G8" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H8" s="15">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>76.923076923076934</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -6118,15 +6137,19 @@
         <f t="shared" si="1"/>
         <v>52</v>
       </c>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
+      <c r="E9" s="4">
+        <v>16</v>
+      </c>
+      <c r="F9" s="4">
+        <v>20</v>
+      </c>
       <c r="G9" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H9" s="15">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>69.230769230769226</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -6143,15 +6166,19 @@
         <f t="shared" si="1"/>
         <v>46</v>
       </c>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
+      <c r="E10" s="4">
+        <v>20</v>
+      </c>
+      <c r="F10" s="4">
+        <v>15</v>
+      </c>
       <c r="G10" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H10" s="15">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>76.08695652173914</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -6168,15 +6195,19 @@
         <f t="shared" si="1"/>
         <v>42</v>
       </c>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
+      <c r="E11" s="4">
+        <v>14</v>
+      </c>
+      <c r="F11" s="4">
+        <v>18</v>
+      </c>
       <c r="G11" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="H11" s="15">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>76.19047619047619</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -6193,15 +6224,19 @@
         <f t="shared" si="1"/>
         <v>45</v>
       </c>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
+      <c r="E12" s="4">
+        <v>20</v>
+      </c>
+      <c r="F12" s="4">
+        <v>16</v>
+      </c>
       <c r="G12" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H12" s="15">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -6218,15 +6253,19 @@
         <f t="shared" si="1"/>
         <v>42</v>
       </c>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
+      <c r="E13" s="4">
+        <v>13</v>
+      </c>
+      <c r="F13" s="4">
+        <v>21</v>
+      </c>
       <c r="G13" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="H13" s="15">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>80.952380952380949</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -6243,15 +6282,19 @@
         <f t="shared" si="1"/>
         <v>35</v>
       </c>
-      <c r="E14" s="21"/>
-      <c r="F14" s="16"/>
+      <c r="E14" s="21">
+        <v>12</v>
+      </c>
+      <c r="F14" s="16">
+        <v>12</v>
+      </c>
       <c r="G14" s="21">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="H14" s="22">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>68.571428571428569</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -6272,19 +6315,19 @@
       </c>
       <c r="E15" s="11">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>211</v>
       </c>
       <c r="F15" s="11">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>199</v>
       </c>
       <c r="G15" s="11">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>410</v>
       </c>
       <c r="H15" s="25">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>77.212806026365342</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -6303,6 +6346,1232 @@
     </dataValidation>
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Wrong Entry" error="Kindly Enter Value Less then Available Boys" sqref="E5:E13" xr:uid="{44B33FB1-88C8-4CEE-9374-1BD3AADD558E}">
       <formula1>B5&gt;=E5</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94C5932F-D0EF-4351-A903-D03E0351189A}">
+  <dimension ref="A1:H16"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5703125" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" customWidth="1"/>
+    <col min="7" max="7" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.35">
+      <c r="A1" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="28"/>
+    </row>
+    <row r="2" spans="1:8" ht="21" x14ac:dyDescent="0.35">
+      <c r="A2" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="31"/>
+    </row>
+    <row r="3" spans="1:8" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="32">
+        <v>45680</v>
+      </c>
+      <c r="B3" s="33"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
+      <c r="H3" s="34"/>
+    </row>
+    <row r="4" spans="1:8" ht="48" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="18">
+        <v>61</v>
+      </c>
+      <c r="C5" s="18">
+        <v>49</v>
+      </c>
+      <c r="D5" s="18">
+        <f>B5+C5</f>
+        <v>110</v>
+      </c>
+      <c r="E5" s="18">
+        <v>55</v>
+      </c>
+      <c r="F5" s="18">
+        <v>34</v>
+      </c>
+      <c r="G5" s="18">
+        <f t="shared" ref="G5" si="0">E5+F5</f>
+        <v>89</v>
+      </c>
+      <c r="H5" s="19">
+        <f>G5/D5*100</f>
+        <v>80.909090909090907</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="1">
+        <v>32</v>
+      </c>
+      <c r="C6" s="1">
+        <v>23</v>
+      </c>
+      <c r="D6" s="4">
+        <f t="shared" ref="D6:D14" si="1">B6+C6</f>
+        <v>55</v>
+      </c>
+      <c r="E6" s="4">
+        <v>29</v>
+      </c>
+      <c r="F6" s="4">
+        <v>19</v>
+      </c>
+      <c r="G6" s="1">
+        <f>E6+F6</f>
+        <v>48</v>
+      </c>
+      <c r="H6" s="15">
+        <f t="shared" ref="H6:H15" si="2">G6/D6*100</f>
+        <v>87.272727272727266</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="1">
+        <v>26</v>
+      </c>
+      <c r="C7" s="1">
+        <v>26</v>
+      </c>
+      <c r="D7" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="E7" s="4">
+        <v>21</v>
+      </c>
+      <c r="F7" s="4">
+        <v>18</v>
+      </c>
+      <c r="G7" s="1">
+        <f t="shared" ref="G7:G14" si="3">E7+F7</f>
+        <v>39</v>
+      </c>
+      <c r="H7" s="15">
+        <f t="shared" si="2"/>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="1">
+        <v>28</v>
+      </c>
+      <c r="C8" s="1">
+        <v>24</v>
+      </c>
+      <c r="D8" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="E8" s="4">
+        <v>21</v>
+      </c>
+      <c r="F8" s="4">
+        <v>21</v>
+      </c>
+      <c r="G8" s="1">
+        <f t="shared" si="3"/>
+        <v>42</v>
+      </c>
+      <c r="H8" s="15">
+        <f t="shared" si="2"/>
+        <v>80.769230769230774</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="1">
+        <v>22</v>
+      </c>
+      <c r="C9" s="1">
+        <v>30</v>
+      </c>
+      <c r="D9" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="E9" s="4">
+        <v>18</v>
+      </c>
+      <c r="F9" s="4">
+        <v>25</v>
+      </c>
+      <c r="G9" s="1">
+        <f t="shared" si="3"/>
+        <v>43</v>
+      </c>
+      <c r="H9" s="15">
+        <f t="shared" si="2"/>
+        <v>82.692307692307693</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="1">
+        <v>23</v>
+      </c>
+      <c r="C10" s="1">
+        <v>23</v>
+      </c>
+      <c r="D10" s="4">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="E10" s="4">
+        <v>17</v>
+      </c>
+      <c r="F10" s="4">
+        <v>14</v>
+      </c>
+      <c r="G10" s="1">
+        <f t="shared" si="3"/>
+        <v>31</v>
+      </c>
+      <c r="H10" s="15">
+        <f t="shared" si="2"/>
+        <v>67.391304347826093</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="1">
+        <v>17</v>
+      </c>
+      <c r="C11" s="1">
+        <v>25</v>
+      </c>
+      <c r="D11" s="4">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="E11" s="4">
+        <v>16</v>
+      </c>
+      <c r="F11" s="4">
+        <v>21</v>
+      </c>
+      <c r="G11" s="1">
+        <f t="shared" si="3"/>
+        <v>37</v>
+      </c>
+      <c r="H11" s="15">
+        <f t="shared" si="2"/>
+        <v>88.095238095238088</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="1">
+        <v>27</v>
+      </c>
+      <c r="C12" s="1">
+        <v>18</v>
+      </c>
+      <c r="D12" s="4">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="E12" s="4">
+        <v>23</v>
+      </c>
+      <c r="F12" s="4">
+        <v>16</v>
+      </c>
+      <c r="G12" s="1">
+        <f t="shared" si="3"/>
+        <v>39</v>
+      </c>
+      <c r="H12" s="15">
+        <f t="shared" si="2"/>
+        <v>86.666666666666671</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="1">
+        <v>19</v>
+      </c>
+      <c r="C13" s="1">
+        <v>23</v>
+      </c>
+      <c r="D13" s="4">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="E13" s="4">
+        <v>16</v>
+      </c>
+      <c r="F13" s="4">
+        <v>19</v>
+      </c>
+      <c r="G13" s="1">
+        <f t="shared" si="3"/>
+        <v>35</v>
+      </c>
+      <c r="H13" s="15">
+        <f t="shared" si="2"/>
+        <v>83.333333333333343</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="21">
+        <v>16</v>
+      </c>
+      <c r="C14" s="21">
+        <v>19</v>
+      </c>
+      <c r="D14" s="16">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="E14" s="21">
+        <v>14</v>
+      </c>
+      <c r="F14" s="16">
+        <v>16</v>
+      </c>
+      <c r="G14" s="21">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+      <c r="H14" s="22">
+        <f t="shared" si="2"/>
+        <v>85.714285714285708</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" s="11">
+        <f t="shared" ref="B15:G15" si="4">SUM(B5:B14)</f>
+        <v>271</v>
+      </c>
+      <c r="C15" s="11">
+        <f t="shared" si="4"/>
+        <v>260</v>
+      </c>
+      <c r="D15" s="11">
+        <f t="shared" si="4"/>
+        <v>531</v>
+      </c>
+      <c r="E15" s="11">
+        <f t="shared" si="4"/>
+        <v>230</v>
+      </c>
+      <c r="F15" s="11">
+        <f t="shared" si="4"/>
+        <v>203</v>
+      </c>
+      <c r="G15" s="11">
+        <f t="shared" si="4"/>
+        <v>433</v>
+      </c>
+      <c r="H15" s="25">
+        <f t="shared" si="2"/>
+        <v>81.544256120527308</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E16" s="23"/>
+      <c r="F16" s="24"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:H3"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Wrong Entry" error="Kindly Enter Value Less then Available Boys" sqref="E5:E13" xr:uid="{1797ACB8-5C2F-4B08-8940-8EEB1BBE1DA8}">
+      <formula1>B5&gt;=E5</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Wrong Entry" error="Kindly Enter Value Less then Available Girls" sqref="F5:F14" xr:uid="{773387D3-F5B4-4BEE-BA3D-C7021FAEE1B5}">
+      <formula1>C5&gt;=F5</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B03221B-01B2-459B-BF82-E169ECED329C}">
+  <dimension ref="A1:H16"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5703125" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" customWidth="1"/>
+    <col min="7" max="7" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.35">
+      <c r="A1" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="28"/>
+    </row>
+    <row r="2" spans="1:8" ht="21" x14ac:dyDescent="0.35">
+      <c r="A2" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="31"/>
+    </row>
+    <row r="3" spans="1:8" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="32">
+        <v>45680</v>
+      </c>
+      <c r="B3" s="33"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
+      <c r="H3" s="34"/>
+    </row>
+    <row r="4" spans="1:8" ht="48" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="18">
+        <v>61</v>
+      </c>
+      <c r="C5" s="18">
+        <v>49</v>
+      </c>
+      <c r="D5" s="18">
+        <f>B5+C5</f>
+        <v>110</v>
+      </c>
+      <c r="E5" s="18">
+        <v>15</v>
+      </c>
+      <c r="F5" s="18">
+        <v>16</v>
+      </c>
+      <c r="G5" s="18">
+        <f t="shared" ref="G5" si="0">E5+F5</f>
+        <v>31</v>
+      </c>
+      <c r="H5" s="19">
+        <f>G5/D5*100</f>
+        <v>28.18181818181818</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="1">
+        <v>32</v>
+      </c>
+      <c r="C6" s="1">
+        <v>23</v>
+      </c>
+      <c r="D6" s="4">
+        <f t="shared" ref="D6:D14" si="1">B6+C6</f>
+        <v>55</v>
+      </c>
+      <c r="E6" s="4">
+        <v>27</v>
+      </c>
+      <c r="F6" s="4">
+        <v>16</v>
+      </c>
+      <c r="G6" s="1">
+        <f>E6+F6</f>
+        <v>43</v>
+      </c>
+      <c r="H6" s="15">
+        <f t="shared" ref="H6:H15" si="2">G6/D6*100</f>
+        <v>78.181818181818187</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="1">
+        <v>26</v>
+      </c>
+      <c r="C7" s="1">
+        <v>26</v>
+      </c>
+      <c r="D7" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="E7" s="4">
+        <v>18</v>
+      </c>
+      <c r="F7" s="4">
+        <v>19</v>
+      </c>
+      <c r="G7" s="1">
+        <f t="shared" ref="G7:G14" si="3">E7+F7</f>
+        <v>37</v>
+      </c>
+      <c r="H7" s="15">
+        <f t="shared" si="2"/>
+        <v>71.15384615384616</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="1">
+        <v>28</v>
+      </c>
+      <c r="C8" s="1">
+        <v>24</v>
+      </c>
+      <c r="D8" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="E8" s="4">
+        <v>15</v>
+      </c>
+      <c r="F8" s="4">
+        <v>14</v>
+      </c>
+      <c r="G8" s="1">
+        <f t="shared" si="3"/>
+        <v>29</v>
+      </c>
+      <c r="H8" s="15">
+        <f t="shared" si="2"/>
+        <v>55.769230769230774</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="1">
+        <v>22</v>
+      </c>
+      <c r="C9" s="1">
+        <v>30</v>
+      </c>
+      <c r="D9" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="E9" s="4">
+        <v>14</v>
+      </c>
+      <c r="F9" s="4">
+        <v>20</v>
+      </c>
+      <c r="G9" s="1">
+        <f t="shared" si="3"/>
+        <v>34</v>
+      </c>
+      <c r="H9" s="15">
+        <f t="shared" si="2"/>
+        <v>65.384615384615387</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="1">
+        <v>23</v>
+      </c>
+      <c r="C10" s="1">
+        <v>23</v>
+      </c>
+      <c r="D10" s="4">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="E10" s="4">
+        <v>16</v>
+      </c>
+      <c r="F10" s="4">
+        <v>13</v>
+      </c>
+      <c r="G10" s="1">
+        <f t="shared" si="3"/>
+        <v>29</v>
+      </c>
+      <c r="H10" s="15">
+        <f t="shared" si="2"/>
+        <v>63.04347826086957</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="1">
+        <v>17</v>
+      </c>
+      <c r="C11" s="1">
+        <v>25</v>
+      </c>
+      <c r="D11" s="4">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="E11" s="4">
+        <v>13</v>
+      </c>
+      <c r="F11" s="4">
+        <v>18</v>
+      </c>
+      <c r="G11" s="1">
+        <f t="shared" si="3"/>
+        <v>31</v>
+      </c>
+      <c r="H11" s="15">
+        <f t="shared" si="2"/>
+        <v>73.80952380952381</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="1">
+        <v>27</v>
+      </c>
+      <c r="C12" s="1">
+        <v>18</v>
+      </c>
+      <c r="D12" s="4">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="E12" s="4">
+        <v>23</v>
+      </c>
+      <c r="F12" s="4">
+        <v>15</v>
+      </c>
+      <c r="G12" s="1">
+        <f t="shared" si="3"/>
+        <v>38</v>
+      </c>
+      <c r="H12" s="15">
+        <f t="shared" si="2"/>
+        <v>84.444444444444443</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="1">
+        <v>19</v>
+      </c>
+      <c r="C13" s="1">
+        <v>23</v>
+      </c>
+      <c r="D13" s="4">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="E13" s="4">
+        <v>13</v>
+      </c>
+      <c r="F13" s="4">
+        <v>20</v>
+      </c>
+      <c r="G13" s="1">
+        <f t="shared" si="3"/>
+        <v>33</v>
+      </c>
+      <c r="H13" s="15">
+        <f t="shared" si="2"/>
+        <v>78.571428571428569</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="21">
+        <v>16</v>
+      </c>
+      <c r="C14" s="21">
+        <v>19</v>
+      </c>
+      <c r="D14" s="16">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="E14" s="21">
+        <v>13</v>
+      </c>
+      <c r="F14" s="16">
+        <v>13</v>
+      </c>
+      <c r="G14" s="21">
+        <f t="shared" si="3"/>
+        <v>26</v>
+      </c>
+      <c r="H14" s="22">
+        <f t="shared" si="2"/>
+        <v>74.285714285714292</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" s="11">
+        <f t="shared" ref="B15:G15" si="4">SUM(B5:B14)</f>
+        <v>271</v>
+      </c>
+      <c r="C15" s="11">
+        <f t="shared" si="4"/>
+        <v>260</v>
+      </c>
+      <c r="D15" s="11">
+        <f t="shared" si="4"/>
+        <v>531</v>
+      </c>
+      <c r="E15" s="11">
+        <f t="shared" si="4"/>
+        <v>167</v>
+      </c>
+      <c r="F15" s="11">
+        <f t="shared" si="4"/>
+        <v>164</v>
+      </c>
+      <c r="G15" s="11">
+        <f t="shared" si="4"/>
+        <v>331</v>
+      </c>
+      <c r="H15" s="25">
+        <f t="shared" si="2"/>
+        <v>62.335216572504706</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E16" s="23"/>
+      <c r="F16" s="24"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:H3"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Wrong Entry" error="Kindly Enter Value Less then Available Girls" sqref="F5:F14" xr:uid="{4AF20BBE-3E42-4B1A-B9B6-9D368B56227D}">
+      <formula1>C5&gt;=F5</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Wrong Entry" error="Kindly Enter Value Less then Available Boys" sqref="E5:E13" xr:uid="{A5BFBC9F-FA05-450E-AD3D-ED659F88CA79}">
+      <formula1>B5&gt;=E5</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{107E5DC9-11DF-44A8-91DF-C9D8A21964B6}">
+  <dimension ref="A1:H16"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5703125" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" customWidth="1"/>
+    <col min="7" max="7" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.35">
+      <c r="A1" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="28"/>
+    </row>
+    <row r="2" spans="1:8" ht="21" x14ac:dyDescent="0.35">
+      <c r="A2" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="31"/>
+    </row>
+    <row r="3" spans="1:8" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="32">
+        <v>45680</v>
+      </c>
+      <c r="B3" s="33"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
+      <c r="H3" s="34"/>
+    </row>
+    <row r="4" spans="1:8" ht="48" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="18">
+        <v>61</v>
+      </c>
+      <c r="C5" s="18">
+        <v>49</v>
+      </c>
+      <c r="D5" s="18">
+        <f>B5+C5</f>
+        <v>110</v>
+      </c>
+      <c r="E5" s="18"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18">
+        <f t="shared" ref="G5" si="0">E5+F5</f>
+        <v>0</v>
+      </c>
+      <c r="H5" s="19">
+        <f>G5/D5*100</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="1">
+        <v>32</v>
+      </c>
+      <c r="C6" s="1">
+        <v>23</v>
+      </c>
+      <c r="D6" s="4">
+        <f t="shared" ref="D6:D14" si="1">B6+C6</f>
+        <v>55</v>
+      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="1">
+        <f>E6+F6</f>
+        <v>0</v>
+      </c>
+      <c r="H6" s="15">
+        <f t="shared" ref="H6:H15" si="2">G6/D6*100</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="1">
+        <v>26</v>
+      </c>
+      <c r="C7" s="1">
+        <v>26</v>
+      </c>
+      <c r="D7" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="1">
+        <f t="shared" ref="G7:G14" si="3">E7+F7</f>
+        <v>0</v>
+      </c>
+      <c r="H7" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="1">
+        <v>28</v>
+      </c>
+      <c r="C8" s="1">
+        <v>24</v>
+      </c>
+      <c r="D8" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H8" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="1">
+        <v>22</v>
+      </c>
+      <c r="C9" s="1">
+        <v>30</v>
+      </c>
+      <c r="D9" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H9" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="1">
+        <v>23</v>
+      </c>
+      <c r="C10" s="1">
+        <v>23</v>
+      </c>
+      <c r="D10" s="4">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H10" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="1">
+        <v>17</v>
+      </c>
+      <c r="C11" s="1">
+        <v>25</v>
+      </c>
+      <c r="D11" s="4">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H11" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="1">
+        <v>27</v>
+      </c>
+      <c r="C12" s="1">
+        <v>18</v>
+      </c>
+      <c r="D12" s="4">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H12" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="1">
+        <v>19</v>
+      </c>
+      <c r="C13" s="1">
+        <v>23</v>
+      </c>
+      <c r="D13" s="4">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H13" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="21">
+        <v>16</v>
+      </c>
+      <c r="C14" s="21">
+        <v>19</v>
+      </c>
+      <c r="D14" s="16">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="E14" s="21"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="21">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H14" s="22">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" s="11">
+        <f t="shared" ref="B15:G15" si="4">SUM(B5:B14)</f>
+        <v>271</v>
+      </c>
+      <c r="C15" s="11">
+        <f t="shared" si="4"/>
+        <v>260</v>
+      </c>
+      <c r="D15" s="11">
+        <f t="shared" si="4"/>
+        <v>531</v>
+      </c>
+      <c r="E15" s="11">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F15" s="11">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G15" s="11">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H15" s="25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E16" s="23"/>
+      <c r="F16" s="24"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:H3"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Wrong Entry" error="Kindly Enter Value Less then Available Boys" sqref="E5:E13" xr:uid="{6B92B8A2-9FD4-425D-B6FE-9B8E87147166}">
+      <formula1>B5&gt;=E5</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Wrong Entry" error="Kindly Enter Value Less then Available Girls" sqref="F5:F14" xr:uid="{5F70843E-DA46-4E2F-991E-6AA389496AED}">
+      <formula1>C5&gt;=F5</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Sindhi Muslim/People Diary/January-2025.xlsx
+++ b/Sindhi Muslim/People Diary/January-2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\People Diary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B5B1975-A462-4127-A060-B00E8933A340}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DB47F40-1C70-453A-A1C6-2D58484D972D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="17" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="19" activeTab="24" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01-01-2025" sheetId="1" r:id="rId1"/>
@@ -36,6 +36,8 @@
     <sheet name="24-01-2025" sheetId="21" r:id="rId21"/>
     <sheet name="25-01-2025" sheetId="22" r:id="rId22"/>
     <sheet name="27-01-2025" sheetId="23" r:id="rId23"/>
+    <sheet name="29-01-2025" sheetId="24" r:id="rId24"/>
+    <sheet name="30-01-2025" sheetId="25" r:id="rId25"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -56,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="21">
   <si>
     <t>CLASS WISE ENROLLED SUMMARY</t>
   </si>
@@ -1451,11 +1453,11 @@
         <v>32</v>
       </c>
       <c r="C6" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6" s="4">
         <f t="shared" ref="D6:D14" si="1">B6+C6</f>
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
@@ -1848,11 +1850,11 @@
         <v>32</v>
       </c>
       <c r="C6" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6" s="4">
         <f t="shared" ref="D6:D14" si="1">B6+C6</f>
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E6" s="4">
         <v>27</v>
@@ -1866,7 +1868,7 @@
       </c>
       <c r="H6" s="15">
         <f t="shared" ref="H6:H14" si="2">G6/D6*100</f>
-        <v>89.090909090909093</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2249,11 +2251,11 @@
         <v>32</v>
       </c>
       <c r="C6" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6" s="4">
         <f t="shared" ref="D6:D14" si="1">B6+C6</f>
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E6" s="4">
         <v>27</v>
@@ -2267,7 +2269,7 @@
       </c>
       <c r="H6" s="15">
         <f t="shared" ref="H6:H14" si="2">G6/D6*100</f>
-        <v>80</v>
+        <v>78.571428571428569</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2512,11 +2514,11 @@
       </c>
       <c r="C15" s="11">
         <f t="shared" si="4"/>
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D15" s="11">
         <f t="shared" si="4"/>
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E15" s="11">
         <f t="shared" si="4"/>
@@ -2668,11 +2670,11 @@
         <v>32</v>
       </c>
       <c r="C6" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6" s="4">
         <f t="shared" ref="D6:D14" si="1">B6+C6</f>
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E6" s="4">
         <v>31</v>
@@ -2686,7 +2688,7 @@
       </c>
       <c r="H6" s="15">
         <f t="shared" ref="H6:H15" si="2">G6/D6*100</f>
-        <v>90.909090909090907</v>
+        <v>89.285714285714292</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -2931,11 +2933,11 @@
       </c>
       <c r="C15" s="11">
         <f t="shared" si="4"/>
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D15" s="11">
         <f t="shared" si="4"/>
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E15" s="11">
         <f t="shared" si="4"/>
@@ -2951,7 +2953,7 @@
       </c>
       <c r="H15" s="25">
         <f t="shared" si="2"/>
-        <v>83.050847457627114</v>
+        <v>82.89473684210526</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -3090,11 +3092,11 @@
         <v>32</v>
       </c>
       <c r="C6" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6" s="4">
         <f t="shared" ref="D6:D14" si="1">B6+C6</f>
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E6" s="4">
         <v>30</v>
@@ -3108,7 +3110,7 @@
       </c>
       <c r="H6" s="15">
         <f t="shared" ref="H6:H15" si="2">G6/D6*100</f>
-        <v>87.272727272727266</v>
+        <v>85.714285714285708</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3353,11 +3355,11 @@
       </c>
       <c r="C15" s="11">
         <f t="shared" si="4"/>
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D15" s="11">
         <f t="shared" si="4"/>
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E15" s="11">
         <f t="shared" si="4"/>
@@ -3373,7 +3375,7 @@
       </c>
       <c r="H15" s="25">
         <f t="shared" si="2"/>
-        <v>83.804143126177024</v>
+        <v>83.646616541353382</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -3512,11 +3514,11 @@
         <v>32</v>
       </c>
       <c r="C6" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6" s="4">
         <f t="shared" ref="D6:D14" si="1">B6+C6</f>
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E6" s="4">
         <v>26</v>
@@ -3530,7 +3532,7 @@
       </c>
       <c r="H6" s="15">
         <f t="shared" ref="H6:H15" si="2">G6/D6*100</f>
-        <v>85.454545454545453</v>
+        <v>83.928571428571431</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3775,11 +3777,11 @@
       </c>
       <c r="C15" s="11">
         <f t="shared" si="4"/>
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D15" s="11">
         <f t="shared" si="4"/>
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E15" s="11">
         <f t="shared" si="4"/>
@@ -3795,7 +3797,7 @@
       </c>
       <c r="H15" s="25">
         <f t="shared" si="2"/>
-        <v>79.472693032015059</v>
+        <v>79.323308270676691</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -3934,11 +3936,11 @@
         <v>32</v>
       </c>
       <c r="C6" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6" s="4">
         <f t="shared" ref="D6:D14" si="1">B6+C6</f>
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E6" s="4">
         <v>28</v>
@@ -3952,7 +3954,7 @@
       </c>
       <c r="H6" s="15">
         <f t="shared" ref="H6:H15" si="2">G6/D6*100</f>
-        <v>80</v>
+        <v>78.571428571428569</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -4197,11 +4199,11 @@
       </c>
       <c r="C15" s="11">
         <f t="shared" si="4"/>
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D15" s="11">
         <f t="shared" si="4"/>
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E15" s="11">
         <f t="shared" si="4"/>
@@ -4217,7 +4219,7 @@
       </c>
       <c r="H15" s="25">
         <f t="shared" si="2"/>
-        <v>70.621468926553675</v>
+        <v>70.488721804511272</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -4356,11 +4358,11 @@
         <v>32</v>
       </c>
       <c r="C6" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6" s="4">
         <f t="shared" ref="D6:D14" si="1">B6+C6</f>
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E6" s="4">
         <v>29</v>
@@ -4374,7 +4376,7 @@
       </c>
       <c r="H6" s="15">
         <f t="shared" ref="H6:H15" si="2">G6/D6*100</f>
-        <v>87.272727272727266</v>
+        <v>85.714285714285708</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -4619,11 +4621,11 @@
       </c>
       <c r="C15" s="11">
         <f t="shared" si="4"/>
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D15" s="11">
         <f t="shared" si="4"/>
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E15" s="11">
         <f t="shared" si="4"/>
@@ -4639,7 +4641,7 @@
       </c>
       <c r="H15" s="25">
         <f t="shared" si="2"/>
-        <v>81.355932203389841</v>
+        <v>81.203007518796994</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -4778,11 +4780,11 @@
         <v>32</v>
       </c>
       <c r="C6" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6" s="4">
         <f t="shared" ref="D6:D14" si="1">B6+C6</f>
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E6" s="4">
         <v>31</v>
@@ -4796,7 +4798,7 @@
       </c>
       <c r="H6" s="15">
         <f t="shared" ref="H6:H15" si="2">G6/D6*100</f>
-        <v>87.272727272727266</v>
+        <v>85.714285714285708</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -5041,11 +5043,11 @@
       </c>
       <c r="C15" s="11">
         <f t="shared" si="4"/>
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D15" s="11">
         <f t="shared" si="4"/>
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E15" s="11">
         <f t="shared" si="4"/>
@@ -5061,7 +5063,7 @@
       </c>
       <c r="H15" s="25">
         <f t="shared" si="2"/>
-        <v>82.674199623352166</v>
+        <v>82.518796992481199</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -5200,11 +5202,11 @@
         <v>32</v>
       </c>
       <c r="C6" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6" s="4">
         <f t="shared" ref="D6:D14" si="1">B6+C6</f>
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E6" s="4">
         <v>32</v>
@@ -5218,7 +5220,7 @@
       </c>
       <c r="H6" s="15">
         <f t="shared" ref="H6:H15" si="2">G6/D6*100</f>
-        <v>90.909090909090907</v>
+        <v>89.285714285714292</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -5463,11 +5465,11 @@
       </c>
       <c r="C15" s="11">
         <f t="shared" si="4"/>
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D15" s="11">
         <f t="shared" si="4"/>
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E15" s="11">
         <f t="shared" si="4"/>
@@ -5483,7 +5485,7 @@
       </c>
       <c r="H15" s="25">
         <f t="shared" si="2"/>
-        <v>81.16760828625236</v>
+        <v>81.015037593984957</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -6044,11 +6046,11 @@
         <v>32</v>
       </c>
       <c r="C6" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6" s="4">
         <f t="shared" ref="D6:D14" si="1">B6+C6</f>
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E6" s="4">
         <v>27</v>
@@ -6062,7 +6064,7 @@
       </c>
       <c r="H6" s="15">
         <f t="shared" ref="H6:H15" si="2">G6/D6*100</f>
-        <v>85.454545454545453</v>
+        <v>83.928571428571431</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -6307,11 +6309,11 @@
       </c>
       <c r="C15" s="11">
         <f t="shared" si="4"/>
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D15" s="11">
         <f t="shared" si="4"/>
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E15" s="11">
         <f t="shared" si="4"/>
@@ -6327,7 +6329,7 @@
       </c>
       <c r="H15" s="25">
         <f t="shared" si="2"/>
-        <v>77.212806026365342</v>
+        <v>77.067669172932327</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -6393,7 +6395,7 @@
     </row>
     <row r="3" spans="1:8" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="32">
-        <v>45680</v>
+        <v>45681</v>
       </c>
       <c r="B3" s="33"/>
       <c r="C3" s="33"/>
@@ -6466,11 +6468,11 @@
         <v>32</v>
       </c>
       <c r="C6" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6" s="4">
         <f t="shared" ref="D6:D14" si="1">B6+C6</f>
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E6" s="4">
         <v>29</v>
@@ -6484,7 +6486,7 @@
       </c>
       <c r="H6" s="15">
         <f t="shared" ref="H6:H15" si="2">G6/D6*100</f>
-        <v>87.272727272727266</v>
+        <v>85.714285714285708</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -6729,11 +6731,11 @@
       </c>
       <c r="C15" s="11">
         <f t="shared" si="4"/>
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D15" s="11">
         <f t="shared" si="4"/>
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E15" s="11">
         <f t="shared" si="4"/>
@@ -6749,7 +6751,7 @@
       </c>
       <c r="H15" s="25">
         <f t="shared" si="2"/>
-        <v>81.544256120527308</v>
+        <v>81.390977443609032</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -6815,7 +6817,7 @@
     </row>
     <row r="3" spans="1:8" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="32">
-        <v>45680</v>
+        <v>45682</v>
       </c>
       <c r="B3" s="33"/>
       <c r="C3" s="33"/>
@@ -6888,11 +6890,11 @@
         <v>32</v>
       </c>
       <c r="C6" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6" s="4">
         <f t="shared" ref="D6:D14" si="1">B6+C6</f>
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E6" s="4">
         <v>27</v>
@@ -6906,7 +6908,7 @@
       </c>
       <c r="H6" s="15">
         <f t="shared" ref="H6:H15" si="2">G6/D6*100</f>
-        <v>78.181818181818187</v>
+        <v>76.785714285714292</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -7151,11 +7153,11 @@
       </c>
       <c r="C15" s="11">
         <f t="shared" si="4"/>
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D15" s="11">
         <f t="shared" si="4"/>
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E15" s="11">
         <f t="shared" si="4"/>
@@ -7171,7 +7173,7 @@
       </c>
       <c r="H15" s="25">
         <f t="shared" si="2"/>
-        <v>62.335216572504706</v>
+        <v>62.218045112781951</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -7237,7 +7239,7 @@
     </row>
     <row r="3" spans="1:8" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="32">
-        <v>45680</v>
+        <v>45684</v>
       </c>
       <c r="B3" s="33"/>
       <c r="C3" s="33"/>
@@ -7287,15 +7289,19 @@
         <f>B5+C5</f>
         <v>110</v>
       </c>
-      <c r="E5" s="18"/>
-      <c r="F5" s="18"/>
+      <c r="E5" s="18">
+        <v>53</v>
+      </c>
+      <c r="F5" s="18">
+        <v>37</v>
+      </c>
       <c r="G5" s="18">
         <f t="shared" ref="G5" si="0">E5+F5</f>
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H5" s="19">
         <f>G5/D5*100</f>
-        <v>0</v>
+        <v>81.818181818181827</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -7306,21 +7312,25 @@
         <v>32</v>
       </c>
       <c r="C6" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6" s="4">
         <f t="shared" ref="D6:D14" si="1">B6+C6</f>
-        <v>55</v>
-      </c>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
+        <v>56</v>
+      </c>
+      <c r="E6" s="4">
+        <v>30</v>
+      </c>
+      <c r="F6" s="4">
+        <v>13</v>
+      </c>
       <c r="G6" s="1">
         <f>E6+F6</f>
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="H6" s="15">
         <f t="shared" ref="H6:H15" si="2">G6/D6*100</f>
-        <v>0</v>
+        <v>76.785714285714292</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -7337,15 +7347,19 @@
         <f t="shared" si="1"/>
         <v>52</v>
       </c>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
+      <c r="E7" s="4">
+        <v>18</v>
+      </c>
+      <c r="F7" s="4">
+        <v>19</v>
+      </c>
       <c r="G7" s="1">
         <f t="shared" ref="G7:G14" si="3">E7+F7</f>
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="H7" s="15">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>71.15384615384616</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -7362,15 +7376,19 @@
         <f t="shared" si="1"/>
         <v>52</v>
       </c>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
+      <c r="E8" s="4">
+        <v>18</v>
+      </c>
+      <c r="F8" s="4">
+        <v>19</v>
+      </c>
       <c r="G8" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="H8" s="15">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>71.15384615384616</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -7387,15 +7405,19 @@
         <f t="shared" si="1"/>
         <v>52</v>
       </c>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
+      <c r="E9" s="4">
+        <v>11</v>
+      </c>
+      <c r="F9" s="4">
+        <v>26</v>
+      </c>
       <c r="G9" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="H9" s="15">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>71.15384615384616</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -7412,15 +7434,19 @@
         <f t="shared" si="1"/>
         <v>46</v>
       </c>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
+      <c r="E10" s="4">
+        <v>17</v>
+      </c>
+      <c r="F10" s="4">
+        <v>16</v>
+      </c>
       <c r="G10" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="H10" s="15">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>71.739130434782609</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -7437,15 +7463,19 @@
         <f t="shared" si="1"/>
         <v>42</v>
       </c>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
+      <c r="E11" s="4">
+        <v>13</v>
+      </c>
+      <c r="F11" s="4">
+        <v>19</v>
+      </c>
       <c r="G11" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="H11" s="15">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>76.19047619047619</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -7462,15 +7492,19 @@
         <f t="shared" si="1"/>
         <v>45</v>
       </c>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
+      <c r="E12" s="4">
+        <v>18</v>
+      </c>
+      <c r="F12" s="4">
+        <v>14</v>
+      </c>
       <c r="G12" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="H12" s="15">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>71.111111111111114</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -7487,15 +7521,19 @@
         <f t="shared" si="1"/>
         <v>42</v>
       </c>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
+      <c r="E13" s="4">
+        <v>11</v>
+      </c>
+      <c r="F13" s="4">
+        <v>16</v>
+      </c>
       <c r="G13" s="1">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="H13" s="15">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>64.285714285714292</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -7512,15 +7550,19 @@
         <f t="shared" si="1"/>
         <v>35</v>
       </c>
-      <c r="E14" s="21"/>
-      <c r="F14" s="16"/>
+      <c r="E14" s="21">
+        <v>14</v>
+      </c>
+      <c r="F14" s="16">
+        <v>16</v>
+      </c>
       <c r="G14" s="21">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H14" s="22">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>85.714285714285708</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -7533,27 +7575,27 @@
       </c>
       <c r="C15" s="11">
         <f t="shared" si="4"/>
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D15" s="11">
         <f t="shared" si="4"/>
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E15" s="11">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>203</v>
       </c>
       <c r="F15" s="11">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>195</v>
       </c>
       <c r="G15" s="11">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>398</v>
       </c>
       <c r="H15" s="25">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>74.812030075187977</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -7571,6 +7613,810 @@
       <formula1>B5&gt;=E5</formula1>
     </dataValidation>
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Wrong Entry" error="Kindly Enter Value Less then Available Girls" sqref="F5:F14" xr:uid="{5F70843E-DA46-4E2F-991E-6AA389496AED}">
+      <formula1>C5&gt;=F5</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACE092E5-22BB-4B31-BEA4-1946C96FEA91}">
+  <dimension ref="A1:H16"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5703125" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" customWidth="1"/>
+    <col min="7" max="7" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.35">
+      <c r="A1" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="28"/>
+    </row>
+    <row r="2" spans="1:8" ht="21" x14ac:dyDescent="0.35">
+      <c r="A2" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="31"/>
+    </row>
+    <row r="3" spans="1:8" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="32">
+        <v>45686</v>
+      </c>
+      <c r="B3" s="33"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
+      <c r="H3" s="34"/>
+    </row>
+    <row r="4" spans="1:8" ht="48" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="18">
+        <v>61</v>
+      </c>
+      <c r="C5" s="18">
+        <v>49</v>
+      </c>
+      <c r="D5" s="18">
+        <f>B5+C5</f>
+        <v>110</v>
+      </c>
+      <c r="E5" s="18">
+        <v>51</v>
+      </c>
+      <c r="F5" s="18">
+        <v>41</v>
+      </c>
+      <c r="G5" s="18">
+        <f t="shared" ref="G5" si="0">E5+F5</f>
+        <v>92</v>
+      </c>
+      <c r="H5" s="19">
+        <f>G5/D5*100</f>
+        <v>83.636363636363626</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="1">
+        <v>32</v>
+      </c>
+      <c r="C6" s="1">
+        <v>24</v>
+      </c>
+      <c r="D6" s="4">
+        <f t="shared" ref="D6:D14" si="1">B6+C6</f>
+        <v>56</v>
+      </c>
+      <c r="E6" s="4">
+        <v>20</v>
+      </c>
+      <c r="F6" s="4">
+        <v>17</v>
+      </c>
+      <c r="G6" s="1">
+        <f>E6+F6</f>
+        <v>37</v>
+      </c>
+      <c r="H6" s="15">
+        <f t="shared" ref="H6:H15" si="2">G6/D6*100</f>
+        <v>66.071428571428569</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="1">
+        <v>26</v>
+      </c>
+      <c r="C7" s="1">
+        <v>26</v>
+      </c>
+      <c r="D7" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="E7" s="4">
+        <v>22</v>
+      </c>
+      <c r="F7" s="4">
+        <v>18</v>
+      </c>
+      <c r="G7" s="1">
+        <f t="shared" ref="G7:G14" si="3">E7+F7</f>
+        <v>40</v>
+      </c>
+      <c r="H7" s="15">
+        <f t="shared" si="2"/>
+        <v>76.923076923076934</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="1">
+        <v>28</v>
+      </c>
+      <c r="C8" s="1">
+        <v>24</v>
+      </c>
+      <c r="D8" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="E8" s="4">
+        <v>21</v>
+      </c>
+      <c r="F8" s="4">
+        <v>22</v>
+      </c>
+      <c r="G8" s="1">
+        <f t="shared" si="3"/>
+        <v>43</v>
+      </c>
+      <c r="H8" s="15">
+        <f t="shared" si="2"/>
+        <v>82.692307692307693</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="1">
+        <v>22</v>
+      </c>
+      <c r="C9" s="1">
+        <v>30</v>
+      </c>
+      <c r="D9" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="E9" s="4">
+        <v>17</v>
+      </c>
+      <c r="F9" s="4">
+        <v>25</v>
+      </c>
+      <c r="G9" s="1">
+        <f t="shared" si="3"/>
+        <v>42</v>
+      </c>
+      <c r="H9" s="15">
+        <f t="shared" si="2"/>
+        <v>80.769230769230774</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="1">
+        <v>23</v>
+      </c>
+      <c r="C10" s="1">
+        <v>23</v>
+      </c>
+      <c r="D10" s="4">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="E10" s="4">
+        <v>18</v>
+      </c>
+      <c r="F10" s="4">
+        <v>15</v>
+      </c>
+      <c r="G10" s="1">
+        <f t="shared" si="3"/>
+        <v>33</v>
+      </c>
+      <c r="H10" s="15">
+        <f t="shared" si="2"/>
+        <v>71.739130434782609</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="1">
+        <v>17</v>
+      </c>
+      <c r="C11" s="1">
+        <v>25</v>
+      </c>
+      <c r="D11" s="4">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="E11" s="4">
+        <v>16</v>
+      </c>
+      <c r="F11" s="4">
+        <v>20</v>
+      </c>
+      <c r="G11" s="1">
+        <f t="shared" si="3"/>
+        <v>36</v>
+      </c>
+      <c r="H11" s="15">
+        <f t="shared" si="2"/>
+        <v>85.714285714285708</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="1">
+        <v>27</v>
+      </c>
+      <c r="C12" s="1">
+        <v>18</v>
+      </c>
+      <c r="D12" s="4">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="E12" s="4">
+        <v>21</v>
+      </c>
+      <c r="F12" s="4">
+        <v>16</v>
+      </c>
+      <c r="G12" s="1">
+        <f t="shared" si="3"/>
+        <v>37</v>
+      </c>
+      <c r="H12" s="15">
+        <f t="shared" si="2"/>
+        <v>82.222222222222214</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="1">
+        <v>19</v>
+      </c>
+      <c r="C13" s="1">
+        <v>23</v>
+      </c>
+      <c r="D13" s="4">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="E13" s="4">
+        <v>15</v>
+      </c>
+      <c r="F13" s="4">
+        <v>19</v>
+      </c>
+      <c r="G13" s="1">
+        <f t="shared" si="3"/>
+        <v>34</v>
+      </c>
+      <c r="H13" s="15">
+        <f t="shared" si="2"/>
+        <v>80.952380952380949</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="21">
+        <v>16</v>
+      </c>
+      <c r="C14" s="21">
+        <v>19</v>
+      </c>
+      <c r="D14" s="16">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="E14" s="21">
+        <v>13</v>
+      </c>
+      <c r="F14" s="16">
+        <v>16</v>
+      </c>
+      <c r="G14" s="21">
+        <f t="shared" si="3"/>
+        <v>29</v>
+      </c>
+      <c r="H14" s="22">
+        <f t="shared" si="2"/>
+        <v>82.857142857142861</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" s="11">
+        <f t="shared" ref="B15:G15" si="4">SUM(B5:B14)</f>
+        <v>271</v>
+      </c>
+      <c r="C15" s="11">
+        <f t="shared" si="4"/>
+        <v>261</v>
+      </c>
+      <c r="D15" s="11">
+        <f t="shared" si="4"/>
+        <v>532</v>
+      </c>
+      <c r="E15" s="11">
+        <f t="shared" si="4"/>
+        <v>214</v>
+      </c>
+      <c r="F15" s="11">
+        <f t="shared" si="4"/>
+        <v>209</v>
+      </c>
+      <c r="G15" s="11">
+        <f t="shared" si="4"/>
+        <v>423</v>
+      </c>
+      <c r="H15" s="25">
+        <f t="shared" si="2"/>
+        <v>79.511278195488728</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E16" s="23"/>
+      <c r="F16" s="24"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:H3"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Wrong Entry" error="Kindly Enter Value Less then Available Girls" sqref="F5:F14" xr:uid="{160051C7-1DB5-48E1-99B9-E19397B2F206}">
+      <formula1>C5&gt;=F5</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Wrong Entry" error="Kindly Enter Value Less then Available Boys" sqref="E5:E13" xr:uid="{3DD331C5-E0BC-428A-AB87-7F0FE41D5C44}">
+      <formula1>B5&gt;=E5</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF7D6CB9-70D6-46BD-8DC8-A9FAF11E7AB6}">
+  <dimension ref="A1:H16"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5703125" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" customWidth="1"/>
+    <col min="7" max="7" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.35">
+      <c r="A1" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="28"/>
+    </row>
+    <row r="2" spans="1:8" ht="21" x14ac:dyDescent="0.35">
+      <c r="A2" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="31"/>
+    </row>
+    <row r="3" spans="1:8" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="32">
+        <v>45687</v>
+      </c>
+      <c r="B3" s="33"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
+      <c r="H3" s="34"/>
+    </row>
+    <row r="4" spans="1:8" ht="48" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="18">
+        <v>61</v>
+      </c>
+      <c r="C5" s="18">
+        <v>49</v>
+      </c>
+      <c r="D5" s="18">
+        <f>B5+C5</f>
+        <v>110</v>
+      </c>
+      <c r="E5" s="18"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18">
+        <f t="shared" ref="G5" si="0">E5+F5</f>
+        <v>0</v>
+      </c>
+      <c r="H5" s="19">
+        <f>G5/D5*100</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="1">
+        <v>32</v>
+      </c>
+      <c r="C6" s="1">
+        <v>24</v>
+      </c>
+      <c r="D6" s="4">
+        <f t="shared" ref="D6:D14" si="1">B6+C6</f>
+        <v>56</v>
+      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="1">
+        <f>E6+F6</f>
+        <v>0</v>
+      </c>
+      <c r="H6" s="15">
+        <f t="shared" ref="H6:H15" si="2">G6/D6*100</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="1">
+        <v>26</v>
+      </c>
+      <c r="C7" s="1">
+        <v>26</v>
+      </c>
+      <c r="D7" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="1">
+        <f t="shared" ref="G7:G14" si="3">E7+F7</f>
+        <v>0</v>
+      </c>
+      <c r="H7" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="1">
+        <v>28</v>
+      </c>
+      <c r="C8" s="1">
+        <v>24</v>
+      </c>
+      <c r="D8" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H8" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="1">
+        <v>22</v>
+      </c>
+      <c r="C9" s="1">
+        <v>30</v>
+      </c>
+      <c r="D9" s="4">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H9" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="1">
+        <v>23</v>
+      </c>
+      <c r="C10" s="1">
+        <v>23</v>
+      </c>
+      <c r="D10" s="4">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H10" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="1">
+        <v>17</v>
+      </c>
+      <c r="C11" s="1">
+        <v>25</v>
+      </c>
+      <c r="D11" s="4">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H11" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="1">
+        <v>27</v>
+      </c>
+      <c r="C12" s="1">
+        <v>18</v>
+      </c>
+      <c r="D12" s="4">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H12" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="1">
+        <v>19</v>
+      </c>
+      <c r="C13" s="1">
+        <v>23</v>
+      </c>
+      <c r="D13" s="4">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="1">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H13" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="21">
+        <v>16</v>
+      </c>
+      <c r="C14" s="21">
+        <v>19</v>
+      </c>
+      <c r="D14" s="16">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="E14" s="21"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="21">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H14" s="22">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" s="11">
+        <f t="shared" ref="B15:G15" si="4">SUM(B5:B14)</f>
+        <v>271</v>
+      </c>
+      <c r="C15" s="11">
+        <f t="shared" si="4"/>
+        <v>261</v>
+      </c>
+      <c r="D15" s="11">
+        <f t="shared" si="4"/>
+        <v>532</v>
+      </c>
+      <c r="E15" s="11">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F15" s="11">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G15" s="11">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H15" s="25">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E16" s="23"/>
+      <c r="F16" s="24"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:H3"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Wrong Entry" error="Kindly Enter Value Less then Available Boys" sqref="E5:E13" xr:uid="{EF61987D-9AD7-4891-A54D-FDC946B646BC}">
+      <formula1>B5&gt;=E5</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Wrong Entry" error="Kindly Enter Value Less then Available Girls" sqref="F5:F14" xr:uid="{D3B829F5-24B6-4F6A-A816-DAD7A2712EC3}">
       <formula1>C5&gt;=F5</formula1>
     </dataValidation>
   </dataValidations>
@@ -9409,11 +10255,11 @@
         <v>32</v>
       </c>
       <c r="C7" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D7" s="4">
         <f t="shared" si="1"/>
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E7" s="1">
         <v>24</v>
@@ -9427,7 +10273,7 @@
       </c>
       <c r="H7" s="15">
         <f t="shared" si="2"/>
-        <v>81.818181818181827</v>
+        <v>80.357142857142861</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -9802,11 +10648,11 @@
         <v>32</v>
       </c>
       <c r="C6" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6" s="4">
         <f t="shared" ref="D6:D14" si="1">B6+C6</f>
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E6" s="1">
         <v>25</v>
@@ -9820,7 +10666,7 @@
       </c>
       <c r="H6" s="15">
         <f t="shared" ref="H6:H14" si="2">G6/D6*100</f>
-        <v>81.818181818181827</v>
+        <v>80.357142857142861</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -10195,11 +11041,11 @@
         <v>32</v>
       </c>
       <c r="C6" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6" s="4">
         <f t="shared" ref="D6:D14" si="1">B6+C6</f>
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E6" s="4">
         <v>29</v>
@@ -10213,7 +11059,7 @@
       </c>
       <c r="H6" s="15">
         <f t="shared" ref="H6:H14" si="2">G6/D6*100</f>
-        <v>89.090909090909093</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
